--- a/2026-10-25/weekly-2026-10-25.xlsx
+++ b/2026-10-25/weekly-2026-10-25.xlsx
@@ -2952,7 +2952,7 @@
     <row r="14">
       <c r="B14" s="74" t="inlineStr">
         <is>
-          <t>网页版：https://psylch.github.io/sourcing/2026-10-25/</t>
+          <t>网页版：https://psylch.github.io/rising-projects/2026-10-25/</t>
         </is>
       </c>
     </row>

--- a/2026-10-25/weekly-2026-10-25.xlsx
+++ b/2026-10-25/weekly-2026-10-25.xlsx
@@ -13,15 +13,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'华人项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全球项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'链接'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,8 +33,8 @@
     <numFmt numFmtId="164" formatCode="&quot;#&quot;0"/>
     <numFmt numFmtId="165" formatCode="+#,##0&quot; 🚀&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot; ★&quot;"/>
-    <numFmt numFmtId="167" formatCode="+#,##0"/>
-    <numFmt numFmtId="168" formatCode="&quot;PH #&quot;0"/>
+    <numFmt numFmtId="167" formatCode="&quot;PH #&quot;0"/>
+    <numFmt numFmtId="168" formatCode="+#,##0"/>
     <numFmt numFmtId="169" formatCode="#,##0&quot; 票&quot;"/>
   </numFmts>
   <fonts count="16">
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -264,6 +264,39 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -273,13 +306,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -288,37 +321,16 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -333,7 +345,7 @@
     <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -348,59 +360,53 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -409,10 +415,16 @@
     <xf numFmtId="166" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -797,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -941,14 +953,14 @@
         <v>4</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>1165</v>
+        <v>2371</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>139696</v>
+        <v>140740</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>10-19 #11 +154 → 10-20 #4 +1,011🚀</t>
+          <t>10-19 #11 +154 → 10-20 #4 +1,011🚀 → 10-21 #6 +1,206</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
@@ -1112,51 +1124,51 @@
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Kronos</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>🚀 Kronos</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>面向金融 K 线的预训练基础模型（45 家交易所、超 120 亿条 K 线），做价格/波动率预测与合成 K 线</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>363</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>41640</v>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>10-20 #9 +363</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="D6" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1096</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>42344</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>10-20 #9 +363 → 10-21 #8 +733🚀</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Yu Shi（中文名未查到）</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>一作、仓库作者</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>南京大学本科；清华大学在读博士</t>
         </is>
       </c>
-      <c r="K6" s="16" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1177,32 +1189,32 @@
           </r>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>北京（清华在读）</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>shi-y23@mails.tsinghua.edu.cn</t>
         </is>
       </c>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="14" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P6" s="15" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="Q6" s="16" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
@@ -1216,22 +1228,22 @@
       <c r="E7" s="13" t="n"/>
       <c r="F7" s="13" t="n"/>
       <c r="G7" s="13" t="n"/>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>其余作者：Zongliang Fu、Shuo Chen、Bohan Zhao、Wei Xu、Changshui Zhang、Jian Li</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>论文合著者</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1260,12 +1272,12 @@
           </r>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="M7" s="16" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>fzl22@mails.tsinghua.edu.cn
 zhaobh23@mails.tsinghua.edu.cn
@@ -1275,76 +1287,76 @@
 lapordge@gmail.com</t>
         </is>
       </c>
-      <c r="N7" s="21" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O7" s="22" t="inlineStr">
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P7" s="16" t="inlineStr">
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q7" s="23" t="inlineStr">
+      <c r="Q7" s="15" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Wally by Willow</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>语音</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Mac AI 语音输入工具 Willow 的新功能 Wally，学习用户写作风格；YC 公司，2025 年成立，团队 7 人，总部旧金山
 团队：按姓名与背景判断为华人，本人族裔表述未查到</t>
         </is>
       </c>
-      <c r="D8" s="27" t="n">
+      <c r="D8" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="21" t="n">
         <v>123</v>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>10-19 #7</t>
         </is>
       </c>
-      <c r="H8" s="30" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>Allan Guo</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO</t>
         </is>
       </c>
-      <c r="J8" s="26" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>斯坦福计算机系（2023–2024，离校创业）；University of Toronto Schools</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1365,32 +1377,32 @@
           </r>
         </is>
       </c>
-      <c r="L8" s="26" t="inlineStr">
+      <c r="L8" s="18" t="inlineStr">
         <is>
           <t>旧金山</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t>allanguo@stanford.edu</t>
         </is>
       </c>
-      <c r="N8" s="31" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O8" s="32" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P8" s="26" t="inlineStr">
+      <c r="P8" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q8" s="26" t="inlineStr">
+      <c r="Q8" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
@@ -1404,22 +1416,22 @@
       <c r="E9" s="13" t="n"/>
       <c r="F9" s="13" t="n"/>
       <c r="G9" s="13" t="n"/>
-      <c r="H9" s="30" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>Lawrence Liu</t>
         </is>
       </c>
-      <c r="I9" s="26" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>联合创始人兼 CTO</t>
         </is>
       </c>
-      <c r="J9" s="26" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>斯坦福计算机学士；就读过卡内基梅隆；Fox Chapel Area High School</t>
         </is>
       </c>
-      <c r="K9" s="26" t="inlineStr">
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1448,49 +1460,377 @@
           </r>
         </is>
       </c>
-      <c r="L9" s="26" t="inlineStr">
+      <c r="L9" s="18" t="inlineStr">
         <is>
           <t>LinkedIn 写匹兹堡；公司在旧金山</t>
         </is>
       </c>
-      <c r="M9" s="31" t="inlineStr">
+      <c r="M9" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="N9" s="31" t="inlineStr">
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O9" s="32" t="inlineStr">
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P9" s="26" t="inlineStr">
+      <c r="P9" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q9" s="26" t="inlineStr">
+      <c r="Q9" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Mintlify 常驻文档智能体，自动随代码更新文档；YC 公司</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>122</v>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
+        <is>
+          <t>10-20 #6</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="I10" s="27" t="inlineStr">
+        <is>
+          <t>联合创始人兼 CEO</t>
+        </is>
+      </c>
+      <c r="J10" s="27" t="inlineStr">
+        <is>
+          <t>康奈尔大学信息科学学士</t>
+        </is>
+      </c>
+      <c r="K10" s="27" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">创办 FoodFul、People（后被收购）；Bain Capital Ventures；2021 起创办 Mintlify；曾在 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Meta</t>
+          </r>
+        </is>
+      </c>
+      <c r="L10" s="27" t="inlineStr">
+        <is>
+          <t>旧金山</t>
+        </is>
+      </c>
+      <c r="M10" s="27" t="inlineStr">
+        <is>
+          <t>han@mintlify.com</t>
+        </is>
+      </c>
+      <c r="N10" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O10" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P10" s="27" t="inlineStr">
+        <is>
+          <t>个人站
+X</t>
+        </is>
+      </c>
+      <c r="Q10" s="27" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>Hahnbee Lee</t>
+        </is>
+      </c>
+      <c r="I11" s="27" t="inlineStr">
+        <is>
+          <t>联合创始人</t>
+        </is>
+      </c>
+      <c r="J11" s="27" t="inlineStr">
+        <is>
+          <t>康奈尔大学计算机本科</t>
+        </is>
+      </c>
+      <c r="K11" s="27" t="inlineStr">
+        <is>
+          <t>与 Han 共同创办 Mintlify；早年参与 People</t>
+        </is>
+      </c>
+      <c r="L11" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M11" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N11" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O11" s="34" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P11" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q11" s="35" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Menlo Research 的可定制人形机器人；新加坡开放 AI/机器人实验室
+团队：新加坡华人背景（籍贯/姓氏）；Daniel 公开写在新加坡长大</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>10-20 #8</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>Daniel Ong</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>联合创始人</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>斯坦福大学（转读计算机）</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>新加坡警察 5 年；早期以太坊相关创业；与 Nicole 创办 Menlo Research</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="inlineStr">
+        <is>
+          <t>dan@daniel.ai</t>
+        </is>
+      </c>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O12" s="36" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P12" s="18" t="inlineStr">
+        <is>
+          <t>个人站
+GitHub</t>
+        </is>
+      </c>
+      <c r="Q12" s="18" t="inlineStr">
+        <is>
+          <t>来源1、来源2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>Nicole Zhu</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>联合创始人</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>斯坦福机械工程学士、计算机硕士</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">前 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Google</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> 高级工程师；Parity、Gojek/GoTo 经历</t>
+          </r>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O13" s="24" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P13" s="18" t="inlineStr">
+        <is>
+          <t>X
+个人站</t>
+        </is>
+      </c>
+      <c r="Q13" s="18" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>orca</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>编程智能体</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1511,36 +1851,36 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="36" t="n">
+      <c r="D14" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="37" t="n">
-        <v>2736</v>
-      </c>
-      <c r="F10" s="38" t="n">
-        <v>98240</v>
-      </c>
-      <c r="G10" s="35" t="inlineStr">
-        <is>
-          <t>10-18/19 #5 +1,146 → 10-20 #2 +1,590</t>
-        </is>
-      </c>
-      <c r="H10" s="39" t="inlineStr">
+      <c r="E14" s="41" t="n">
+        <v>4301</v>
+      </c>
+      <c r="F14" s="42" t="n">
+        <v>99710</v>
+      </c>
+      <c r="G14" s="39" t="inlineStr">
+        <is>
+          <t>10-18/19 #5 +1,146 → 10-20 #2 +1,590 → 10-21 #3 +1,565</t>
+        </is>
+      </c>
+      <c r="H14" s="43" t="inlineStr">
         <is>
           <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
-      <c r="I10" s="35" t="inlineStr">
+      <c r="I14" s="39" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO，Orca 维护者</t>
         </is>
       </c>
-      <c r="J10" s="35" t="inlineStr">
+      <c r="J14" s="39" t="inlineStr">
         <is>
           <t>康奈尔大学校友（专业与学位未查到）</t>
         </is>
       </c>
-      <c r="K10" s="35" t="inlineStr">
+      <c r="K14" s="39" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1569,62 +1909,62 @@
           </r>
         </is>
       </c>
-      <c r="L10" s="35" t="inlineStr">
+      <c r="L14" s="39" t="inlineStr">
         <is>
           <t>美国旧金山湾区</t>
         </is>
       </c>
-      <c r="M10" s="31" t="inlineStr">
+      <c r="M14" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="N10" s="31" t="inlineStr">
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O10" s="40" t="inlineStr">
+      <c r="O14" s="44" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P10" s="35" t="inlineStr">
+      <c r="P14" s="39" t="inlineStr">
         <is>
           <t>X
 GitHub</t>
         </is>
       </c>
-      <c r="Q10" s="35" t="inlineStr">
+      <c r="Q14" s="39" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="13" t="n"/>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="39" t="inlineStr">
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="43" t="inlineStr">
         <is>
           <t>Neil Parker</t>
         </is>
       </c>
-      <c r="I11" s="35" t="inlineStr">
+      <c r="I15" s="39" t="inlineStr">
         <is>
           <t>联合创始人兼 CTO（非华人，列作团队参考）</t>
         </is>
       </c>
-      <c r="J11" s="35" t="inlineStr">
+      <c r="J15" s="39" t="inlineStr">
         <is>
           <t>康奈尔大学校友</t>
         </is>
       </c>
-      <c r="K11" s="35" t="inlineStr">
+      <c r="K15" s="39" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1653,50 +1993,50 @@
           </r>
         </is>
       </c>
-      <c r="L11" s="35" t="inlineStr">
+      <c r="L15" s="39" t="inlineStr">
         <is>
           <t>美国旧金山湾区</t>
         </is>
       </c>
-      <c r="M11" s="31" t="inlineStr">
+      <c r="M15" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="N11" s="31" t="inlineStr">
+      <c r="N15" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O11" s="40" t="inlineStr">
+      <c r="O15" s="44" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P11" s="35" t="inlineStr">
+      <c r="P15" s="39" t="inlineStr">
         <is>
           <t>X
 GitHub</t>
         </is>
       </c>
-      <c r="Q11" s="35" t="inlineStr">
+      <c r="Q15" s="39" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="33" t="inlineStr">
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>CLI-Anything</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>智能体工具</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C16" s="39" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1717,36 +2057,36 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="41" t="n">
+      <c r="D16" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="42" t="n">
+      <c r="E16" s="46" t="n">
         <v>1195</v>
       </c>
-      <c r="F12" s="43" t="n">
+      <c r="F16" s="47" t="n">
         <v>55221</v>
       </c>
-      <c r="G12" s="35" t="inlineStr">
+      <c r="G16" s="39" t="inlineStr">
         <is>
           <t>10-18/19 #6 +589 → 10-20 #6 +606</t>
         </is>
       </c>
-      <c r="H12" s="39" t="inlineStr">
+      <c r="H16" s="43" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
+      <c r="I16" s="39" t="inlineStr">
         <is>
           <t>通讯作者、HKUDS / Data Intelligence Lab 负责人</t>
         </is>
       </c>
-      <c r="J12" s="35" t="inlineStr">
+      <c r="J16" s="39" t="inlineStr">
         <is>
           <t>University of Notre Dame 计算机博士；现港大计算机系助理教授</t>
         </is>
       </c>
-      <c r="K12" s="35" t="inlineStr">
+      <c r="K16" s="39" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1767,124 +2107,124 @@
           </r>
         </is>
       </c>
-      <c r="L12" s="35" t="inlineStr">
+      <c r="L16" s="39" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M12" s="35" t="inlineStr">
+      <c r="M16" s="39" t="inlineStr">
         <is>
           <t>chuang@cs.hku.hk
 chaohuang75@gmail.com</t>
         </is>
       </c>
-      <c r="N12" s="31" t="inlineStr">
+      <c r="N16" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O12" s="44" t="inlineStr">
+      <c r="O16" s="36" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P12" s="35" t="inlineStr">
+      <c r="P16" s="39" t="inlineStr">
         <is>
           <t>个人站
 GitHub 组织</t>
         </is>
       </c>
-      <c r="Q12" s="35" t="inlineStr">
+      <c r="Q16" s="39" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1">
-      <c r="A13" s="45" t="n"/>
-      <c r="B13" s="45" t="n"/>
-      <c r="C13" s="45" t="n"/>
-      <c r="D13" s="45" t="n"/>
-      <c r="E13" s="45" t="n"/>
-      <c r="F13" s="45" t="n"/>
-      <c r="G13" s="45" t="n"/>
-      <c r="H13" s="39" t="inlineStr">
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="48" t="n"/>
+      <c r="B17" s="48" t="n"/>
+      <c r="C17" s="48" t="n"/>
+      <c r="D17" s="48" t="n"/>
+      <c r="E17" s="48" t="n"/>
+      <c r="F17" s="48" t="n"/>
+      <c r="G17" s="48" t="n"/>
+      <c r="H17" s="43" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="I13" s="35" t="inlineStr">
+      <c r="I17" s="39" t="inlineStr">
         <is>
           <t>一作</t>
         </is>
       </c>
-      <c r="J13" s="35" t="inlineStr">
+      <c r="J17" s="39" t="inlineStr">
         <is>
           <t>香港大学博士（论文获 2026 ACM SIGKDD Dissertation Award Runner-Up）</t>
         </is>
       </c>
-      <c r="K13" s="35" t="inlineStr">
+      <c r="K17" s="39" t="inlineStr">
         <is>
           <t>主导 CLI-Anything；此前 UltraCUA、Aria-UI 等 computer-use 工作</t>
         </is>
       </c>
-      <c r="L13" s="35" t="inlineStr">
+      <c r="L17" s="39" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M13" s="35" t="inlineStr">
+      <c r="M17" s="39" t="inlineStr">
         <is>
           <t>itsyuhaoy@gmail.com
 yuhao-yang@outlook.com</t>
         </is>
       </c>
-      <c r="N13" s="31" t="inlineStr">
+      <c r="N17" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O13" s="44" t="inlineStr">
+      <c r="O17" s="36" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P13" s="35" t="inlineStr">
+      <c r="P17" s="39" t="inlineStr">
         <is>
           <t>个人站
 GitHub</t>
         </is>
       </c>
-      <c r="Q13" s="35" t="inlineStr">
+      <c r="Q17" s="39" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="64" customHeight="1">
-      <c r="A14" s="13" t="n"/>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="39" t="inlineStr">
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="43" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="I14" s="35" t="inlineStr">
+      <c r="I18" s="39" t="inlineStr">
         <is>
           <t>共同作者</t>
         </is>
       </c>
-      <c r="J14" s="35" t="inlineStr">
+      <c r="J18" s="39" t="inlineStr">
         <is>
           <t>浙江大学自动化本科（2020–2024）；香港大学计算机博士在读（2024–）</t>
         </is>
       </c>
-      <c r="K14" s="35" t="inlineStr">
+      <c r="K18" s="39" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1913,78 +2253,92 @@
           </r>
         </is>
       </c>
-      <c r="L14" s="35" t="inlineStr">
+      <c r="L18" s="39" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M14" s="35" t="inlineStr">
+      <c r="M18" s="39" t="inlineStr">
         <is>
           <t>tianyufan0504@gmail.com</t>
         </is>
       </c>
-      <c r="N14" s="31" t="inlineStr">
+      <c r="N18" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O14" s="44" t="inlineStr">
+      <c r="O18" s="36" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P14" s="35" t="inlineStr">
+      <c r="P18" s="39" t="inlineStr">
         <is>
           <t>个人站
 未在个人站显著标注主账号</t>
         </is>
       </c>
-      <c r="Q14" s="35" t="inlineStr">
+      <c r="Q18" s="39" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q14"/>
-  <mergeCells count="37">
-    <mergeCell ref="A12:A14"/>
+  <autoFilter ref="A3:Q18"/>
+  <mergeCells count="51">
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="C12:C14"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="G8:G9"/>
-    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="G10:G11"/>
+    <mergeCell ref="B14:B15"/>
     <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="E16:E18"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="G16:G18"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="G14:G15"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
-    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="F16:F18"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="F14:F15"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A16:A18"/>
     <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C15"/>
     <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D16:D18"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="F6:F7"/>
+    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1998,8 +2352,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId18"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2013,7 +2372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2127,21 +2486,21 @@
           <t>开源编程智能体</t>
         </is>
       </c>
-      <c r="E4" s="46" t="n">
+      <c r="E4" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="47" t="n">
-        <v>2725</v>
+      <c r="F4" s="50" t="n">
+        <v>3965</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>1414</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>217782</v>
+        <v>218894</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>10-19 #3 +1,414🚀 → 10-20 #3 +1,311</t>
+          <t>10-19 #3 +1,414🚀 → 10-20 #3 +1,311 → 10-21 #4 +1,240</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
@@ -2154,678 +2513,748 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L4" s="48" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>🚀 ai-memory</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>ponytail</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>智能体工具</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>编程智能体 CLI 的长期记忆与跨厂商交接</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n">
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>208 ⭐，总星 169,611，让 AI 智能体按「最懒高级工程师」思路写代码</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：能不写就不写</t>
+          </r>
+        </is>
+      </c>
+      <c r="E5" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="47" t="n">
-        <v>1178</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>666</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>11322</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>10-19 #8 +512🚀 → 10-20 #5 +666</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>Fabio Akita</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="F5" s="52" t="n">
+        <v>1208</v>
+      </c>
+      <c r="G5" s="53" t="n">
+        <v>1208</v>
+      </c>
+      <c r="H5" s="54" t="n">
+        <v>169611</v>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t>10-21 #5 +1,208</t>
+        </is>
+      </c>
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>作者 DietrichGebert</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>巴西</t>
+      <c r="L5" s="26" t="inlineStr">
+        <is>
+          <t>德文名</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>🚀 ai-memory</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>智能体工具</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>编程智能体 CLI 的长期记忆与跨厂商交接</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="50" t="n">
+        <v>1178</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>666</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>11322</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>10-19 #8 +512🚀 → 10-20 #5 +666</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Fabio Akita</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>🚀 headroom</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>智能体工具</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>把工具输出、日志、RAG 片段压缩后再喂给大模型，编程智能体少用约 20% token</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="50" t="n">
+        <v>859</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>549</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>76744</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>10-20 #10 +310 → 10-21 #11 +549🚀</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Tejas Chopra</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>昨日已核</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>graphify</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>编程智能体</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>总星 130,213，把代码库、文档、SQL、配置和 PDF 变成可查询知识图谱，供编程智能体用</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="56" t="n">
+        <v>802</v>
+      </c>
+      <c r="G8" s="57" t="n">
+        <v>802</v>
+      </c>
+      <c r="H8" s="58" t="n">
+        <v>130213</v>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>10-21 #7 +802</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>Safi Shamsi</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>伯明翰大学；YC S26</t>
+        </is>
+      </c>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>🚀 jasna</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>视频修复工具</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="47" t="n">
+      <c r="F9" s="50" t="n">
         <v>613</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G9" s="8" t="n">
         <v>498</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H9" s="9" t="n">
         <v>2879</v>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>10-19 #12 +115 → 10-20 #8 +498🚀</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L6" s="48" t="inlineStr">
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>headroom</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>agency-agents</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>智能体工具</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>把工具输出、日志、RAG 片段压缩后再喂给大模型，编程智能体少用约 20% token</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="n">
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>总星 162,328，一整套「AI 外包公司」式智能体角色包，从前端到社区运营</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="18" t="n">
-        <v>310</v>
-      </c>
-      <c r="G7" s="49" t="n">
-        <v>310</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>76232</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>10-20 #10 +310</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
-        <is>
-          <t>Tejas Chopra</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="F10" s="56" t="n">
+        <v>562</v>
+      </c>
+      <c r="G10" s="57" t="n">
+        <v>562</v>
+      </c>
+      <c r="H10" s="58" t="n">
+        <v>162328</v>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>10-21 #10 +562</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>Michael/Marek Sitarzewski</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="22" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>达拉斯</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>/dev/null</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>面向开发者的社交网络，JetBrains 办公室 48 小时直播从零写出来的开源项目</t>
+        </is>
+      </c>
+      <c r="E11" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="30" t="n">
+        <v>401</v>
+      </c>
+      <c r="I11" s="27" t="inlineStr">
+        <is>
+          <t>10-20 #1</t>
+        </is>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>Nuno Maduro、Brent Roose、Matthieu Napoli、Pauline Vos 等</t>
+        </is>
+      </c>
+      <c r="K11" s="27" t="inlineStr">
+        <is>
+          <t>JetBrains 直播</t>
+        </is>
+      </c>
+      <c r="L11" s="34" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>os-taxonomy</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="inlineStr">
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Beam.win</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>在一台 Mac 上跑 AI 智能体，在另一台上直接用它的窗口</t>
+        </is>
+      </c>
+      <c r="E12" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>293</v>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>10-19 #1</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>maker Hiten Shah、Sam Asante</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="36" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>Inbox Zero</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>开源 AI 邮件助手兼客户端，对标 Superhuman</t>
+        </is>
+      </c>
+      <c r="E13" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>279</v>
+      </c>
+      <c r="I13" s="27" t="inlineStr">
+        <is>
+          <t>10-18 #1</t>
+        </is>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>Elie Steinbock</t>
+        </is>
+      </c>
+      <c r="K13" s="27" t="inlineStr">
+        <is>
+          <t>以色列特拉维夫</t>
+        </is>
+      </c>
+      <c r="L13" s="34" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Composio Instant</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>给 AI 智能体接 1000+ 生产级工具，含托管鉴权与沙箱执行</t>
+        </is>
+      </c>
+      <c r="E14" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>251</v>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>10-20 #2</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Composio</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>常见公开资料</t>
+        </is>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>印度创始团队</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>🚀 ai-job-search</t>
+        </is>
+      </c>
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="D15" s="39" t="inlineStr">
+        <is>
+          <t>本机运行的 AI 求职框架，基于 Claude Code 评岗位、改简历、写求职信、备面试</t>
+        </is>
+      </c>
+      <c r="E15" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="62" t="n">
+        <v>9949</v>
+      </c>
+      <c r="G15" s="63" t="n">
+        <v>3861</v>
+      </c>
+      <c r="H15" s="64" t="n">
+        <v>60514</v>
+      </c>
+      <c r="I15" s="39" t="inlineStr">
+        <is>
+          <t>10-18/19 #1 +2,232🚀 → 10-20 #1 +3,856🚀 → 10-21 #1 +3,861</t>
+        </is>
+      </c>
+      <c r="J15" s="43" t="inlineStr">
+        <is>
+          <t>Mads Lorentzen</t>
+        </is>
+      </c>
+      <c r="K15" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="38" t="inlineStr">
+        <is>
+          <t>丹麦</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="37" t="inlineStr">
+        <is>
+          <t>VoiceStudio</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>Marble 开源的小学阶段知识点图谱，1,591 个微知识点、3,225 条先修关系</t>
-        </is>
-      </c>
-      <c r="E8" s="50" t="n">
-        <v>11</v>
-      </c>
-      <c r="F8" s="51" t="n">
-        <v>284</v>
-      </c>
-      <c r="G8" s="52" t="n">
-        <v>284</v>
-      </c>
-      <c r="H8" s="53" t="n">
-        <v>6106</v>
-      </c>
-      <c r="I8" s="26" t="inlineStr">
-        <is>
-          <t>10-20 #11 +284</t>
-        </is>
-      </c>
-      <c r="J8" s="30" t="inlineStr">
-        <is>
-          <t>Marble</t>
-        </is>
-      </c>
-      <c r="K8" s="26" t="inlineStr">
-        <is>
-          <t>Laura Mionel、Guillaume Boniface</t>
-        </is>
-      </c>
-      <c r="L8" s="44" t="inlineStr">
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>完全本地的开源 ElevenLabs 替代品</t>
+        </is>
+      </c>
+      <c r="E16" s="65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="46" t="n">
+        <v>2082</v>
+      </c>
+      <c r="G16" s="66" t="n">
+        <v>2082</v>
+      </c>
+      <c r="H16" s="47" t="n">
+        <v>75310</v>
+      </c>
+      <c r="I16" s="39" t="inlineStr">
+        <is>
+          <t>10-18/19 #2 +2,082</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>llm-course</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="K16" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="36" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>ruflo</t>
+        </is>
+      </c>
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>带路线图和 Colab 笔记本的大模型入门课</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>81</v>
-      </c>
-      <c r="G9" s="49" t="n">
-        <v>81</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>84016</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>10-19 #13 +81</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
+        <is>
+          <t>多智能体编排</t>
+        </is>
+      </c>
+      <c r="D17" s="39" t="inlineStr">
+        <is>
+          <t>多智能体蜂群编排框架</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="41" t="n">
+        <v>1761</v>
+      </c>
+      <c r="G17" s="68" t="n">
+        <v>684</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>77830</v>
+      </c>
+      <c r="I17" s="39" t="inlineStr">
+        <is>
+          <t>10-18/19 #7 +513 → 10-20 #7 +564 → 10-21 #9 +684</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="K9" s="16" t="inlineStr">
+      <c r="K17" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L17" s="36" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>Beam.win</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>在一台 Mac 上跑 AI 智能体，在另一台上直接用它的窗口</t>
-        </is>
-      </c>
-      <c r="E10" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>293</v>
-      </c>
-      <c r="I10" s="26" t="inlineStr">
-        <is>
-          <t>10-19 #1</t>
-        </is>
-      </c>
-      <c r="J10" s="30" t="inlineStr">
-        <is>
-          <t>maker Hiten Shah、Sam Asante</t>
-        </is>
-      </c>
-      <c r="K10" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="44" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Inbox Zero</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>开源 AI 邮件助手兼客户端，对标 Superhuman</t>
-        </is>
-      </c>
-      <c r="E11" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="56" t="n">
-        <v>279</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>10-18 #1</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>Elie Steinbock</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>以色列特拉维夫</t>
-        </is>
-      </c>
-      <c r="L11" s="22" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>MyLens</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="inlineStr">
-        <is>
-          <t>给每位观众一场 AI 驱动的一对一实时演示，现场答疑、加页</t>
-        </is>
-      </c>
-      <c r="E12" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" s="29" t="n">
-        <v>170</v>
-      </c>
-      <c r="I12" s="26" t="inlineStr">
-        <is>
-          <t>10-18 #2</t>
-        </is>
-      </c>
-      <c r="J12" s="30" t="inlineStr">
-        <is>
-          <t>Amin Zamani</t>
-        </is>
-      </c>
-      <c r="K12" s="26" t="inlineStr">
-        <is>
-          <t>、Ardalan Mirshani（美国克利夫兰），公司在芝加哥</t>
-        </is>
-      </c>
-      <c r="L12" s="25" t="inlineStr">
-        <is>
-          <t>伊斯坦布尔</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>readywhen</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>住在 WhatsApp 里的私人助理</t>
-        </is>
-      </c>
-      <c r="E13" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="56" t="n">
-        <v>167</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>10-19 #2</t>
-        </is>
-      </c>
-      <c r="J13" s="20" t="inlineStr">
-        <is>
-          <t>Huw Slater 等</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="22" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
-        <is>
-          <t>🚀 ai-job-search</t>
-        </is>
-      </c>
-      <c r="B14" s="34" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="D14" s="35" t="inlineStr">
-        <is>
-          <t>本机运行的 AI 求职框架，基于 Claude Code 评岗位、改简历、写求职信、备面试</t>
-        </is>
-      </c>
-      <c r="E14" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="60" t="n">
-        <v>6088</v>
-      </c>
-      <c r="G14" s="61" t="n">
-        <v>3856</v>
-      </c>
-      <c r="H14" s="62" t="n">
-        <v>57168</v>
-      </c>
-      <c r="I14" s="35" t="inlineStr">
-        <is>
-          <t>10-18/19 #1 +2,232🚀 → 10-20 #1 +3,856🚀</t>
-        </is>
-      </c>
-      <c r="J14" s="39" t="inlineStr">
-        <is>
-          <t>Mads Lorentzen</t>
-        </is>
-      </c>
-      <c r="K14" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L14" s="34" t="inlineStr">
-        <is>
-          <t>丹麦</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="33" t="inlineStr">
-        <is>
-          <t>VoiceStudio</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="inlineStr">
-        <is>
-          <t>完全本地的开源 ElevenLabs 替代品</t>
-        </is>
-      </c>
-      <c r="E15" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="37" t="n">
-        <v>2082</v>
-      </c>
-      <c r="G15" s="63" t="n">
-        <v>2082</v>
-      </c>
-      <c r="H15" s="38" t="n">
-        <v>75310</v>
-      </c>
-      <c r="I15" s="35" t="inlineStr">
-        <is>
-          <t>10-18/19 #2 +2,082</t>
-        </is>
-      </c>
-      <c r="J15" s="31" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K15" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="44" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>ruflo</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="inlineStr">
-        <is>
-          <t>多智能体编排</t>
-        </is>
-      </c>
-      <c r="D16" s="35" t="inlineStr">
-        <is>
-          <t>多智能体蜂群编排框架</t>
-        </is>
-      </c>
-      <c r="E16" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>1077</v>
-      </c>
-      <c r="G16" s="64" t="n">
-        <v>564</v>
-      </c>
-      <c r="H16" s="43" t="n">
-        <v>77172</v>
-      </c>
-      <c r="I16" s="35" t="inlineStr">
-        <is>
-          <t>10-18/19 #7 +513 → 10-20 #7 +564</t>
-        </is>
-      </c>
-      <c r="J16" s="31" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K16" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L16" s="44" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:L16"/>
+  <autoFilter ref="A3:L17"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
@@ -2844,6 +3273,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2865,92 +3295,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="B1" s="65" t="inlineStr">
+      <c r="B1" s="69" t="inlineStr">
         <is>
           <t>每周开源 / 产品 Sourcing 周报（2026-10-19 – 10-25）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="66" t="inlineStr">
-        <is>
-          <t>全球项目 13 个 · 华人项目 5 个 · 核心人物 11 位</t>
+      <c r="B2" s="70" t="inlineStr">
+        <is>
+          <t>全球项目 14 个 · 华人项目 7 个 · 核心人物 15 位</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="67" t="inlineStr">
+      <c r="B4" s="71" t="inlineStr">
         <is>
           <t>本周总览</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="69" t="inlineStr">
-        <is>
-          <t>本周进行中 · 已更新至 10-20（第 2/7 天），每天日报后自动刷新。</t>
+      <c r="B5" s="73" t="inlineStr">
+        <is>
+          <t>本周进行中 · 已更新至 10-21（第 3/7 天），每天日报后自动刷新。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="69" t="inlineStr">
-        <is>
-          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search；已收录全球项目 13 个、华人项目 5 个，今日新增华人项目：shiyu-coder/Kronos、Wally by Willow。</t>
+      <c r="B6" s="73" t="inlineStr">
+        <is>
+          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search；已收录全球项目 14 个、华人项目 7 个，今日新增华人项目：Mintlify Autopilot、Asimov 1。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="68" t="inlineStr">
+      <c r="A7" s="72" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="69" t="inlineStr">
+      <c r="B7" s="73" t="inlineStr">
         <is>
           <t>标「✨ 今日新增」的为今天首次上榜；灰色为前 3 周周报已出现过的项目，排在最后。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="70" t="inlineStr">
+      <c r="B9" s="74" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="71" t="inlineStr">
+      <c r="B10" s="75" t="inlineStr">
         <is>
           <t>黄底：日榜第 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="72" t="inlineStr">
+      <c r="B11" s="76" t="inlineStr">
         <is>
           <t>橙色：🚀 单日星增速明显放大（华人项目为 ≥ 前一天 1.5 倍）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="73" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>灰色斜体：未查到</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="74" t="inlineStr">
+      <c r="B14" s="78" t="inlineStr">
         <is>
           <t>网页版：https://psylch.github.io/rising-projects/2026-10-25/</t>
         </is>
@@ -2971,7 +3401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3023,979 +3453,1276 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Yoland Yan（闫，全名中文未查到）</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E4" s="75" t="inlineStr">
+      <c r="E4" s="79" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/yolandyan</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Yoland Yan（闫，全名中文未查到）</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>https://x.com/yoland_yan</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Yoland Yan（闫，全名中文未查到）</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E6" s="75" t="inlineStr">
+      <c r="E6" s="79" t="inlineStr">
         <is>
           <t>https://github.com/yoland68</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Yoland Yan（闫，全名中文未查到）</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>https://www.stackforce.co/talent/6a4f76052978e57b300365dc</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Yoland Yan（闫，全名中文未查到）</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E8" s="75" t="inlineStr">
+      <c r="E8" s="79" t="inlineStr">
         <is>
           <t>https://research.crustdata.com/company/comfyui</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Robin Huang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/robinjhuang</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Robin Huang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E10" s="75" t="inlineStr">
+      <c r="E10" s="79" t="inlineStr">
         <is>
           <t>https://x.com/robinjhuang</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Robin Huang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>https://github.com/robinjhuang</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Robin Huang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E12" s="75" t="inlineStr">
+      <c r="E12" s="79" t="inlineStr">
         <is>
           <t>https://www.getprog.ai/profile/5674242</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Robin Huang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/posts/concordia-international-school-shanghai_comfy-jobs-activity-7498183966257078272-p3K4</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>shiyu-coder/Kronos</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Yu Shi（中文名未查到）</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E14" s="75" t="inlineStr">
+      <c r="E14" s="79" t="inlineStr">
         <is>
           <t>https://github.com/shiyu-coder</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>shiyu-coder/Kronos</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Yu Shi（中文名未查到）</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>https://arxiv.org/html/2508.02739</t>
         </is>
       </c>
     </row>
     <row r="16" ht="64" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>shiyu-coder/Kronos</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>其余作者：Zongliang Fu、Shuo Chen、Bohan Zhao、Wei Xu、Changshui Zhang、Jian Li</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E16" s="75" t="inlineStr">
+      <c r="E16" s="79" t="inlineStr">
         <is>
           <t>https://arxiv.org/html/2508.02739</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Wally by Willow</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Allan Guo</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/allan-guo</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Wally by Willow</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Allan Guo</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E18" s="75" t="inlineStr">
+      <c r="E18" s="79" t="inlineStr">
         <is>
           <t>https://www.ycombinator.com/companies/willow</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Wally by Willow</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>Allan Guo</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>https://profiles.stanford.edu/allan-guo</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Wally by Willow</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Lawrence Liu</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E20" s="75" t="inlineStr">
+      <c r="E20" s="79" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/lawrenceliuu</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Wally by Willow</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>Lawrence Liu</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="35" t="inlineStr">
         <is>
           <t>https://www.stackforce.co/talent/lawrence-liu-ceo-69d744662a55b09f46c5deaa</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" s="79" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/handotdev</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>https://han.dev/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E24" s="79" t="inlineStr">
+        <is>
+          <t>https://x.com/handotdev</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E26" s="79" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/handotdev_my-grandparents-in-rural-china-use-ai-more-activity-7430270997586489346-XzLv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>Hahnbee Lee</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Daniel Ong</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E28" s="79" t="inlineStr">
+        <is>
+          <t>https://daniel.ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Daniel Ong</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>https://github.com/dan-menlo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Nicole Zhu</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E30" s="79" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/nicolezhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Nicole Zhu</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>https://x.com/freelerobot</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Nicole Zhu</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E32" s="79" t="inlineStr">
+        <is>
+          <t>https://nicole.ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E22" s="75" t="inlineStr">
+      <c r="E33" s="35" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/jinjingliang</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D34" s="18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E34" s="79" t="inlineStr">
         <is>
           <t>https://x.com/JinjingLiang</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B35" s="27" t="inlineStr">
         <is>
           <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D35" s="27" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E24" s="75" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>https://github.com/AmethystLiang</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D36" s="18" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E36" s="79" t="inlineStr">
         <is>
           <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B37" s="27" t="inlineStr">
         <is>
           <t>Neil Parker</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E26" s="75" t="inlineStr">
+      <c r="E37" s="35" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/neilwilliamparker</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Neil Parker</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D38" s="18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E38" s="79" t="inlineStr">
         <is>
           <t>https://x.com/nwparker_</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B39" s="27" t="inlineStr">
         <is>
           <t>Neil Parker</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D39" s="27" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E28" s="75" t="inlineStr">
+      <c r="E39" s="35" t="inlineStr">
         <is>
           <t>https://github.com/nwparker</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>Neil Parker</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D40" s="18" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E40" s="79" t="inlineStr">
         <is>
           <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B41" s="27" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E30" s="75" t="inlineStr">
+      <c r="E41" s="35" t="inlineStr">
         <is>
           <t>https://sites.google.com/view/chaoh</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D42" s="18" t="inlineStr">
         <is>
           <t>GitHub 组织</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E42" s="79" t="inlineStr">
         <is>
           <t>https://github.com/HKUDS</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="31" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B43" s="27" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D43" s="27" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E32" s="75" t="inlineStr">
+      <c r="E43" s="35" t="inlineStr">
         <is>
           <t>https://datascience.hku.hk/people/chao-huang/</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B44" s="18" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D44" s="18" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E44" s="79" t="inlineStr">
         <is>
           <t>https://www.ai.hku.hk/people/academic-staff/chuang</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="31" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B45" s="27" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="C34" s="25" t="inlineStr">
+      <c r="C45" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D45" s="27" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E34" s="75" t="inlineStr">
+      <c r="E45" s="35" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B46" s="18" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D46" s="18" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E46" s="79" t="inlineStr">
         <is>
           <t>https://yuh-yang.github.io</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="30" t="inlineStr">
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="31" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B47" s="27" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C36" s="25" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D47" s="27" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E36" s="75" t="inlineStr">
+      <c r="E47" s="35" t="inlineStr">
         <is>
           <t>https://github.com/yuh-yang</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D48" s="18" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E48" s="79" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="30" t="inlineStr">
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="31" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B49" s="27" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="C38" s="25" t="inlineStr">
+      <c r="C49" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D49" s="27" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E38" s="75" t="inlineStr">
+      <c r="E49" s="35" t="inlineStr">
         <is>
           <t>https://tianyufan0504.github.io/</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B50" s="18" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D50" s="18" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E50" s="79" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E39"/>
+  <autoFilter ref="A3:E50"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -4037,6 +4764,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId47"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/2026-10-25/weekly-2026-10-25.xlsx
+++ b/2026-10-25/weekly-2026-10-25.xlsx
@@ -13,15 +13,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'华人项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全球项目'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$60</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'链接'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -157,12 +157,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F7FA"/>
+        <fgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE68A"/>
+        <fgColor rgb="00F5F7FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -279,58 +279,62 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -342,13 +346,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -357,47 +361,22 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -415,16 +394,10 @@
     <xf numFmtId="166" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="168" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -437,11 +410,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -809,7 +782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -953,14 +926,14 @@
         <v>4</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>2371</v>
+        <v>3310</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>140740</v>
+        <v>141499</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>10-19 #11 +154 → 10-20 #4 +1,011🚀 → 10-21 #6 +1,206</t>
+          <t>10-19 #11 +154 → 10-20 #4 +1,011🚀 → 10-21 #6 +1,206 → 10-22 #5 +939</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
@@ -1140,17 +1113,17 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1096</v>
+        <v>1671</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>42344</v>
+        <v>42816</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>10-20 #9 +363 → 10-21 #8 +733🚀</t>
+          <t>10-20 #9 +363 → 10-21 #8 +733🚀 → 10-22 #6 +575</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -1308,55 +1281,331 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1">
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Computer Use Agent 做设计</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：直接操作设计软件，输出可编辑、可生产的源文件（PSD/AI/SVG）</t>
+          </r>
+        </is>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>264</v>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>10-21 #1</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>创始人兼 CEO</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>中科院计算所博士；NUS 博士后</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>NUS Show Lab 高级研究员；AssistGUI、AssistGPT、ShowUI 作者；2025-07 起创办 UseIt AI</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O8" s="24" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P8" s="25" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="Q8" s="18" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3、来源4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="26" t="n"/>
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="26" t="n"/>
+      <c r="G9" s="26" t="n"/>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>陈芷恒（Lindia Chen）</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>联合创始人兼增长负责人</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>新加坡国立大学硕士</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>曾在学而思做策划；上海中学校友</t>
+        </is>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N9" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O9" s="27" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P9" s="25" t="inlineStr">
+        <is>
+          <t>producthunt</t>
+        </is>
+      </c>
+      <c r="Q9" s="18" t="inlineStr">
+        <is>
+          <t>来源1、来源2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>丁云培</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>联合创始人兼产品负责人</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>UCL 计算机视觉硕士</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>连续创业者</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M10" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N10" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O10" s="27" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P10" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q10" s="25" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>刘佳琦</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>联合创始人兼技术负责人</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>北京工业大学人工智能博士</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>连续创业者；前 AIGC 创作分享平台技术负责人</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M11" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N11" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O11" s="27" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P11" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q11" s="25" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
           <t>Wally by Willow</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>语音</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>Mac AI 语音输入工具 Willow 的新功能 Wally，学习用户写作风格；YC 公司，2025 年成立，团队 7 人，总部旧金山
 团队：按姓名与背景判断为华人，本人族裔表述未查到</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D12" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F12" s="33" t="n">
         <v>123</v>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t>10-19 #7</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H12" s="34" t="inlineStr">
         <is>
           <t>Allan Guo</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J12" s="30" t="inlineStr">
         <is>
           <t>斯坦福计算机系（2023–2024，离校创业）；University of Toronto Schools</t>
         </is>
       </c>
-      <c r="K8" s="18" t="inlineStr">
+      <c r="K12" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1377,61 +1626,61 @@
           </r>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
+      <c r="L12" s="30" t="inlineStr">
         <is>
           <t>旧金山</t>
         </is>
       </c>
-      <c r="M8" s="18" t="inlineStr">
+      <c r="M12" s="30" t="inlineStr">
         <is>
           <t>allanguo@stanford.edu</t>
         </is>
       </c>
-      <c r="N8" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="N12" s="35" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O12" s="36" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P8" s="18" t="inlineStr">
+      <c r="P12" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q8" s="18" t="inlineStr">
+      <c r="Q12" s="30" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="13" t="n"/>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="22" t="inlineStr">
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="34" t="inlineStr">
         <is>
           <t>Lawrence Liu</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t>联合创始人兼 CTO</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J13" s="30" t="inlineStr">
         <is>
           <t>斯坦福计算机学士；就读过卡内基梅隆；Fox Chapel Area High School</t>
         </is>
       </c>
-      <c r="K9" s="18" t="inlineStr">
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1460,85 +1709,85 @@
           </r>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L13" s="30" t="inlineStr">
         <is>
           <t>LinkedIn 写匹兹堡；公司在旧金山</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N9" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O9" s="24" t="inlineStr">
+      <c r="M13" s="35" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N13" s="35" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O13" s="36" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P9" s="18" t="inlineStr">
+      <c r="P13" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q9" s="18" t="inlineStr">
+      <c r="Q13" s="30" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Mintlify Autopilot</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Mintlify 常驻文档智能体，自动随代码更新文档；YC 公司</t>
         </is>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D14" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F14" s="21" t="n">
         <v>122</v>
       </c>
-      <c r="G10" s="27" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>10-20 #6</t>
         </is>
       </c>
-      <c r="H10" s="31" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>Han Wang（王，生于河南新乡）</t>
         </is>
       </c>
-      <c r="I10" s="27" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO</t>
         </is>
       </c>
-      <c r="J10" s="27" t="inlineStr">
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>康奈尔大学信息科学学士</t>
         </is>
       </c>
-      <c r="K10" s="27" t="inlineStr">
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1559,206 +1808,206 @@
           </r>
         </is>
       </c>
-      <c r="L10" s="27" t="inlineStr">
+      <c r="L14" s="18" t="inlineStr">
         <is>
           <t>旧金山</t>
         </is>
       </c>
-      <c r="M10" s="27" t="inlineStr">
+      <c r="M14" s="18" t="inlineStr">
         <is>
           <t>han@mintlify.com</t>
         </is>
       </c>
-      <c r="N10" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O10" s="33" t="inlineStr">
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P10" s="27" t="inlineStr">
+      <c r="P14" s="18" t="inlineStr">
         <is>
           <t>个人站
 X</t>
         </is>
       </c>
-      <c r="Q10" s="27" t="inlineStr">
+      <c r="Q14" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="13" t="n"/>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="31" t="inlineStr">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>Hahnbee Lee</t>
         </is>
       </c>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>联合创始人</t>
         </is>
       </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="J15" s="18" t="inlineStr">
         <is>
           <t>康奈尔大学计算机本科</t>
         </is>
       </c>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>与 Han 共同创办 Mintlify；早年参与 People</t>
         </is>
       </c>
-      <c r="L11" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M11" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N11" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O11" s="34" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P11" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="Q11" s="35" t="inlineStr">
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M15" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N15" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O15" s="27" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q15" s="25" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Asimov 1</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>Menlo Research 的可定制人形机器人；新加坡开放 AI/机器人实验室
 团队：新加坡华人背景（籍贯/姓氏）；Daniel 公开写在新加坡长大</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D16" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F16" s="33" t="n">
         <v>110</v>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>10-20 #8</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H16" s="34" t="inlineStr">
         <is>
           <t>Daniel Ong</t>
         </is>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="I16" s="30" t="inlineStr">
         <is>
           <t>联合创始人</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="J16" s="30" t="inlineStr">
         <is>
           <t>斯坦福大学（转读计算机）</t>
         </is>
       </c>
-      <c r="K12" s="18" t="inlineStr">
+      <c r="K16" s="30" t="inlineStr">
         <is>
           <t>新加坡警察 5 年；早期以太坊相关创业；与 Nicole 创办 Menlo Research</t>
         </is>
       </c>
-      <c r="L12" s="18" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>新加坡</t>
         </is>
       </c>
-      <c r="M12" s="18" t="inlineStr">
+      <c r="M16" s="30" t="inlineStr">
         <is>
           <t>dan@daniel.ai</t>
         </is>
       </c>
-      <c r="N12" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O12" s="36" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P12" s="18" t="inlineStr">
+      <c r="N16" s="35" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O16" s="38" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P16" s="30" t="inlineStr">
         <is>
           <t>个人站
 GitHub</t>
         </is>
       </c>
-      <c r="Q12" s="18" t="inlineStr">
+      <c r="Q16" s="30" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="13" t="n"/>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="22" t="inlineStr">
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="34" t="inlineStr">
         <is>
           <t>Nicole Zhu</t>
         </is>
       </c>
-      <c r="I13" s="18" t="inlineStr">
+      <c r="I17" s="30" t="inlineStr">
         <is>
           <t>联合创始人</t>
         </is>
       </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="J17" s="30" t="inlineStr">
         <is>
           <t>斯坦福机械工程学士、计算机硕士</t>
         </is>
       </c>
-      <c r="K13" s="18" t="inlineStr">
+      <c r="K17" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1787,50 +2036,50 @@
           </r>
         </is>
       </c>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>新加坡</t>
         </is>
       </c>
-      <c r="M13" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O13" s="24" t="inlineStr">
+      <c r="M17" s="35" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N17" s="35" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O17" s="36" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P13" s="18" t="inlineStr">
+      <c r="P17" s="30" t="inlineStr">
         <is>
           <t>X
 个人站</t>
         </is>
       </c>
-      <c r="Q13" s="18" t="inlineStr">
+      <c r="Q17" s="30" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="64" customHeight="1">
-      <c r="A14" s="37" t="inlineStr">
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>orca</t>
         </is>
       </c>
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>编程智能体</t>
         </is>
       </c>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="C18" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1851,36 +2100,36 @@
           </r>
         </is>
       </c>
-      <c r="D14" s="40" t="n">
+      <c r="D18" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="41" t="n">
-        <v>4301</v>
-      </c>
-      <c r="F14" s="42" t="n">
-        <v>99710</v>
-      </c>
-      <c r="G14" s="39" t="inlineStr">
-        <is>
-          <t>10-18/19 #5 +1,146 → 10-20 #2 +1,590 → 10-21 #3 +1,565</t>
-        </is>
-      </c>
-      <c r="H14" s="43" t="inlineStr">
+      <c r="E18" s="43" t="n">
+        <v>5842</v>
+      </c>
+      <c r="F18" s="44" t="n">
+        <v>101219</v>
+      </c>
+      <c r="G18" s="41" t="inlineStr">
+        <is>
+          <t>10-18/19 #5 +1,146 → 10-20 #2 +1,590 → 10-21 #3 +1,565 → 10-22 #3 +1,541</t>
+        </is>
+      </c>
+      <c r="H18" s="45" t="inlineStr">
         <is>
           <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
-      <c r="I14" s="39" t="inlineStr">
+      <c r="I18" s="41" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO，Orca 维护者</t>
         </is>
       </c>
-      <c r="J14" s="39" t="inlineStr">
+      <c r="J18" s="41" t="inlineStr">
         <is>
           <t>康奈尔大学校友（专业与学位未查到）</t>
         </is>
       </c>
-      <c r="K14" s="39" t="inlineStr">
+      <c r="K18" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1909,62 +2158,62 @@
           </r>
         </is>
       </c>
-      <c r="L14" s="39" t="inlineStr">
+      <c r="L18" s="41" t="inlineStr">
         <is>
           <t>美国旧金山湾区</t>
         </is>
       </c>
-      <c r="M14" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N14" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O14" s="44" t="inlineStr">
+      <c r="M18" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N18" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O18" s="46" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P14" s="39" t="inlineStr">
+      <c r="P18" s="41" t="inlineStr">
         <is>
           <t>X
 GitHub</t>
         </is>
       </c>
-      <c r="Q14" s="39" t="inlineStr">
+      <c r="Q18" s="41" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="43" t="inlineStr">
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="45" t="inlineStr">
         <is>
           <t>Neil Parker</t>
         </is>
       </c>
-      <c r="I15" s="39" t="inlineStr">
+      <c r="I19" s="41" t="inlineStr">
         <is>
           <t>联合创始人兼 CTO（非华人，列作团队参考）</t>
         </is>
       </c>
-      <c r="J15" s="39" t="inlineStr">
+      <c r="J19" s="41" t="inlineStr">
         <is>
           <t>康奈尔大学校友</t>
         </is>
       </c>
-      <c r="K15" s="39" t="inlineStr">
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1993,50 +2242,50 @@
           </r>
         </is>
       </c>
-      <c r="L15" s="39" t="inlineStr">
+      <c r="L19" s="41" t="inlineStr">
         <is>
           <t>美国旧金山湾区</t>
         </is>
       </c>
-      <c r="M15" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N15" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O15" s="44" t="inlineStr">
+      <c r="M19" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N19" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O19" s="46" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P15" s="39" t="inlineStr">
+      <c r="P19" s="41" t="inlineStr">
         <is>
           <t>X
 GitHub</t>
         </is>
       </c>
-      <c r="Q15" s="39" t="inlineStr">
+      <c r="Q19" s="41" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="64" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>CLI-Anything</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>智能体工具</t>
         </is>
       </c>
-      <c r="C16" s="39" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2057,36 +2306,36 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="45" t="n">
+      <c r="D20" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="46" t="n">
+      <c r="E20" s="48" t="n">
         <v>1195</v>
       </c>
-      <c r="F16" s="47" t="n">
+      <c r="F20" s="49" t="n">
         <v>55221</v>
       </c>
-      <c r="G16" s="39" t="inlineStr">
+      <c r="G20" s="41" t="inlineStr">
         <is>
           <t>10-18/19 #6 +589 → 10-20 #6 +606</t>
         </is>
       </c>
-      <c r="H16" s="43" t="inlineStr">
+      <c r="H20" s="45" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="I16" s="39" t="inlineStr">
+      <c r="I20" s="41" t="inlineStr">
         <is>
           <t>通讯作者、HKUDS / Data Intelligence Lab 负责人</t>
         </is>
       </c>
-      <c r="J16" s="39" t="inlineStr">
+      <c r="J20" s="41" t="inlineStr">
         <is>
           <t>University of Notre Dame 计算机博士；现港大计算机系助理教授</t>
         </is>
       </c>
-      <c r="K16" s="39" t="inlineStr">
+      <c r="K20" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2107,124 +2356,124 @@
           </r>
         </is>
       </c>
-      <c r="L16" s="39" t="inlineStr">
+      <c r="L20" s="41" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M16" s="39" t="inlineStr">
+      <c r="M20" s="41" t="inlineStr">
         <is>
           <t>chuang@cs.hku.hk
 chaohuang75@gmail.com</t>
         </is>
       </c>
-      <c r="N16" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O16" s="36" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P16" s="39" t="inlineStr">
+      <c r="N20" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O20" s="27" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P20" s="41" t="inlineStr">
         <is>
           <t>个人站
 GitHub 组织</t>
         </is>
       </c>
-      <c r="Q16" s="39" t="inlineStr">
+      <c r="Q20" s="41" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="48" t="n"/>
-      <c r="B17" s="48" t="n"/>
-      <c r="C17" s="48" t="n"/>
-      <c r="D17" s="48" t="n"/>
-      <c r="E17" s="48" t="n"/>
-      <c r="F17" s="48" t="n"/>
-      <c r="G17" s="48" t="n"/>
-      <c r="H17" s="43" t="inlineStr">
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="26" t="n"/>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="26" t="n"/>
+      <c r="G21" s="26" t="n"/>
+      <c r="H21" s="45" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="I17" s="39" t="inlineStr">
+      <c r="I21" s="41" t="inlineStr">
         <is>
           <t>一作</t>
         </is>
       </c>
-      <c r="J17" s="39" t="inlineStr">
+      <c r="J21" s="41" t="inlineStr">
         <is>
           <t>香港大学博士（论文获 2026 ACM SIGKDD Dissertation Award Runner-Up）</t>
         </is>
       </c>
-      <c r="K17" s="39" t="inlineStr">
+      <c r="K21" s="41" t="inlineStr">
         <is>
           <t>主导 CLI-Anything；此前 UltraCUA、Aria-UI 等 computer-use 工作</t>
         </is>
       </c>
-      <c r="L17" s="39" t="inlineStr">
+      <c r="L21" s="41" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M17" s="39" t="inlineStr">
+      <c r="M21" s="41" t="inlineStr">
         <is>
           <t>itsyuhaoy@gmail.com
 yuhao-yang@outlook.com</t>
         </is>
       </c>
-      <c r="N17" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O17" s="36" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P17" s="39" t="inlineStr">
+      <c r="N21" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O21" s="27" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P21" s="41" t="inlineStr">
         <is>
           <t>个人站
 GitHub</t>
         </is>
       </c>
-      <c r="Q17" s="39" t="inlineStr">
+      <c r="Q21" s="41" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="64" customHeight="1">
-      <c r="A18" s="13" t="n"/>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="43" t="inlineStr">
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="45" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="I18" s="39" t="inlineStr">
+      <c r="I22" s="41" t="inlineStr">
         <is>
           <t>共同作者</t>
         </is>
       </c>
-      <c r="J18" s="39" t="inlineStr">
+      <c r="J22" s="41" t="inlineStr">
         <is>
           <t>浙江大学自动化本科（2020–2024）；香港大学计算机博士在读（2024–）</t>
         </is>
       </c>
-      <c r="K18" s="39" t="inlineStr">
+      <c r="K22" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2253,90 +2502,97 @@
           </r>
         </is>
       </c>
-      <c r="L18" s="39" t="inlineStr">
+      <c r="L22" s="41" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M18" s="39" t="inlineStr">
+      <c r="M22" s="41" t="inlineStr">
         <is>
           <t>tianyufan0504@gmail.com</t>
         </is>
       </c>
-      <c r="N18" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O18" s="36" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P18" s="39" t="inlineStr">
+      <c r="N22" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O22" s="27" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P22" s="41" t="inlineStr">
         <is>
           <t>个人站
 未在个人站显著标注主账号</t>
         </is>
       </c>
-      <c r="Q18" s="39" t="inlineStr">
+      <c r="Q22" s="41" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q18"/>
-  <mergeCells count="51">
-    <mergeCell ref="E8:E9"/>
+  <autoFilter ref="A3:Q22"/>
+  <mergeCells count="58">
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="G8:G9"/>
     <mergeCell ref="B12:B13"/>
+    <mergeCell ref="E8:E11"/>
     <mergeCell ref="E4:E5"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="G8:G11"/>
     <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="C16:C17"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="G10:G11"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B8:B11"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B20:B22"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="D20:D22"/>
     <mergeCell ref="G6:G7"/>
+    <mergeCell ref="D16:D17"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="D12:D13"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B10:B11"/>
     <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="G18:G19"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A8:A11"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
-    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="E20:E22"/>
     <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G16:G17"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="F14:F15"/>
-    <mergeCell ref="D10:D11"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="D8:D11"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="E12:E13"/>
-    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="E18:E19"/>
     <mergeCell ref="G12:G13"/>
+    <mergeCell ref="F20:F22"/>
     <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B16:B17"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D16:D18"/>
     <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F16:F17"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="E14:E15"/>
   </mergeCells>
@@ -2349,16 +2605,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId24"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2486,10 +2748,10 @@
           <t>开源编程智能体</t>
         </is>
       </c>
-      <c r="E4" s="49" t="n">
+      <c r="E4" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="50" t="n">
+      <c r="F4" s="51" t="n">
         <v>3965</v>
       </c>
       <c r="G4" s="8" t="n">
@@ -2520,22 +2782,22 @@
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>ponytail</t>
-        </is>
-      </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>🚀 ponytail</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2544,7 +2806,7 @@
               <color rgb="001F2937"/>
               <sz val="10"/>
             </rPr>
-            <t>208 ⭐，总星 169,611，让 AI 智能体按「最懒高级工程师」思路写代码</t>
+            <t>让 AI 智能体按「最懒高级工程师」思路写代码</t>
           </r>
           <r>
             <rPr>
@@ -2556,43 +2818,43 @@
           </r>
         </is>
       </c>
-      <c r="E5" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="52" t="n">
-        <v>1208</v>
-      </c>
-      <c r="G5" s="53" t="n">
-        <v>1208</v>
-      </c>
-      <c r="H5" s="54" t="n">
-        <v>169611</v>
-      </c>
-      <c r="I5" s="27" t="inlineStr">
-        <is>
-          <t>10-21 #5 +1,208</t>
-        </is>
-      </c>
-      <c r="J5" s="31" t="inlineStr">
+      <c r="E5" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="51" t="n">
+        <v>3287</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>2079</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>171588</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>10-21 #5 +1,208 → 10-22 #1 +2,079🚀</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>作者 DietrichGebert</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="26" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>德文名</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>🚀 ai-memory</t>
+          <t>🚀 graphify</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -2602,152 +2864,152 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>智能体工具</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>编程智能体 CLI 的长期记忆与跨厂商交接</t>
+          <t>把代码库、文档、SQL、PDF 变成可查询知识图谱</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="50" t="n">
-        <v>1178</v>
+        <v>4</v>
+      </c>
+      <c r="F6" s="51" t="n">
+        <v>2235</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>666</v>
+        <v>1433</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>11322</v>
+        <v>131608</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>10-19 #8 +512🚀 → 10-20 #5 +666</t>
+          <t>10-21 #7 +802 → 10-22 #4 +1,433🚀</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>Fabio Akita</t>
+          <t>Safi Shamsi</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>伯明翰大学；YC S26</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>印度</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>🚀 ai-memory</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>智能体工具</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>总星 12,315，给编程 CLI 智能体的长期记忆，方便在不同厂商的智能体之间交接</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="51" t="n">
+        <v>1464</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>666</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>12315</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>10-19 #8 +512🚀 → 10-20 #5 +666 → 10-22 #10 +286</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Fabio Akita</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t>🚀 headroom</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>智能体工具</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>把工具输出、日志、RAG 片段压缩后再喂给大模型，编程智能体少用约 20% token</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="50" t="n">
-        <v>859</v>
-      </c>
-      <c r="G7" s="8" t="n">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>喂给大模型前压缩工具输出和日志，省 token</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="51" t="n">
+        <v>1333</v>
+      </c>
+      <c r="G8" s="8" t="n">
         <v>549</v>
       </c>
-      <c r="H7" s="9" t="n">
-        <v>76744</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>10-20 #10 +310 → 10-21 #11 +549🚀</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="H8" s="9" t="n">
+        <v>77240</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>10-20 #10 +310 → 10-21 #11 +549🚀 → 10-22 #8 +474</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Tejas Chopra</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>昨日已核</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>graphify</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>编程智能体</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>总星 130,213，把代码库、文档、SQL、配置和 PDF 变成可查询知识图谱，供编程智能体用</t>
-        </is>
-      </c>
-      <c r="E8" s="55" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="56" t="n">
-        <v>802</v>
-      </c>
-      <c r="G8" s="57" t="n">
-        <v>802</v>
-      </c>
-      <c r="H8" s="58" t="n">
-        <v>130213</v>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>10-21 #7 +802</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="inlineStr">
-        <is>
-          <t>Safi Shamsi</t>
-        </is>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>伯明翰大学；YC S26</t>
-        </is>
-      </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>印度</t>
         </is>
       </c>
     </row>
@@ -2775,7 +3037,7 @@
       <c r="E9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F9" s="50" t="n">
+      <c r="F9" s="51" t="n">
         <v>613</v>
       </c>
       <c r="G9" s="8" t="n">
@@ -2805,113 +3067,113 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>agency-agents</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>🚀 vllm</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>推理基建</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>高吞吐 LLM 推理引擎</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="51" t="n">
+        <v>569</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>441</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>94855</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>10-21 #13 +128 → 10-22 #9 +441🚀</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>UC Berkeley 主导</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>/dev/null</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>总星 162,328，一整套「AI 外包公司」式智能体角色包，从前端到社区运营</t>
-        </is>
-      </c>
-      <c r="E10" s="55" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="56" t="n">
-        <v>562</v>
-      </c>
-      <c r="G10" s="57" t="n">
-        <v>562</v>
-      </c>
-      <c r="H10" s="58" t="n">
-        <v>162328</v>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>10-21 #10 +562</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="inlineStr">
-        <is>
-          <t>Michael/Marek Sitarzewski</t>
-        </is>
-      </c>
-      <c r="K10" s="18" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>面向开发者的社交网络，JetBrains 办公室 48 小时直播从零写出来的开源项目</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>达拉斯</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>/dev/null</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>面向开发者的社交网络，JetBrains 办公室 48 小时直播从零写出来的开源项目</t>
-        </is>
-      </c>
-      <c r="E11" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="29" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="30" t="n">
+      <c r="H11" s="33" t="n">
         <v>401</v>
       </c>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>10-20 #1</t>
         </is>
       </c>
-      <c r="J11" s="31" t="inlineStr">
+      <c r="J11" s="34" t="inlineStr">
         <is>
           <t>Nuno Maduro、Brent Roose、Matthieu Napoli、Pauline Vos 等</t>
         </is>
       </c>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t>JetBrains 直播</t>
         </is>
       </c>
-      <c r="L11" s="34" t="inlineStr">
+      <c r="L11" s="38" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -2938,7 +3200,7 @@
           <t>在一台 Mac 上跑 AI 智能体，在另一台上直接用它的窗口</t>
         </is>
       </c>
-      <c r="E12" s="59" t="n">
+      <c r="E12" s="19" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -2969,65 +3231,65 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L12" s="36" t="inlineStr">
+      <c r="L12" s="27" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>Inbox Zero</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>开源 AI 邮件助手兼客户端，对标 Superhuman</t>
         </is>
       </c>
-      <c r="E13" s="59" t="n">
+      <c r="E13" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="29" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="29" t="inlineStr">
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="30" t="n">
+      <c r="H13" s="33" t="n">
         <v>279</v>
       </c>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t>10-18 #1</t>
         </is>
       </c>
-      <c r="J13" s="31" t="inlineStr">
+      <c r="J13" s="34" t="inlineStr">
         <is>
           <t>Elie Steinbock</t>
         </is>
       </c>
-      <c r="K13" s="27" t="inlineStr">
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <t>以色列特拉维夫</t>
         </is>
       </c>
-      <c r="L13" s="34" t="inlineStr">
+      <c r="L13" s="38" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -3054,7 +3316,7 @@
           <t>给 AI 智能体接 1000+ 生产级工具，含托管鉴权与沙箱执行</t>
         </is>
       </c>
-      <c r="E14" s="60" t="n">
+      <c r="E14" s="53" t="n">
         <v>2</v>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -3092,93 +3354,93 @@
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>🚀 ai-job-search</t>
         </is>
       </c>
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C15" s="40" t="inlineStr">
         <is>
           <t>应用</t>
         </is>
       </c>
-      <c r="D15" s="39" t="inlineStr">
+      <c r="D15" s="41" t="inlineStr">
         <is>
           <t>本机运行的 AI 求职框架，基于 Claude Code 评岗位、改简历、写求职信、备面试</t>
         </is>
       </c>
-      <c r="E15" s="61" t="n">
+      <c r="E15" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="62" t="n">
+      <c r="F15" s="55" t="n">
         <v>9949</v>
       </c>
-      <c r="G15" s="63" t="n">
+      <c r="G15" s="56" t="n">
         <v>3861</v>
       </c>
-      <c r="H15" s="64" t="n">
+      <c r="H15" s="57" t="n">
         <v>60514</v>
       </c>
-      <c r="I15" s="39" t="inlineStr">
+      <c r="I15" s="41" t="inlineStr">
         <is>
           <t>10-18/19 #1 +2,232🚀 → 10-20 #1 +3,856🚀 → 10-21 #1 +3,861</t>
         </is>
       </c>
-      <c r="J15" s="43" t="inlineStr">
+      <c r="J15" s="45" t="inlineStr">
         <is>
           <t>Mads Lorentzen</t>
         </is>
       </c>
-      <c r="K15" s="39" t="inlineStr">
+      <c r="K15" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="38" t="inlineStr">
+      <c r="L15" s="40" t="inlineStr">
         <is>
           <t>丹麦</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>VoiceStudio</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D16" s="39" t="inlineStr">
+      <c r="D16" s="41" t="inlineStr">
         <is>
           <t>完全本地的开源 ElevenLabs 替代品</t>
         </is>
       </c>
-      <c r="E16" s="65" t="n">
+      <c r="E16" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="46" t="n">
+      <c r="F16" s="43" t="n">
         <v>2082</v>
       </c>
-      <c r="G16" s="66" t="n">
+      <c r="G16" s="58" t="n">
         <v>2082</v>
       </c>
-      <c r="H16" s="47" t="n">
+      <c r="H16" s="44" t="n">
         <v>75310</v>
       </c>
-      <c r="I16" s="39" t="inlineStr">
+      <c r="I16" s="41" t="inlineStr">
         <is>
           <t>10-18/19 #2 +2,082</t>
         </is>
@@ -3188,51 +3450,51 @@
           <t>未查到</t>
         </is>
       </c>
-      <c r="K16" s="39" t="inlineStr">
+      <c r="K16" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L16" s="36" t="inlineStr">
+      <c r="L16" s="27" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>ruflo</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>多智能体编排</t>
         </is>
       </c>
-      <c r="D17" s="39" t="inlineStr">
+      <c r="D17" s="41" t="inlineStr">
         <is>
           <t>多智能体蜂群编排框架</t>
         </is>
       </c>
-      <c r="E17" s="67" t="n">
+      <c r="E17" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="41" t="n">
+      <c r="F17" s="48" t="n">
         <v>1761</v>
       </c>
-      <c r="G17" s="68" t="n">
+      <c r="G17" s="59" t="n">
         <v>684</v>
       </c>
-      <c r="H17" s="42" t="n">
+      <c r="H17" s="49" t="n">
         <v>77830</v>
       </c>
-      <c r="I17" s="39" t="inlineStr">
+      <c r="I17" s="41" t="inlineStr">
         <is>
           <t>10-18/19 #7 +513 → 10-20 #7 +564 → 10-21 #9 +684</t>
         </is>
@@ -3242,12 +3504,12 @@
           <t>未查到</t>
         </is>
       </c>
-      <c r="K17" s="39" t="inlineStr">
+      <c r="K17" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L17" s="36" t="inlineStr">
+      <c r="L17" s="27" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -3295,92 +3557,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="60" t="inlineStr">
         <is>
           <t>每周开源 / 产品 Sourcing 周报（2026-10-19 – 10-25）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="70" t="inlineStr">
-        <is>
-          <t>全球项目 14 个 · 华人项目 7 个 · 核心人物 15 位</t>
+      <c r="B2" s="61" t="inlineStr">
+        <is>
+          <t>全球项目 14 个 · 华人项目 8 个 · 核心人物 19 位</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="71" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>本周总览</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="72" t="inlineStr">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="73" t="inlineStr">
-        <is>
-          <t>本周进行中 · 已更新至 10-21（第 3/7 天），每天日报后自动刷新。</t>
+      <c r="B5" s="64" t="inlineStr">
+        <is>
+          <t>本周进行中 · 已更新至 10-22（第 4/7 天），每天日报后自动刷新。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="72" t="inlineStr">
+      <c r="A6" s="63" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="73" t="inlineStr">
-        <is>
-          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search；已收录全球项目 14 个、华人项目 7 个，今日新增华人项目：Mintlify Autopilot、Asimov 1。</t>
+      <c r="B6" s="64" t="inlineStr">
+        <is>
+          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search；已收录全球项目 14 个、华人项目 8 个，今日新增华人项目：UseIt Studio。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="72" t="inlineStr">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="73" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>标「✨ 今日新增」的为今天首次上榜；灰色为前 3 周周报已出现过的项目，排在最后。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="74" t="inlineStr">
+      <c r="B9" s="65" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="75" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>黄底：日榜第 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="76" t="inlineStr">
+      <c r="B11" s="67" t="inlineStr">
         <is>
           <t>橙色：🚀 单日星增速明显放大（华人项目为 ≥ 前一天 1.5 倍）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="77" t="inlineStr">
+      <c r="B12" s="68" t="inlineStr">
         <is>
           <t>灰色斜体：未查到</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="78" t="inlineStr">
+      <c r="B14" s="69" t="inlineStr">
         <is>
           <t>网页版：https://psylch.github.io/rising-projects/2026-10-25/</t>
         </is>
@@ -3401,7 +3663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3473,34 +3735,34 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E4" s="79" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/yolandyan</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Yoland Yan（闫，全名中文未查到）</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="70" t="inlineStr">
         <is>
           <t>https://x.com/yoland_yan</t>
         </is>
@@ -3527,34 +3789,34 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E6" s="79" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>https://github.com/yoland68</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Yoland Yan（闫，全名中文未查到）</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="70" t="inlineStr">
         <is>
           <t>https://www.stackforce.co/talent/6a4f76052978e57b300365dc</t>
         </is>
@@ -3581,34 +3843,34 @@
           <t>来源4</t>
         </is>
       </c>
-      <c r="E8" s="79" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>https://research.crustdata.com/company/comfyui</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Robin Huang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="70" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/robinjhuang</t>
         </is>
@@ -3635,34 +3897,34 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E10" s="79" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>https://x.com/robinjhuang</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Robin Huang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="70" t="inlineStr">
         <is>
           <t>https://github.com/robinjhuang</t>
         </is>
@@ -3689,34 +3951,34 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E12" s="79" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>https://www.getprog.ai/profile/5674242</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Robin Huang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" s="70" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/posts/concordia-international-school-shanghai_comfy-jobs-activity-7498183966257078272-p3K4</t>
         </is>
@@ -3743,34 +4005,34 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E14" s="79" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>https://github.com/shiyu-coder</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>shiyu-coder/Kronos</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Yu Shi（中文名未查到）</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E15" s="35" t="inlineStr">
+      <c r="E15" s="70" t="inlineStr">
         <is>
           <t>https://arxiv.org/html/2508.02739</t>
         </is>
@@ -3797,372 +4059,372 @@
           <t>来源1</t>
         </is>
       </c>
-      <c r="E16" s="79" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>https://arxiv.org/html/2508.02739</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" s="70" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/daniel-gao-342504253</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?hl=en&amp;user=No9OsocAAAAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D19" s="30" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E19" s="70" t="inlineStr">
+        <is>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>https://www.alphaxiv.org/@difei-gao</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E21" s="70" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2024/html/Gao_AssistGUI_Task-Oriented_PC_Graphical_User_Interface_Automation_CVPR_2024_paper.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>陈芷恒（Lindia Chen）</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>producthunt</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/@lindiac</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>陈芷恒（Lindia Chen）</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D23" s="30" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E23" s="70" t="inlineStr">
+        <is>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>陈芷恒（Lindia Chen）</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/useit-studio-from-idea-to-delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>丁云培</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E25" s="70" t="inlineStr">
+        <is>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>刘佳琦</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>Wally by Willow</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Allan Guo</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E17" s="35" t="inlineStr">
+      <c r="E27" s="70" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/allan-guo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>Wally by Willow</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>Allan Guo</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E18" s="79" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/companies/willow</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>Wally by Willow</t>
-        </is>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>Allan Guo</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E19" s="35" t="inlineStr">
-        <is>
-          <t>https://profiles.stanford.edu/allan-guo</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>Wally by Willow</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>Lawrence Liu</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E20" s="79" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/lawrenceliuu</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>Wally by Willow</t>
-        </is>
-      </c>
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>Lawrence Liu</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D21" s="27" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E21" s="35" t="inlineStr">
-        <is>
-          <t>https://www.stackforce.co/talent/lawrence-liu-ceo-69d744662a55b09f46c5deaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>Mintlify Autopilot</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>Han Wang（王，生于河南新乡）</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E22" s="79" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/handotdev</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>Mintlify Autopilot</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>Han Wang（王，生于河南新乡）</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D23" s="27" t="inlineStr">
-        <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="inlineStr">
-        <is>
-          <t>https://han.dev/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>Mintlify Autopilot</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>Han Wang（王，生于河南新乡）</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E24" s="79" t="inlineStr">
-        <is>
-          <t>https://x.com/handotdev</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>Mintlify Autopilot</t>
-        </is>
-      </c>
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>Han Wang（王，生于河南新乡）</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D25" s="27" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E25" s="35" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>Mintlify Autopilot</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>Han Wang（王，生于河南新乡）</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E26" s="79" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/handotdev_my-grandparents-in-rural-china-use-ai-more-activity-7430270997586489346-XzLv</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>Mintlify Autopilot</t>
-        </is>
-      </c>
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>Hahnbee Lee</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D27" s="27" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E27" s="35" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>Asimov 1</t>
+          <t>Wally by Willow</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Daniel Ong</t>
+          <t>Allan Guo</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E28" s="79" t="inlineStr">
-        <is>
-          <t>https://daniel.ai/</t>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/willow</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
-        <is>
-          <t>Asimov 1</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="inlineStr">
-        <is>
-          <t>Daniel Ong</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E29" s="35" t="inlineStr">
-        <is>
-          <t>https://github.com/dan-menlo</t>
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>Wally by Willow</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Allan Guo</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E29" s="70" t="inlineStr">
+        <is>
+          <t>https://profiles.stanford.edu/allan-guo</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>Asimov 1</t>
+          <t>Wally by Willow</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>Nicole Zhu</t>
+          <t>Lawrence Liu</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
@@ -4175,102 +4437,102 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E30" s="79" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/nicolezhu</t>
+      <c r="E30" s="25" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/lawrenceliuu</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="31" t="inlineStr">
-        <is>
-          <t>Asimov 1</t>
-        </is>
-      </c>
-      <c r="B31" s="27" t="inlineStr">
-        <is>
-          <t>Nicole Zhu</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>Wally by Willow</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Lawrence Liu</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E31" s="70" t="inlineStr">
+        <is>
+          <t>https://www.stackforce.co/talent/lawrence-liu-ceo-69d744662a55b09f46c5deaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/handotdev</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="34" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D31" s="27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E31" s="35" t="inlineStr">
-        <is>
-          <t>https://x.com/freelerobot</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>Asimov 1</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>Nicole Zhu</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E32" s="79" t="inlineStr">
-        <is>
-          <t>https://nicole.ai/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="inlineStr">
-        <is>
-          <t>Jinjing Liang（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="27" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E33" s="35" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/jinjingliang</t>
+      <c r="E33" s="70" t="inlineStr">
+        <is>
+          <t>https://han.dev/</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>Mintlify Autopilot</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Jinjing Liang（中文名未查到）</t>
+          <t>Han Wang（王，生于河南新乡）</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
@@ -4283,48 +4545,48 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E34" s="79" t="inlineStr">
-        <is>
-          <t>https://x.com/JinjingLiang</t>
+      <c r="E34" s="25" t="inlineStr">
+        <is>
+          <t>https://x.com/handotdev</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="31" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B35" s="27" t="inlineStr">
-        <is>
-          <t>Jinjing Liang（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D35" s="27" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E35" s="35" t="inlineStr">
-        <is>
-          <t>https://github.com/AmethystLiang</t>
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E35" s="70" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>Mintlify Autopilot</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Jinjing Liang（中文名未查到）</t>
+          <t>Han Wang（王，生于河南新乡）</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
@@ -4334,51 +4596,51 @@
       </c>
       <c r="D36" s="18" t="inlineStr">
         <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/handotdev_my-grandparents-in-rural-china-use-ai-more-activity-7430270997586489346-XzLv</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="34" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>Hahnbee Lee</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D37" s="30" t="inlineStr">
+        <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E36" s="79" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="31" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="inlineStr">
-        <is>
-          <t>Neil Parker</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D37" s="27" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E37" s="35" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/neilwilliamparker</t>
+      <c r="E37" s="70" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>Asimov 1</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Neil Parker</t>
+          <t>Daniel Ong</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
@@ -4388,105 +4650,105 @@
       </c>
       <c r="D38" s="18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E38" s="79" t="inlineStr">
-        <is>
-          <t>https://x.com/nwparker_</t>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="inlineStr">
+        <is>
+          <t>https://daniel.ai/</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B39" s="27" t="inlineStr">
-        <is>
-          <t>Neil Parker</t>
-        </is>
-      </c>
-      <c r="C39" s="26" t="inlineStr">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>Daniel Ong</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D39" s="27" t="inlineStr">
+      <c r="D39" s="30" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E39" s="35" t="inlineStr">
-        <is>
-          <t>https://github.com/nwparker</t>
+      <c r="E39" s="70" t="inlineStr">
+        <is>
+          <t>https://github.com/dan-menlo</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>Asimov 1</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Neil Parker</t>
+          <t>Nicole Zhu</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
         <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E40" s="79" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/nicolezhu</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="31" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B41" s="27" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
+      <c r="A41" s="34" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>Nicole Zhu</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D41" s="27" t="inlineStr">
-        <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E41" s="35" t="inlineStr">
-        <is>
-          <t>https://sites.google.com/view/chaoh</t>
+      <c r="D41" s="30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E41" s="70" t="inlineStr">
+        <is>
+          <t>https://x.com/freelerobot</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>HKUDS/CLI-Anything</t>
+          <t>Asimov 1</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Huang Chao（黄超）</t>
+          <t>Nicole Zhu</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
@@ -4496,233 +4758,503 @@
       </c>
       <c r="D42" s="18" t="inlineStr">
         <is>
-          <t>GitHub 组织</t>
-        </is>
-      </c>
-      <c r="E42" s="79" t="inlineStr">
-        <is>
-          <t>https://github.com/HKUDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="31" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D43" s="27" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E43" s="35" t="inlineStr">
-        <is>
-          <t>https://datascience.hku.hk/people/chao-huang/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E42" s="25" t="inlineStr">
+        <is>
+          <t>https://nicole.ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="34" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D43" s="30" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E43" s="70" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/jinjingliang</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>HKUDS/CLI-Anything</t>
+          <t>stablyai/orca</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Huang Chao（黄超）</t>
+          <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>其他联系</t>
         </is>
       </c>
       <c r="D44" s="18" t="inlineStr">
         <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E44" s="79" t="inlineStr">
-        <is>
-          <t>https://www.ai.hku.hk/people/academic-staff/chuang</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="31" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B45" s="27" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D45" s="27" t="inlineStr">
-        <is>
-          <t>来源4</t>
-        </is>
-      </c>
-      <c r="E45" s="35" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2606.03854</t>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E44" s="25" t="inlineStr">
+        <is>
+          <t>https://x.com/JinjingLiang</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D45" s="30" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E45" s="70" t="inlineStr">
+        <is>
+          <t>https://github.com/AmethystLiang</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="22" t="inlineStr">
         <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B47" s="30" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D47" s="30" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E47" s="70" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/neilwilliamparker</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E48" s="25" t="inlineStr">
+        <is>
+          <t>https://x.com/nwparker_</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C49" s="29" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D49" s="30" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E49" s="70" t="inlineStr">
+        <is>
+          <t>https://github.com/nwparker</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E50" s="25" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B46" s="18" t="inlineStr">
+      <c r="B51" s="30" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D51" s="30" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E51" s="70" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/chaoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>GitHub 组织</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="inlineStr">
+        <is>
+          <t>https://github.com/HKUDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="34" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B53" s="30" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C53" s="29" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D53" s="30" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E53" s="70" t="inlineStr">
+        <is>
+          <t>https://datascience.hku.hk/people/chao-huang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E54" s="25" t="inlineStr">
+        <is>
+          <t>https://www.ai.hku.hk/people/academic-staff/chuang</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="34" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B55" s="30" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C55" s="29" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D55" s="30" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E55" s="70" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.03854</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D46" s="18" t="inlineStr">
+      <c r="D56" s="18" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E46" s="79" t="inlineStr">
+      <c r="E56" s="25" t="inlineStr">
         <is>
           <t>https://yuh-yang.github.io</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="31" t="inlineStr">
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="34" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B47" s="27" t="inlineStr">
+      <c r="B57" s="30" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="C57" s="29" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D47" s="27" t="inlineStr">
+      <c r="D57" s="30" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E47" s="35" t="inlineStr">
+      <c r="E57" s="70" t="inlineStr">
         <is>
           <t>https://github.com/yuh-yang</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="22" t="inlineStr">
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B48" s="18" t="inlineStr">
+      <c r="B58" s="18" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C58" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D48" s="18" t="inlineStr">
+      <c r="D58" s="18" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E48" s="79" t="inlineStr">
+      <c r="E58" s="25" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="31" t="inlineStr">
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="34" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B49" s="27" t="inlineStr">
+      <c r="B59" s="30" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="C49" s="26" t="inlineStr">
+      <c r="C59" s="29" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D49" s="27" t="inlineStr">
+      <c r="D59" s="30" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E49" s="35" t="inlineStr">
+      <c r="E59" s="70" t="inlineStr">
         <is>
           <t>https://tianyufan0504.github.io/</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="22" t="inlineStr">
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B60" s="18" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D50" s="18" t="inlineStr">
+      <c r="D60" s="18" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E50" s="79" t="inlineStr">
+      <c r="E60" s="25" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E50"/>
+  <autoFilter ref="A3:E60"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -4775,6 +5307,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId57"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/2026-10-25/weekly-2026-10-25.xlsx
+++ b/2026-10-25/weekly-2026-10-25.xlsx
@@ -13,15 +13,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'华人项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全球项目'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'链接'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,8 +33,8 @@
     <numFmt numFmtId="164" formatCode="&quot;#&quot;0"/>
     <numFmt numFmtId="165" formatCode="+#,##0&quot; 🚀&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot; ★&quot;"/>
-    <numFmt numFmtId="167" formatCode="&quot;PH #&quot;0"/>
-    <numFmt numFmtId="168" formatCode="+#,##0"/>
+    <numFmt numFmtId="167" formatCode="+#,##0"/>
+    <numFmt numFmtId="168" formatCode="&quot;PH #&quot;0"/>
     <numFmt numFmtId="169" formatCode="#,##0&quot; 票&quot;"/>
   </numFmts>
   <fonts count="16">
@@ -157,12 +157,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE68A"/>
+        <fgColor rgb="00F5F7FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F7FA"/>
+        <fgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -279,64 +279,76 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -346,58 +358,76 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -410,13 +440,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -782,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1284,15 +1311,315 @@
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
+          <t>PCL</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Minecraft 启动器 Plain Craft Launcher（PCL）</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>119</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>8682</v>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>10-23 #8 +119</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>主要作者</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>Meloong（瓜皮龙工作室）开发 PCL/PCL2</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>admin@meloong.com</t>
+        </is>
+      </c>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O8" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P8" s="18" t="inlineStr">
+        <is>
+          <t>bilibili
+afdian
+个人站</t>
+        </is>
+      </c>
+      <c r="Q8" s="18" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>DeepCell</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>办公室截止日期联动工作包</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：.deepcell 格式串联表格/文档/幻灯片与 cheat sheet，一处改数全局更新</t>
+          </r>
+        </is>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>265</v>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>10-22 #1</t>
+        </is>
+      </c>
+      <c r="H9" s="31" t="inlineStr">
+        <is>
+          <t>梦琪（Mengqi）</t>
+        </is>
+      </c>
+      <c r="I9" s="27" t="inlineStr">
+        <is>
+          <t>联合创始人 / 主要搭建者</t>
+        </is>
+      </c>
+      <c r="J9" s="27" t="inlineStr">
+        <is>
+          <t>中欧 MBA 2024</t>
+        </is>
+      </c>
+      <c r="K9" s="27" t="inlineStr">
+        <is>
+          <t>非 CS 科班；用 AI coding 从 0 写产品前后端；约 10 年企业职场</t>
+        </is>
+      </c>
+      <c r="L9" s="27" t="inlineStr">
+        <is>
+          <t>上海（公司总部）</t>
+        </is>
+      </c>
+      <c r="M9" s="27" t="inlineStr">
+        <is>
+          <t>hello@deepcell.net</t>
+        </is>
+      </c>
+      <c r="N9" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O9" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P9" s="34" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="Q9" s="27" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3、来源4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="I10" s="27" t="inlineStr">
+        <is>
+          <t>产品联合创始人</t>
+        </is>
+      </c>
+      <c r="J10" s="27" t="inlineStr">
+        <is>
+          <t>中欧 MBA 2024</t>
+        </is>
+      </c>
+      <c r="K10" s="27" t="inlineStr">
+        <is>
+          <t>前 PwC 约四年，估值建模与投资备忘录</t>
+        </is>
+      </c>
+      <c r="L10" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M10" s="27" t="inlineStr">
+        <is>
+          <t>hello@deepcell.net</t>
+        </is>
+      </c>
+      <c r="N10" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O10" s="36" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P10" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" s="27" t="inlineStr">
+        <is>
+          <t>来源1、来源2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>Amy Wang</t>
+        </is>
+      </c>
+      <c r="I11" s="27" t="inlineStr">
+        <is>
+          <t>联合创始人</t>
+        </is>
+      </c>
+      <c r="J11" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K11" s="27" t="inlineStr">
+        <is>
+          <t>软件工程师背景；DeepCell 联合创始人</t>
+        </is>
+      </c>
+      <c r="L11" s="27" t="inlineStr">
+        <is>
+          <t>上海 / 胡志明市（LinkedIn 任职地不一）</t>
+        </is>
+      </c>
+      <c r="M11" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N11" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O11" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P11" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q11" s="27" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
           <t>UseIt Studio</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1313,299 +1640,299 @@
           </r>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D12" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F12" s="38" t="n">
         <v>264</v>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>10-21 #1</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>郜迪飞（Difei Gao / Daniel Gao）</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>创始人兼 CEO</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>中科院计算所博士；NUS 博士后</t>
         </is>
       </c>
-      <c r="K8" s="18" t="inlineStr">
+      <c r="K12" s="18" t="inlineStr">
         <is>
           <t>NUS Show Lab 高级研究员；AssistGUI、AssistGPT、ShowUI 作者；2025-07 起创办 UseIt AI</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
+      <c r="L12" s="18" t="inlineStr">
         <is>
           <t>新加坡</t>
         </is>
       </c>
-      <c r="M8" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N8" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="M12" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O12" s="39" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P8" s="25" t="inlineStr">
+      <c r="P12" s="40" t="inlineStr">
         <is>
           <t>Google Scholar</t>
         </is>
       </c>
-      <c r="Q8" s="18" t="inlineStr">
+      <c r="Q12" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="26" t="n"/>
-      <c r="B9" s="26" t="n"/>
-      <c r="C9" s="26" t="n"/>
-      <c r="D9" s="26" t="n"/>
-      <c r="E9" s="26" t="n"/>
-      <c r="F9" s="26" t="n"/>
-      <c r="G9" s="26" t="n"/>
-      <c r="H9" s="22" t="inlineStr">
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n"/>
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>陈芷恒（Lindia Chen）</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>联合创始人兼增长负责人</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>新加坡国立大学硕士</t>
         </is>
       </c>
-      <c r="K9" s="18" t="inlineStr">
+      <c r="K13" s="18" t="inlineStr">
         <is>
           <t>曾在学而思做策划；上海中学校友</t>
         </is>
       </c>
-      <c r="L9" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M9" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N9" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O9" s="27" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P9" s="25" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O13" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P13" s="40" t="inlineStr">
         <is>
           <t>producthunt</t>
         </is>
       </c>
-      <c r="Q9" s="18" t="inlineStr">
+      <c r="Q13" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="26" t="n"/>
-      <c r="B10" s="26" t="n"/>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="26" t="n"/>
-      <c r="G10" s="26" t="n"/>
-      <c r="H10" s="22" t="inlineStr">
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>丁云培</t>
         </is>
       </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>联合创始人兼产品负责人</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>UCL 计算机视觉硕士</t>
         </is>
       </c>
-      <c r="K10" s="18" t="inlineStr">
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t>连续创业者</t>
         </is>
       </c>
-      <c r="L10" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N10" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O10" s="27" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M14" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O14" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q14" s="40" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="13" t="n"/>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="22" t="inlineStr">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>刘佳琦</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>联合创始人兼技术负责人</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J15" s="18" t="inlineStr">
         <is>
           <t>北京工业大学人工智能博士</t>
         </is>
       </c>
-      <c r="K11" s="18" t="inlineStr">
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>连续创业者；前 AIGC 创作分享平台技术负责人</t>
         </is>
       </c>
-      <c r="L11" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M11" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N11" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O11" s="27" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P11" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="Q11" s="25" t="inlineStr">
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M15" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N15" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O15" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q15" s="40" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Wally by Willow</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>语音</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>Mac AI 语音输入工具 Willow 的新功能 Wally，学习用户写作风格；YC 公司，2025 年成立，团队 7 人，总部旧金山
 团队：按姓名与背景判断为华人，本人族裔表述未查到</t>
         </is>
       </c>
-      <c r="D12" s="31" t="n">
+      <c r="D16" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F16" s="30" t="n">
         <v>123</v>
       </c>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>10-19 #7</t>
         </is>
       </c>
-      <c r="H12" s="34" t="inlineStr">
+      <c r="H16" s="31" t="inlineStr">
         <is>
           <t>Allan Guo</t>
         </is>
       </c>
-      <c r="I12" s="30" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO</t>
         </is>
       </c>
-      <c r="J12" s="30" t="inlineStr">
+      <c r="J16" s="27" t="inlineStr">
         <is>
           <t>斯坦福计算机系（2023–2024，离校创业）；University of Toronto Schools</t>
         </is>
       </c>
-      <c r="K12" s="30" t="inlineStr">
+      <c r="K16" s="27" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1626,61 +1953,61 @@
           </r>
         </is>
       </c>
-      <c r="L12" s="30" t="inlineStr">
+      <c r="L16" s="27" t="inlineStr">
         <is>
           <t>旧金山</t>
         </is>
       </c>
-      <c r="M12" s="30" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t>allanguo@stanford.edu</t>
         </is>
       </c>
-      <c r="N12" s="35" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O12" s="36" t="inlineStr">
+      <c r="N16" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O16" s="33" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P12" s="30" t="inlineStr">
+      <c r="P16" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q12" s="30" t="inlineStr">
+      <c r="Q16" s="27" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1">
-      <c r="A13" s="13" t="n"/>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="34" t="inlineStr">
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="31" t="inlineStr">
         <is>
           <t>Lawrence Liu</t>
         </is>
       </c>
-      <c r="I13" s="30" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>联合创始人兼 CTO</t>
         </is>
       </c>
-      <c r="J13" s="30" t="inlineStr">
+      <c r="J17" s="27" t="inlineStr">
         <is>
           <t>斯坦福计算机学士；就读过卡内基梅隆；Fox Chapel Area High School</t>
         </is>
       </c>
-      <c r="K13" s="30" t="inlineStr">
+      <c r="K17" s="27" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1709,85 +2036,85 @@
           </r>
         </is>
       </c>
-      <c r="L13" s="30" t="inlineStr">
+      <c r="L17" s="27" t="inlineStr">
         <is>
           <t>LinkedIn 写匹兹堡；公司在旧金山</t>
         </is>
       </c>
-      <c r="M13" s="35" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N13" s="35" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O13" s="36" t="inlineStr">
+      <c r="M17" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N17" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O17" s="33" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P13" s="30" t="inlineStr">
+      <c r="P17" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q13" s="30" t="inlineStr">
+      <c r="Q17" s="27" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Mintlify Autopilot</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Mintlify 常驻文档智能体，自动随代码更新文档；YC 公司</t>
         </is>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D18" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E18" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F18" s="38" t="n">
         <v>122</v>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>10-20 #6</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>Han Wang（王，生于河南新乡）</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J18" s="18" t="inlineStr">
         <is>
           <t>康奈尔大学信息科学学士</t>
         </is>
       </c>
-      <c r="K14" s="18" t="inlineStr">
+      <c r="K18" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1808,206 +2135,289 @@
           </r>
         </is>
       </c>
-      <c r="L14" s="18" t="inlineStr">
+      <c r="L18" s="18" t="inlineStr">
         <is>
           <t>旧金山</t>
         </is>
       </c>
-      <c r="M14" s="18" t="inlineStr">
+      <c r="M18" s="18" t="inlineStr">
         <is>
           <t>han@mintlify.com</t>
         </is>
       </c>
-      <c r="N14" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O14" s="24" t="inlineStr">
+      <c r="N18" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O18" s="39" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P14" s="18" t="inlineStr">
+      <c r="P18" s="18" t="inlineStr">
         <is>
           <t>个人站
 X</t>
         </is>
       </c>
-      <c r="Q14" s="18" t="inlineStr">
+      <c r="Q18" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="22" t="inlineStr">
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>Hahnbee Lee</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>联合创始人</t>
         </is>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J19" s="18" t="inlineStr">
         <is>
           <t>康奈尔大学计算机本科</t>
         </is>
       </c>
-      <c r="K15" s="18" t="inlineStr">
+      <c r="K19" s="18" t="inlineStr">
         <is>
           <t>与 Han 共同创办 Mintlify；早年参与 People</t>
         </is>
       </c>
-      <c r="L15" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M15" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N15" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O15" s="27" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="Q15" s="25" t="inlineStr">
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M19" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N19" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O19" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P19" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q19" s="40" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
+    <row r="20" ht="50" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>CutBay</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>聊天式 AI 视频智能体，由 PearlMountain（FlexClip 团队）出品</t>
+        </is>
+      </c>
+      <c r="D20" s="41" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>117</v>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>10-22 #9</t>
+        </is>
+      </c>
+      <c r="H20" s="31" t="inlineStr">
+        <is>
+          <t>林霄（David Lin / Lin Xiao）</t>
+        </is>
+      </c>
+      <c r="I20" s="27" t="inlineStr">
+        <is>
+          <t>PearlMountain 创始人兼 CEO</t>
+        </is>
+      </c>
+      <c r="J20" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>PearlMountain Limited 创始人；FlexClip 创始人兼 CEO</t>
+        </is>
+      </c>
+      <c r="L20" s="27" t="inlineStr">
+        <is>
+          <t>香港（公司）</t>
+        </is>
+      </c>
+      <c r="M20" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N20" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O20" s="36" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P20" s="34" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="Q20" s="27" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="50" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Asimov 1</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>Menlo Research 的可定制人形机器人；新加坡开放 AI/机器人实验室
 团队：新加坡华人背景（籍贯/姓氏）；Daniel 公开写在新加坡长大</t>
         </is>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D21" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="E16" s="32" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="33" t="n">
+      <c r="F21" s="38" t="n">
         <v>110</v>
       </c>
-      <c r="G16" s="30" t="inlineStr">
+      <c r="G21" s="18" t="inlineStr">
         <is>
           <t>10-20 #8</t>
         </is>
       </c>
-      <c r="H16" s="34" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>Daniel Ong</t>
         </is>
       </c>
-      <c r="I16" s="30" t="inlineStr">
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>联合创始人</t>
         </is>
       </c>
-      <c r="J16" s="30" t="inlineStr">
+      <c r="J21" s="18" t="inlineStr">
         <is>
           <t>斯坦福大学（转读计算机）</t>
         </is>
       </c>
-      <c r="K16" s="30" t="inlineStr">
+      <c r="K21" s="18" t="inlineStr">
         <is>
           <t>新加坡警察 5 年；早期以太坊相关创业；与 Nicole 创办 Menlo Research</t>
         </is>
       </c>
-      <c r="L16" s="30" t="inlineStr">
+      <c r="L21" s="18" t="inlineStr">
         <is>
           <t>新加坡</t>
         </is>
       </c>
-      <c r="M16" s="30" t="inlineStr">
+      <c r="M21" s="18" t="inlineStr">
         <is>
           <t>dan@daniel.ai</t>
         </is>
       </c>
-      <c r="N16" s="35" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O16" s="38" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P16" s="30" t="inlineStr">
+      <c r="N21" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O21" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P21" s="18" t="inlineStr">
         <is>
           <t>个人站
 GitHub</t>
         </is>
       </c>
-      <c r="Q16" s="30" t="inlineStr">
+      <c r="Q21" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="13" t="n"/>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="34" t="inlineStr">
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>Nicole Zhu</t>
         </is>
       </c>
-      <c r="I17" s="30" t="inlineStr">
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>联合创始人</t>
         </is>
       </c>
-      <c r="J17" s="30" t="inlineStr">
+      <c r="J22" s="18" t="inlineStr">
         <is>
           <t>斯坦福机械工程学士、计算机硕士</t>
         </is>
       </c>
-      <c r="K17" s="30" t="inlineStr">
+      <c r="K22" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2036,50 +2446,50 @@
           </r>
         </is>
       </c>
-      <c r="L17" s="30" t="inlineStr">
+      <c r="L22" s="18" t="inlineStr">
         <is>
           <t>新加坡</t>
         </is>
       </c>
-      <c r="M17" s="35" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N17" s="35" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O17" s="36" t="inlineStr">
+      <c r="M22" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N22" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O22" s="39" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P17" s="30" t="inlineStr">
+      <c r="P22" s="18" t="inlineStr">
         <is>
           <t>X
 个人站</t>
         </is>
       </c>
-      <c r="Q17" s="30" t="inlineStr">
+      <c r="Q22" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="64" customHeight="1">
-      <c r="A18" s="39" t="inlineStr">
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="43" t="inlineStr">
         <is>
           <t>orca</t>
         </is>
       </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="B23" s="44" t="inlineStr">
         <is>
           <t>编程智能体</t>
         </is>
       </c>
-      <c r="C18" s="41" t="inlineStr">
+      <c r="C23" s="45" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2100,36 +2510,36 @@
           </r>
         </is>
       </c>
-      <c r="D18" s="42" t="n">
+      <c r="D23" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="43" t="n">
+      <c r="E23" s="47" t="n">
         <v>5842</v>
       </c>
-      <c r="F18" s="44" t="n">
+      <c r="F23" s="48" t="n">
         <v>101219</v>
       </c>
-      <c r="G18" s="41" t="inlineStr">
+      <c r="G23" s="45" t="inlineStr">
         <is>
           <t>10-18/19 #5 +1,146 → 10-20 #2 +1,590 → 10-21 #3 +1,565 → 10-22 #3 +1,541</t>
         </is>
       </c>
-      <c r="H18" s="45" t="inlineStr">
+      <c r="H23" s="49" t="inlineStr">
         <is>
           <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
-      <c r="I18" s="41" t="inlineStr">
+      <c r="I23" s="45" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO，Orca 维护者</t>
         </is>
       </c>
-      <c r="J18" s="41" t="inlineStr">
+      <c r="J23" s="45" t="inlineStr">
         <is>
           <t>康奈尔大学校友（专业与学位未查到）</t>
         </is>
       </c>
-      <c r="K18" s="41" t="inlineStr">
+      <c r="K23" s="45" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2158,62 +2568,62 @@
           </r>
         </is>
       </c>
-      <c r="L18" s="41" t="inlineStr">
+      <c r="L23" s="45" t="inlineStr">
         <is>
           <t>美国旧金山湾区</t>
         </is>
       </c>
-      <c r="M18" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N18" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O18" s="46" t="inlineStr">
+      <c r="M23" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N23" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O23" s="50" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P18" s="41" t="inlineStr">
+      <c r="P23" s="45" t="inlineStr">
         <is>
           <t>X
 GitHub</t>
         </is>
       </c>
-      <c r="Q18" s="41" t="inlineStr">
+      <c r="Q23" s="45" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="13" t="n"/>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="45" t="inlineStr">
+    <row r="24" ht="50" customHeight="1">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="49" t="inlineStr">
         <is>
           <t>Neil Parker</t>
         </is>
       </c>
-      <c r="I19" s="41" t="inlineStr">
+      <c r="I24" s="45" t="inlineStr">
         <is>
           <t>联合创始人兼 CTO（非华人，列作团队参考）</t>
         </is>
       </c>
-      <c r="J19" s="41" t="inlineStr">
+      <c r="J24" s="45" t="inlineStr">
         <is>
           <t>康奈尔大学校友</t>
         </is>
       </c>
-      <c r="K19" s="41" t="inlineStr">
+      <c r="K24" s="45" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2242,50 +2652,50 @@
           </r>
         </is>
       </c>
-      <c r="L19" s="41" t="inlineStr">
+      <c r="L24" s="45" t="inlineStr">
         <is>
           <t>美国旧金山湾区</t>
         </is>
       </c>
-      <c r="M19" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N19" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O19" s="46" t="inlineStr">
+      <c r="M24" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N24" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O24" s="50" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P19" s="41" t="inlineStr">
+      <c r="P24" s="45" t="inlineStr">
         <is>
           <t>X
 GitHub</t>
         </is>
       </c>
-      <c r="Q19" s="41" t="inlineStr">
+      <c r="Q24" s="45" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="64" customHeight="1">
-      <c r="A20" s="39" t="inlineStr">
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="43" t="inlineStr">
         <is>
           <t>CLI-Anything</t>
         </is>
       </c>
-      <c r="B20" s="40" t="inlineStr">
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t>智能体工具</t>
         </is>
       </c>
-      <c r="C20" s="41" t="inlineStr">
+      <c r="C25" s="45" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2306,36 +2716,36 @@
           </r>
         </is>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D25" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="48" t="n">
+      <c r="E25" s="52" t="n">
         <v>1195</v>
       </c>
-      <c r="F20" s="49" t="n">
+      <c r="F25" s="53" t="n">
         <v>55221</v>
       </c>
-      <c r="G20" s="41" t="inlineStr">
+      <c r="G25" s="45" t="inlineStr">
         <is>
           <t>10-18/19 #6 +589 → 10-20 #6 +606</t>
         </is>
       </c>
-      <c r="H20" s="45" t="inlineStr">
+      <c r="H25" s="49" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="I20" s="41" t="inlineStr">
+      <c r="I25" s="45" t="inlineStr">
         <is>
           <t>通讯作者、HKUDS / Data Intelligence Lab 负责人</t>
         </is>
       </c>
-      <c r="J20" s="41" t="inlineStr">
+      <c r="J25" s="45" t="inlineStr">
         <is>
           <t>University of Notre Dame 计算机博士；现港大计算机系助理教授</t>
         </is>
       </c>
-      <c r="K20" s="41" t="inlineStr">
+      <c r="K25" s="45" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2356,124 +2766,124 @@
           </r>
         </is>
       </c>
-      <c r="L20" s="41" t="inlineStr">
+      <c r="L25" s="45" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M20" s="41" t="inlineStr">
+      <c r="M25" s="45" t="inlineStr">
         <is>
           <t>chuang@cs.hku.hk
 chaohuang75@gmail.com</t>
         </is>
       </c>
-      <c r="N20" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O20" s="27" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P20" s="41" t="inlineStr">
+      <c r="N25" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O25" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P25" s="45" t="inlineStr">
         <is>
           <t>个人站
 GitHub 组织</t>
         </is>
       </c>
-      <c r="Q20" s="41" t="inlineStr">
+      <c r="Q25" s="45" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="64" customHeight="1">
-      <c r="A21" s="26" t="n"/>
-      <c r="B21" s="26" t="n"/>
-      <c r="C21" s="26" t="n"/>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="26" t="n"/>
-      <c r="G21" s="26" t="n"/>
-      <c r="H21" s="45" t="inlineStr">
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="35" t="n"/>
+      <c r="B26" s="35" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="49" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="I21" s="41" t="inlineStr">
+      <c r="I26" s="45" t="inlineStr">
         <is>
           <t>一作</t>
         </is>
       </c>
-      <c r="J21" s="41" t="inlineStr">
+      <c r="J26" s="45" t="inlineStr">
         <is>
           <t>香港大学博士（论文获 2026 ACM SIGKDD Dissertation Award Runner-Up）</t>
         </is>
       </c>
-      <c r="K21" s="41" t="inlineStr">
+      <c r="K26" s="45" t="inlineStr">
         <is>
           <t>主导 CLI-Anything；此前 UltraCUA、Aria-UI 等 computer-use 工作</t>
         </is>
       </c>
-      <c r="L21" s="41" t="inlineStr">
+      <c r="L26" s="45" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M21" s="41" t="inlineStr">
+      <c r="M26" s="45" t="inlineStr">
         <is>
           <t>itsyuhaoy@gmail.com
 yuhao-yang@outlook.com</t>
         </is>
       </c>
-      <c r="N21" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O21" s="27" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P21" s="41" t="inlineStr">
+      <c r="N26" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O26" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P26" s="45" t="inlineStr">
         <is>
           <t>个人站
 GitHub</t>
         </is>
       </c>
-      <c r="Q21" s="41" t="inlineStr">
+      <c r="Q26" s="45" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="64" customHeight="1">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="45" t="inlineStr">
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="49" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="I22" s="41" t="inlineStr">
+      <c r="I27" s="45" t="inlineStr">
         <is>
           <t>共同作者</t>
         </is>
       </c>
-      <c r="J22" s="41" t="inlineStr">
+      <c r="J27" s="45" t="inlineStr">
         <is>
           <t>浙江大学自动化本科（2020–2024）；香港大学计算机博士在读（2024–）</t>
         </is>
       </c>
-      <c r="K22" s="41" t="inlineStr">
+      <c r="K27" s="45" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2502,99 +2912,106 @@
           </r>
         </is>
       </c>
-      <c r="L22" s="41" t="inlineStr">
+      <c r="L27" s="45" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M22" s="41" t="inlineStr">
+      <c r="M27" s="45" t="inlineStr">
         <is>
           <t>tianyufan0504@gmail.com</t>
         </is>
       </c>
-      <c r="N22" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O22" s="27" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P22" s="41" t="inlineStr">
+      <c r="N27" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O27" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P27" s="45" t="inlineStr">
         <is>
           <t>个人站
 未在个人站显著标注主账号</t>
         </is>
       </c>
-      <c r="Q22" s="41" t="inlineStr">
+      <c r="Q27" s="45" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q22"/>
-  <mergeCells count="58">
+  <autoFilter ref="A3:Q27"/>
+  <mergeCells count="65">
+    <mergeCell ref="G23:G24"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E23:E24"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F6:F7"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D9:D11"/>
     <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="G25:G27"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="C21:C22"/>
     <mergeCell ref="G6:G7"/>
+    <mergeCell ref="C12:C15"/>
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="E6:E7"/>
-    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="F23:F24"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="C23:C24"/>
     <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A8:A11"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="D12:D15"/>
     <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A23:A24"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="E16:E17"/>
     <mergeCell ref="G16:G17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F14:F15"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="C25:C27"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E12:E13"/>
     <mergeCell ref="E18:E19"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="G12:G15"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="F16:F17"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="E9:E11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -2604,23 +3021,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId31"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2730,7 +3154,7 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>🚀 opencode</t>
+          <t>🚀 ponytail</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2740,64 +3164,10 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>编程智能体</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>开源编程智能体</t>
-        </is>
-      </c>
-      <c r="E4" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="51" t="n">
-        <v>3965</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>1414</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>218894</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>10-19 #3 +1,414🚀 → 10-20 #3 +1,311 → 10-21 #4 +1,240</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" s="14" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>🚀 ponytail</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2818,26 +3188,80 @@
           </r>
         </is>
       </c>
-      <c r="E5" s="52" t="n">
+      <c r="E4" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="51" t="n">
-        <v>3287</v>
+      <c r="F4" s="55" t="n">
+        <v>5235</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>2079</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>173431</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>10-21 #5 +1,208 → 10-22 #1 +2,079🚀 → 10-23 #2 +1,948</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>作者 DietrichGebert</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>德文名</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>🚀 opencode</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>编程智能体</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>开源编程智能体</t>
+        </is>
+      </c>
+      <c r="E5" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="55" t="n">
+        <v>3965</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>2079</v>
+        <v>1414</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>171588</v>
+        <v>218894</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>10-21 #5 +1,208 → 10-22 #1 +2,079🚀</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>作者 DietrichGebert</t>
+          <t>10-19 #3 +1,414🚀 → 10-20 #3 +1,311 → 10-21 #4 +1,240</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
@@ -2845,9 +3269,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>德文名</t>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>未查到</t>
         </is>
       </c>
     </row>
@@ -2872,21 +3296,21 @@
           <t>把代码库、文档、SQL、PDF 变成可查询知识图谱</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="51" t="n">
-        <v>2235</v>
+      <c r="E6" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="55" t="n">
+        <v>3643</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>1433</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>131608</v>
+        <v>132924</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>10-21 #7 +802 → 10-22 #4 +1,433🚀</t>
+          <t>10-21 #7 +802 → 10-22 #4 +1,433🚀 → 10-23 #3 +1,408</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
@@ -2929,7 +3353,7 @@
       <c r="E7" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="51" t="n">
+      <c r="F7" s="55" t="n">
         <v>1464</v>
       </c>
       <c r="G7" s="8" t="n">
@@ -2983,7 +3407,7 @@
       <c r="E8" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F8" s="51" t="n">
+      <c r="F8" s="55" t="n">
         <v>1333</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -3014,54 +3438,54 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>🚀 jasna</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>supabase</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>视频修复工具</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="51" t="n">
-        <v>613</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>498</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>2879</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>10-19 #12 +115 → 10-20 #8 +498🚀</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Postgres 开发平台</t>
+        </is>
+      </c>
+      <c r="E9" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="58" t="n">
+        <v>1197</v>
+      </c>
+      <c r="G9" s="59" t="n">
+        <v>693</v>
+      </c>
+      <c r="H9" s="60" t="n">
+        <v>113473</v>
+      </c>
+      <c r="I9" s="27" t="inlineStr">
+        <is>
+          <t>10-22 #7 +504 → 10-23 #4 +693</t>
+        </is>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>Supabase</t>
+        </is>
+      </c>
+      <c r="K9" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="L9" s="36" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -3070,7 +3494,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>🚀 vllm</t>
+          <t>🚀 jasna</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -3080,34 +3504,34 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>推理基建</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>高吞吐 LLM 推理引擎</t>
+          <t>视频修复工具</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" s="51" t="n">
-        <v>569</v>
+        <v>8</v>
+      </c>
+      <c r="F10" s="55" t="n">
+        <v>613</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>441</v>
+        <v>498</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>94855</v>
+        <v>2879</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>10-21 #13 +128 → 10-22 #9 +441🚀</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>UC Berkeley 主导</t>
+          <t>10-19 #12 +115 → 10-20 #8 +498🚀</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -3122,58 +3546,58 @@
       </c>
     </row>
     <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>/dev/null</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>面向开发者的社交网络，JetBrains 办公室 48 小时直播从零写出来的开源项目</t>
         </is>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="32" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="33" t="n">
+      <c r="H11" s="30" t="n">
         <v>401</v>
       </c>
-      <c r="I11" s="30" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>10-20 #1</t>
         </is>
       </c>
-      <c r="J11" s="34" t="inlineStr">
+      <c r="J11" s="31" t="inlineStr">
         <is>
           <t>Nuno Maduro、Brent Roose、Matthieu Napoli、Pauline Vos 等</t>
         </is>
       </c>
-      <c r="K11" s="30" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t>JetBrains 直播</t>
         </is>
       </c>
-      <c r="L11" s="38" t="inlineStr">
+      <c r="L11" s="36" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -3200,20 +3624,20 @@
           <t>在一台 Mac 上跑 AI 智能体，在另一台上直接用它的窗口</t>
         </is>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H12" s="38" t="n">
         <v>293</v>
       </c>
       <c r="I12" s="18" t="inlineStr">
@@ -3231,65 +3655,65 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L12" s="27" t="inlineStr">
+      <c r="L12" s="24" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Inbox Zero</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>开源 AI 邮件助手兼客户端，对标 Superhuman</t>
         </is>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="32" t="inlineStr">
+      <c r="G13" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="33" t="n">
+      <c r="H13" s="30" t="n">
         <v>279</v>
       </c>
-      <c r="I13" s="30" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>10-18 #1</t>
         </is>
       </c>
-      <c r="J13" s="34" t="inlineStr">
+      <c r="J13" s="31" t="inlineStr">
         <is>
           <t>Elie Steinbock</t>
         </is>
       </c>
-      <c r="K13" s="30" t="inlineStr">
+      <c r="K13" s="27" t="inlineStr">
         <is>
           <t>以色列特拉维夫</t>
         </is>
       </c>
-      <c r="L13" s="38" t="inlineStr">
+      <c r="L13" s="36" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -3316,20 +3740,20 @@
           <t>给 AI 智能体接 1000+ 生产级工具，含托管鉴权与沙箱执行</t>
         </is>
       </c>
-      <c r="E14" s="53" t="n">
+      <c r="E14" s="61" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="G14" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H14" s="38" t="n">
         <v>251</v>
       </c>
       <c r="I14" s="18" t="inlineStr">
@@ -3354,93 +3778,93 @@
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>🚀 ai-job-search</t>
         </is>
       </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C15" s="44" t="inlineStr">
         <is>
           <t>应用</t>
         </is>
       </c>
-      <c r="D15" s="41" t="inlineStr">
+      <c r="D15" s="45" t="inlineStr">
         <is>
           <t>本机运行的 AI 求职框架，基于 Claude Code 评岗位、改简历、写求职信、备面试</t>
         </is>
       </c>
-      <c r="E15" s="54" t="n">
+      <c r="E15" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="55" t="n">
+      <c r="F15" s="63" t="n">
         <v>9949</v>
       </c>
-      <c r="G15" s="56" t="n">
+      <c r="G15" s="64" t="n">
         <v>3861</v>
       </c>
-      <c r="H15" s="57" t="n">
+      <c r="H15" s="65" t="n">
         <v>60514</v>
       </c>
-      <c r="I15" s="41" t="inlineStr">
+      <c r="I15" s="45" t="inlineStr">
         <is>
           <t>10-18/19 #1 +2,232🚀 → 10-20 #1 +3,856🚀 → 10-21 #1 +3,861</t>
         </is>
       </c>
-      <c r="J15" s="45" t="inlineStr">
+      <c r="J15" s="49" t="inlineStr">
         <is>
           <t>Mads Lorentzen</t>
         </is>
       </c>
-      <c r="K15" s="41" t="inlineStr">
+      <c r="K15" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="40" t="inlineStr">
+      <c r="L15" s="44" t="inlineStr">
         <is>
           <t>丹麦</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>VoiceStudio</t>
         </is>
       </c>
-      <c r="B16" s="40" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C16" s="40" t="inlineStr">
+      <c r="C16" s="44" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D16" s="41" t="inlineStr">
+      <c r="D16" s="45" t="inlineStr">
         <is>
           <t>完全本地的开源 ElevenLabs 替代品</t>
         </is>
       </c>
-      <c r="E16" s="42" t="n">
+      <c r="E16" s="66" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="43" t="n">
+      <c r="F16" s="52" t="n">
         <v>2082</v>
       </c>
-      <c r="G16" s="58" t="n">
+      <c r="G16" s="67" t="n">
         <v>2082</v>
       </c>
-      <c r="H16" s="44" t="n">
+      <c r="H16" s="53" t="n">
         <v>75310</v>
       </c>
-      <c r="I16" s="41" t="inlineStr">
+      <c r="I16" s="45" t="inlineStr">
         <is>
           <t>10-18/19 #2 +2,082</t>
         </is>
@@ -3450,51 +3874,51 @@
           <t>未查到</t>
         </is>
       </c>
-      <c r="K16" s="41" t="inlineStr">
+      <c r="K16" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L16" s="27" t="inlineStr">
+      <c r="L16" s="24" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>ruflo</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
         <is>
           <t>多智能体编排</t>
         </is>
       </c>
-      <c r="D17" s="41" t="inlineStr">
+      <c r="D17" s="45" t="inlineStr">
         <is>
           <t>多智能体蜂群编排框架</t>
         </is>
       </c>
-      <c r="E17" s="47" t="n">
+      <c r="E17" s="68" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="48" t="n">
+      <c r="F17" s="47" t="n">
         <v>1761</v>
       </c>
-      <c r="G17" s="59" t="n">
+      <c r="G17" s="69" t="n">
         <v>684</v>
       </c>
-      <c r="H17" s="49" t="n">
+      <c r="H17" s="48" t="n">
         <v>77830</v>
       </c>
-      <c r="I17" s="41" t="inlineStr">
+      <c r="I17" s="45" t="inlineStr">
         <is>
           <t>10-18/19 #7 +513 → 10-20 #7 +564 → 10-21 #9 +684</t>
         </is>
@@ -3504,12 +3928,12 @@
           <t>未查到</t>
         </is>
       </c>
-      <c r="K17" s="41" t="inlineStr">
+      <c r="K17" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L17" s="27" t="inlineStr">
+      <c r="L17" s="24" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -3557,92 +3981,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="B1" s="60" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>每周开源 / 产品 Sourcing 周报（2026-10-19 – 10-25）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="61" t="inlineStr">
-        <is>
-          <t>全球项目 14 个 · 华人项目 8 个 · 核心人物 19 位</t>
+      <c r="B2" s="71" t="inlineStr">
+        <is>
+          <t>全球项目 14 个 · 华人项目 11 个 · 核心人物 24 位</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="62" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t>本周总览</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="63" t="inlineStr">
+      <c r="A5" s="73" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="64" t="inlineStr">
-        <is>
-          <t>本周进行中 · 已更新至 10-22（第 4/7 天），每天日报后自动刷新。</t>
+      <c r="B5" s="74" t="inlineStr">
+        <is>
+          <t>本周进行中 · 已更新至 10-23（第 5/7 天），每天日报后自动刷新。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="63" t="inlineStr">
+      <c r="A6" s="73" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="64" t="inlineStr">
-        <is>
-          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search；已收录全球项目 14 个、华人项目 8 个，今日新增华人项目：UseIt Studio。</t>
+      <c r="B6" s="74" t="inlineStr">
+        <is>
+          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search；已收录全球项目 14 个、华人项目 11 个，今日新增华人项目：DeepCell、Meloong-Git/PCL、CutBay。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="73" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="B7" s="74" t="inlineStr">
         <is>
           <t>标「✨ 今日新增」的为今天首次上榜；灰色为前 3 周周报已出现过的项目，排在最后。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="65" t="inlineStr">
+      <c r="B9" s="75" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="66" t="inlineStr">
+      <c r="B10" s="76" t="inlineStr">
         <is>
           <t>黄底：日榜第 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="67" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>橙色：🚀 单日星增速明显放大（华人项目为 ≥ 前一天 1.5 倍）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="68" t="inlineStr">
+      <c r="B12" s="78" t="inlineStr">
         <is>
           <t>灰色斜体：未查到</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="69" t="inlineStr">
+      <c r="B14" s="79" t="inlineStr">
         <is>
           <t>网页版：https://psylch.github.io/rising-projects/2026-10-25/</t>
         </is>
@@ -3663,7 +4087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3735,34 +4159,34 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="40" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/yolandyan</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Yoland Yan（闫，全名中文未查到）</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E5" s="70" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t>https://x.com/yoland_yan</t>
         </is>
@@ -3789,34 +4213,34 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="40" t="inlineStr">
         <is>
           <t>https://github.com/yoland68</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Yoland Yan（闫，全名中文未查到）</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D7" s="30" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E7" s="70" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>https://www.stackforce.co/talent/6a4f76052978e57b300365dc</t>
         </is>
@@ -3843,34 +4267,34 @@
           <t>来源4</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="40" t="inlineStr">
         <is>
           <t>https://research.crustdata.com/company/comfyui</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Robin Huang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E9" s="70" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/robinjhuang</t>
         </is>
@@ -3897,34 +4321,34 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="40" t="inlineStr">
         <is>
           <t>https://x.com/robinjhuang</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Robin Huang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E11" s="70" t="inlineStr">
+      <c r="E11" s="34" t="inlineStr">
         <is>
           <t>https://github.com/robinjhuang</t>
         </is>
@@ -3951,34 +4375,34 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="40" t="inlineStr">
         <is>
           <t>https://www.getprog.ai/profile/5674242</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Comfy-Org/ComfyUI</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Robin Huang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E13" s="70" t="inlineStr">
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/posts/concordia-international-school-shanghai_comfy-jobs-activity-7498183966257078272-p3K4</t>
         </is>
@@ -4005,34 +4429,34 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="40" t="inlineStr">
         <is>
           <t>https://github.com/shiyu-coder</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>shiyu-coder/Kronos</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Yu Shi（中文名未查到）</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D15" s="30" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E15" s="70" t="inlineStr">
+      <c r="E15" s="34" t="inlineStr">
         <is>
           <t>https://arxiv.org/html/2508.02739</t>
         </is>
@@ -4059,48 +4483,48 @@
           <t>来源1</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="40" t="inlineStr">
         <is>
           <t>https://arxiv.org/html/2508.02739</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>UseIt Studio</t>
-        </is>
-      </c>
-      <c r="B17" s="30" t="inlineStr">
-        <is>
-          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
-        </is>
-      </c>
-      <c r="C17" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D17" s="30" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E17" s="70" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/daniel-gao-342504253</t>
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Meloong-Git/PCL</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>bilibili</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>https://space.bilibili.com/11343203/dynamic</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>UseIt Studio</t>
+          <t>Meloong-Git/PCL</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -4110,51 +4534,51 @@
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Google Scholar</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?hl=en&amp;user=No9OsocAAAAJ</t>
+          <t>afdian</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>https://meloong.com/afd/a/LTCat</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>UseIt Studio</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="inlineStr">
-        <is>
-          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
-        </is>
-      </c>
-      <c r="C19" s="29" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D19" s="30" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E19" s="70" t="inlineStr">
-        <is>
-          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Meloong-Git/PCL</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E19" s="34" t="inlineStr">
+        <is>
+          <t>https://meloong.com/PCL</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>UseIt Studio</t>
+          <t>Meloong-Git/PCL</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -4164,159 +4588,159 @@
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
+          <t>https://github.com/Meloong-Git/PCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>Meloong-Git/PCL</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E21" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/Meloong-Git</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Meloong-Git/PCL</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>https://www.alphaxiv.org/@difei-gao</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>UseIt Studio</t>
-        </is>
-      </c>
-      <c r="B21" s="30" t="inlineStr">
-        <is>
-          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
-        </is>
-      </c>
-      <c r="C21" s="29" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>来源4</t>
-        </is>
-      </c>
-      <c r="E21" s="70" t="inlineStr">
-        <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2024/html/Gao_AssistGUI_Task-Oriented_PC_Graphical_User_Interface_Automation_CVPR_2024_paper.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>UseIt Studio</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>陈芷恒（Lindia Chen）</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>producthunt</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/@lindiac</t>
+      <c r="E22" s="40" t="inlineStr">
+        <is>
+          <t>https://pcl2.aoe.top/</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="34" t="inlineStr">
-        <is>
-          <t>UseIt Studio</t>
-        </is>
-      </c>
-      <c r="B23" s="30" t="inlineStr">
-        <is>
-          <t>陈芷恒（Lindia Chen）</t>
-        </is>
-      </c>
-      <c r="C23" s="29" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D23" s="30" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E23" s="70" t="inlineStr">
-        <is>
-          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>DeepCell</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>梦琪（Mengqi）</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/deepcell-ai</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>UseIt Studio</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>陈芷恒（Lindia Chen）</t>
+          <t>梦琪（Mengqi）</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E24" s="40" t="inlineStr">
+        <is>
+          <t>https://deepcell.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>DeepCell</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>梦琪（Mengqi）</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/useit-studio-from-idea-to-delivery</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="34" t="inlineStr">
-        <is>
-          <t>UseIt Studio</t>
-        </is>
-      </c>
-      <c r="B25" s="30" t="inlineStr">
-        <is>
-          <t>丁云培</t>
-        </is>
-      </c>
-      <c r="C25" s="29" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D25" s="30" t="inlineStr">
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E25" s="70" t="inlineStr">
-        <is>
-          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>https://cn.ceibs.edu.cn/mba/student-life/27019</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>UseIt Studio</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>刘佳琦</t>
+          <t>梦琪（Mengqi）</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
@@ -4326,51 +4750,51 @@
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E26" s="40" t="inlineStr">
+        <is>
+          <t>https://www.ceibs.edu/mba/student-life/27022</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="34" t="inlineStr">
-        <is>
-          <t>Wally by Willow</t>
-        </is>
-      </c>
-      <c r="B27" s="30" t="inlineStr">
-        <is>
-          <t>Allan Guo</t>
-        </is>
-      </c>
-      <c r="C27" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D27" s="30" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E27" s="70" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/allan-guo</t>
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>DeepCell</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>梦琪（Mengqi）</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/deepcell</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>Wally by Willow</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Allan Guo</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
@@ -4383,48 +4807,48 @@
           <t>来源1</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/companies/willow</t>
+      <c r="E28" s="40" t="inlineStr">
+        <is>
+          <t>https://cn.ceibs.edu.cn/mba/student-life/27019</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="34" t="inlineStr">
-        <is>
-          <t>Wally by Willow</t>
-        </is>
-      </c>
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>Allan Guo</t>
-        </is>
-      </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>DeepCell</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D29" s="30" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E29" s="70" t="inlineStr">
-        <is>
-          <t>https://profiles.stanford.edu/allan-guo</t>
+      <c r="E29" s="34" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/deepcell</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>Wally by Willow</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>Lawrence Liu</t>
+          <t>Amy Wang</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
@@ -4437,102 +4861,102 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/lawrenceliuu</t>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/xinyuan4</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>Wally by Willow</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>Lawrence Liu</t>
-        </is>
-      </c>
-      <c r="C31" s="29" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>DeepCell</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Amy Wang</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E31" s="70" t="inlineStr">
-        <is>
-          <t>https://www.stackforce.co/talent/lawrence-liu-ceo-69d744662a55b09f46c5deaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
+      <c r="E31" s="34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/deepcell-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>Mintlify Autopilot</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>Han Wang（王，生于河南新乡）</t>
+          <t>Amy Wang</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E32" s="40" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/deepcell</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/handotdev</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="34" t="inlineStr">
-        <is>
-          <t>Mintlify Autopilot</t>
-        </is>
-      </c>
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>Han Wang（王，生于河南新乡）</t>
-        </is>
-      </c>
-      <c r="C33" s="29" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D33" s="30" t="inlineStr">
-        <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E33" s="70" t="inlineStr">
-        <is>
-          <t>https://han.dev/</t>
+      <c r="E33" s="34" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/daniel-gao-342504253</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>Mintlify Autopilot</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Han Wang（王，生于河南新乡）</t>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
@@ -4542,51 +4966,51 @@
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="inlineStr">
-        <is>
-          <t>https://x.com/handotdev</t>
+          <t>Google Scholar</t>
+        </is>
+      </c>
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>https://scholar.google.com/citations?hl=en&amp;user=No9OsocAAAAJ</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="34" t="inlineStr">
-        <is>
-          <t>Mintlify Autopilot</t>
-        </is>
-      </c>
-      <c r="B35" s="30" t="inlineStr">
-        <is>
-          <t>Han Wang（王，生于河南新乡）</t>
-        </is>
-      </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D35" s="30" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E35" s="70" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>Mintlify Autopilot</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Han Wang（王，生于河南新乡）</t>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
@@ -4599,48 +5023,48 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/handotdev_my-grandparents-in-rural-china-use-ai-more-activity-7430270997586489346-XzLv</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="34" t="inlineStr">
-        <is>
-          <t>Mintlify Autopilot</t>
-        </is>
-      </c>
-      <c r="B37" s="30" t="inlineStr">
-        <is>
-          <t>Hahnbee Lee</t>
-        </is>
-      </c>
-      <c r="C37" s="29" t="inlineStr">
+      <c r="E36" s="40" t="inlineStr">
+        <is>
+          <t>https://www.alphaxiv.org/@difei-gao</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D37" s="30" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E37" s="70" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
+      <c r="D37" s="27" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E37" s="34" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2024/html/Gao_AssistGUI_Task-Oriented_PC_Graphical_User_Interface_Automation_CVPR_2024_paper.html</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>Asimov 1</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Daniel Ong</t>
+          <t>陈芷恒（Lindia Chen）</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
@@ -4650,611 +5074,1151 @@
       </c>
       <c r="D38" s="18" t="inlineStr">
         <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E38" s="25" t="inlineStr">
-        <is>
-          <t>https://daniel.ai/</t>
+          <t>producthunt</t>
+        </is>
+      </c>
+      <c r="E38" s="40" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/@lindiac</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="34" t="inlineStr">
-        <is>
-          <t>Asimov 1</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="inlineStr">
-        <is>
-          <t>Daniel Ong</t>
-        </is>
-      </c>
-      <c r="C39" s="29" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D39" s="30" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E39" s="70" t="inlineStr">
-        <is>
-          <t>https://github.com/dan-menlo</t>
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>陈芷恒（Lindia Chen）</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E39" s="34" t="inlineStr">
+        <is>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Asimov 1</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Nicole Zhu</t>
+          <t>陈芷恒（Lindia Chen）</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E40" s="25" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/nicolezhu</t>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E40" s="40" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/useit-studio-from-idea-to-delivery</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>Asimov 1</t>
-        </is>
-      </c>
-      <c r="B41" s="30" t="inlineStr">
-        <is>
-          <t>Nicole Zhu</t>
-        </is>
-      </c>
-      <c r="C41" s="29" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D41" s="30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E41" s="70" t="inlineStr">
-        <is>
-          <t>https://x.com/freelerobot</t>
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>丁云培</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D41" s="27" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E41" s="34" t="inlineStr">
+        <is>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>Asimov 1</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Nicole Zhu</t>
+          <t>刘佳琦</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E42" s="40" t="inlineStr">
+        <is>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>Wally by Willow</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Allan Guo</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D43" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E43" s="34" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/allan-guo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Wally by Willow</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Allan Guo</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E44" s="40" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/willow</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>Wally by Willow</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Allan Guo</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D45" s="27" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E45" s="34" t="inlineStr">
+        <is>
+          <t>https://profiles.stanford.edu/allan-guo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>Wally by Willow</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>Lawrence Liu</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E46" s="40" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/lawrenceliuu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>Wally by Willow</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Lawrence Liu</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D47" s="27" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E47" s="34" t="inlineStr">
+        <is>
+          <t>https://www.stackforce.co/talent/lawrence-liu-ceo-69d744662a55b09f46c5deaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E48" s="40" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/handotdev</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="31" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
+      <c r="D49" s="27" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E42" s="25" t="inlineStr">
-        <is>
-          <t>https://nicole.ai/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="34" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B43" s="30" t="inlineStr">
-        <is>
-          <t>Jinjing Liang（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C43" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D43" s="30" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E43" s="70" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/jinjingliang</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="22" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>Jinjing Liang（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="E49" s="34" t="inlineStr">
+        <is>
+          <t>https://han.dev/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D44" s="18" t="inlineStr">
+      <c r="D50" s="18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E44" s="25" t="inlineStr">
-        <is>
-          <t>https://x.com/JinjingLiang</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="34" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B45" s="30" t="inlineStr">
-        <is>
-          <t>Jinjing Liang（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C45" s="29" t="inlineStr">
+      <c r="E50" s="40" t="inlineStr">
+        <is>
+          <t>https://x.com/handotdev</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D51" s="27" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E51" s="34" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Han Wang（王，生于河南新乡）</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E52" s="40" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/handotdev_my-grandparents-in-rural-china-use-ai-more-activity-7430270997586489346-XzLv</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="31" t="inlineStr">
+        <is>
+          <t>Mintlify Autopilot</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>Hahnbee Lee</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D53" s="27" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E53" s="34" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>CutBay</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>林霄（David Lin / Lin Xiao）</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D45" s="30" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E45" s="70" t="inlineStr">
-        <is>
-          <t>https://github.com/AmethystLiang</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B46" s="18" t="inlineStr">
-        <is>
-          <t>Jinjing Liang（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E54" s="40" t="inlineStr">
+        <is>
+          <t>https://www.cutbay.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="31" t="inlineStr">
+        <is>
+          <t>CutBay</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="inlineStr">
+        <is>
+          <t>林霄（David Lin / Lin Xiao）</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D46" s="18" t="inlineStr">
+      <c r="D55" s="27" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E46" s="25" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="34" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B47" s="30" t="inlineStr">
-        <is>
-          <t>Neil Parker</t>
-        </is>
-      </c>
-      <c r="C47" s="29" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D47" s="30" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E47" s="70" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/neilwilliamparker</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="22" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="inlineStr">
-        <is>
-          <t>Neil Parker</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E48" s="25" t="inlineStr">
-        <is>
-          <t>https://x.com/nwparker_</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="34" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B49" s="30" t="inlineStr">
-        <is>
-          <t>Neil Parker</t>
-        </is>
-      </c>
-      <c r="C49" s="29" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D49" s="30" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E49" s="70" t="inlineStr">
-        <is>
-          <t>https://github.com/nwparker</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="22" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B50" s="18" t="inlineStr">
-        <is>
-          <t>Neil Parker</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D50" s="18" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E50" s="25" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="34" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B51" s="30" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C51" s="29" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D51" s="30" t="inlineStr">
-        <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E51" s="70" t="inlineStr">
-        <is>
-          <t>https://sites.google.com/view/chaoh</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="22" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>GitHub 组织</t>
-        </is>
-      </c>
-      <c r="E52" s="25" t="inlineStr">
-        <is>
-          <t>https://github.com/HKUDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="34" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B53" s="30" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C53" s="29" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D53" s="30" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E53" s="70" t="inlineStr">
-        <is>
-          <t>https://datascience.hku.hk/people/chao-huang/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="22" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B54" s="18" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E54" s="25" t="inlineStr">
-        <is>
-          <t>https://www.ai.hku.hk/people/academic-staff/chuang</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="34" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B55" s="30" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C55" s="29" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D55" s="30" t="inlineStr">
-        <is>
-          <t>来源4</t>
-        </is>
-      </c>
-      <c r="E55" s="70" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2606.03854</t>
+      <c r="E55" s="34" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/introducing-cutbay-the-ai-video-agent-transforming-video-creation-with-chat-based-workflows-302908185.html</t>
         </is>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="22" t="inlineStr">
         <is>
+          <t>CutBay</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>林霄（David Lin / Lin Xiao）</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E56" s="40" t="inlineStr">
+        <is>
+          <t>https://www.cutbay.ai/about</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t>CutBay</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>林霄（David Lin / Lin Xiao）</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D57" s="27" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E57" s="34" t="inlineStr">
+        <is>
+          <t>https://kr-asia.com/developing-easy-to-use-software-for-video-editing-inside-chinas-startups</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>Daniel Ong</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E58" s="40" t="inlineStr">
+        <is>
+          <t>https://daniel.ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="31" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>Daniel Ong</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D59" s="27" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E59" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/dan-menlo</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>Nicole Zhu</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E60" s="40" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/nicolezhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>Nicole Zhu</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D61" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E61" s="34" t="inlineStr">
+        <is>
+          <t>https://x.com/freelerobot</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>Nicole Zhu</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E62" s="40" t="inlineStr">
+        <is>
+          <t>https://nicole.ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D63" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E63" s="34" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/jinjingliang</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E64" s="40" t="inlineStr">
+        <is>
+          <t>https://x.com/JinjingLiang</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="36" customHeight="1">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D65" s="27" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E65" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/AmethystLiang</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E66" s="40" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B67" s="27" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D67" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E67" s="34" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/neilwilliamparker</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E68" s="40" t="inlineStr">
+        <is>
+          <t>https://x.com/nwparker_</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B69" s="27" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D69" s="27" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E69" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/nwparker</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="22" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E70" s="40" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B56" s="18" t="inlineStr">
+      <c r="B71" s="27" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C71" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D71" s="27" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E71" s="34" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/chaoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>GitHub 组织</t>
+        </is>
+      </c>
+      <c r="E72" s="40" t="inlineStr">
+        <is>
+          <t>https://github.com/HKUDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C73" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D73" s="27" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E73" s="34" t="inlineStr">
+        <is>
+          <t>https://datascience.hku.hk/people/chao-huang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E74" s="40" t="inlineStr">
+        <is>
+          <t>https://www.ai.hku.hk/people/academic-staff/chuang</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B75" s="27" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C75" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D75" s="27" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E75" s="34" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.03854</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C56" s="17" t="inlineStr">
+      <c r="C76" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D56" s="18" t="inlineStr">
+      <c r="D76" s="18" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E56" s="25" t="inlineStr">
+      <c r="E76" s="40" t="inlineStr">
         <is>
           <t>https://yuh-yang.github.io</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="36" customHeight="1">
-      <c r="A57" s="34" t="inlineStr">
+    <row r="77" ht="36" customHeight="1">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B57" s="30" t="inlineStr">
+      <c r="B77" s="27" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C57" s="29" t="inlineStr">
+      <c r="C77" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D57" s="30" t="inlineStr">
+      <c r="D77" s="27" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E57" s="70" t="inlineStr">
+      <c r="E77" s="34" t="inlineStr">
         <is>
           <t>https://github.com/yuh-yang</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="36" customHeight="1">
-      <c r="A58" s="22" t="inlineStr">
+    <row r="78" ht="36" customHeight="1">
+      <c r="A78" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B58" s="18" t="inlineStr">
+      <c r="B78" s="18" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C58" s="17" t="inlineStr">
+      <c r="C78" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D58" s="18" t="inlineStr">
+      <c r="D78" s="18" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E58" s="25" t="inlineStr">
+      <c r="E78" s="40" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="36" customHeight="1">
-      <c r="A59" s="34" t="inlineStr">
+    <row r="79" ht="36" customHeight="1">
+      <c r="A79" s="31" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B59" s="30" t="inlineStr">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="C59" s="29" t="inlineStr">
+      <c r="C79" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D59" s="30" t="inlineStr">
+      <c r="D79" s="27" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E59" s="70" t="inlineStr">
+      <c r="E79" s="34" t="inlineStr">
         <is>
           <t>https://tianyufan0504.github.io/</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="36" customHeight="1">
-      <c r="A60" s="22" t="inlineStr">
+    <row r="80" ht="36" customHeight="1">
+      <c r="A80" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B60" s="18" t="inlineStr">
+      <c r="B80" s="18" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="C60" s="17" t="inlineStr">
+      <c r="C80" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D60" s="18" t="inlineStr">
+      <c r="D80" s="18" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E60" s="25" t="inlineStr">
+      <c r="E80" s="40" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E60"/>
+  <autoFilter ref="A3:E80"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -5317,6 +6281,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId77"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/2026-10-25/weekly-2026-10-25.xlsx
+++ b/2026-10-25/weekly-2026-10-25.xlsx
@@ -13,15 +13,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'华人项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全球项目'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$102</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'链接'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$80</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -306,7 +306,28 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -315,20 +336,10 @@
     <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -343,10 +354,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="168" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -391,20 +406,8 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -809,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1308,101 +1311,409 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="50" customHeight="1">
+    <row r="8" ht="64" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
+          <t>ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>紫微斗数开源排盘引擎（倪海厦《天纪》体系）+ 67.5 万命盘×13 维解读数据集 v4.0；商业站 metisziwei.com</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>546</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>6845</v>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>10-24 #5 +546</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>作者 / Metis 创始人，自称一人用 AI 做出商业化 SaaS</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>Metis紫微创始人；称专业版订阅超 800、注册超 1 万</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>重庆（运营主体注册地）</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>wdy778@outlook.com</t>
+        </is>
+      </c>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O8" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P8" s="18" t="inlineStr">
+        <is>
+          <t>X
+王多鱼AI2.0
+王多鱼AI
+GitHub</t>
+        </is>
+      </c>
+      <c r="Q8" s="18" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3、来源4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>VoxCPM</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>VoxCPM2 无分词器多语种 TTS；面壁智能（ModelBest）、OpenBMB、清华深研院与清华 NLP 联合发布</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>150</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>40245</v>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>10-24 #7 +150</t>
+        </is>
+      </c>
+      <c r="H9" s="31" t="inlineStr">
+        <is>
+          <t>周逸轩（Yixuan Zhou）</t>
+        </is>
+      </c>
+      <c r="I9" s="27" t="inlineStr">
+        <is>
+          <t>核心贡献者，技术报告第一作者</t>
+        </is>
+      </c>
+      <c r="J9" s="27" t="inlineStr">
+        <is>
+          <t>清华大学博士生（TTS/语音/NLP）</t>
+        </is>
+      </c>
+      <c r="K9" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L9" s="27" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="M9" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N9" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O9" s="33" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P9" s="27" t="inlineStr">
+        <is>
+          <t>GitHub
+Google Scholar</t>
+        </is>
+      </c>
+      <c r="Q9" s="27" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>ZGY（GitHub a710128，全名未查到）</t>
+        </is>
+      </c>
+      <c r="I10" s="27" t="inlineStr">
+        <is>
+          <t>主要贡献者</t>
+        </is>
+      </c>
+      <c r="J10" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K10" s="27" t="inlineStr">
+        <is>
+          <t>OpenBMB</t>
+        </is>
+      </c>
+      <c r="L10" s="27" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="M10" s="27" t="inlineStr">
+        <is>
+          <t>qbjooo@qq.com</t>
+        </is>
+      </c>
+      <c r="N10" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O10" s="33" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P10" s="34" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="Q10" s="34" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
           <t>PCL</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Minecraft 启动器 Plain Craft Launcher（PCL）</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D11" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E11" s="20" t="n">
         <v>119</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F11" s="21" t="n">
         <v>8682</v>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>10-23 #8 +119</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>龙腾猫跃（LTCatt / LTCat）</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>主要作者</t>
         </is>
       </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
         <is>
           <t>Meloong（瓜皮龙工作室）开发 PCL/PCL2</t>
         </is>
       </c>
-      <c r="L8" s="18" t="inlineStr">
+      <c r="L11" s="18" t="inlineStr">
         <is>
           <t>中国</t>
         </is>
       </c>
-      <c r="M8" s="18" t="inlineStr">
+      <c r="M11" s="18" t="inlineStr">
         <is>
           <t>admin@meloong.com</t>
         </is>
       </c>
-      <c r="N8" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O8" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P8" s="18" t="inlineStr">
+      <c r="N11" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O11" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P11" s="18" t="inlineStr">
         <is>
           <t>bilibili
 afdian
 个人站</t>
         </is>
       </c>
-      <c r="Q8" s="18" t="inlineStr">
+      <c r="Q11" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>MOVO AI</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>手机端长视频 AI 智能体，对话式规划、生成、拼接，跨集保持角色一致</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="n">
+        <v>277</v>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>10-23 #2</t>
+        </is>
+      </c>
+      <c r="H12" s="31" t="inlineStr">
+        <is>
+          <t>陈麒聪（Edward Chen）</t>
+        </is>
+      </c>
+      <c r="I12" s="27" t="inlineStr">
+        <is>
+          <t>MOVO AI Co-Maker；Speakly AI / 循环智能联合创始人兼 CEO</t>
+        </is>
+      </c>
+      <c r="J12" s="27" t="inlineStr">
+        <is>
+          <t>卡内基梅隆大学计算机学院语言技术研究所（LTI）</t>
+        </is>
+      </c>
+      <c r="K12" s="27" t="inlineStr">
+        <is>
+          <t>2016 起任循环智能（Recurrent AI，红杉中国、真格等投资）CEO，2024–2026.04 任 Speakly AI CEO；入选创业邦 30 岁以下创业新贵</t>
+        </is>
+      </c>
+      <c r="L12" s="27" t="inlineStr">
+        <is>
+          <t>美国（LinkedIn）</t>
+        </is>
+      </c>
+      <c r="M12" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N12" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O12" s="38" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P12" s="27" t="inlineStr">
+        <is>
+          <t>@edward_chen11</t>
+        </is>
+      </c>
+      <c r="Q12" s="27" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3、来源4、来源5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>DeepCell</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1423,203 +1734,203 @@
           </r>
         </is>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D13" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E13" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F13" s="41" t="n">
         <v>265</v>
       </c>
-      <c r="G9" s="27" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>10-22 #1</t>
         </is>
       </c>
-      <c r="H9" s="31" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>梦琪（Mengqi）</t>
         </is>
       </c>
-      <c r="I9" s="27" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>联合创始人 / 主要搭建者</t>
         </is>
       </c>
-      <c r="J9" s="27" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>中欧 MBA 2024</t>
         </is>
       </c>
-      <c r="K9" s="27" t="inlineStr">
+      <c r="K13" s="18" t="inlineStr">
         <is>
           <t>非 CS 科班；用 AI coding 从 0 写产品前后端；约 10 年企业职场</t>
         </is>
       </c>
-      <c r="L9" s="27" t="inlineStr">
+      <c r="L13" s="18" t="inlineStr">
         <is>
           <t>上海（公司总部）</t>
         </is>
       </c>
-      <c r="M9" s="27" t="inlineStr">
+      <c r="M13" s="18" t="inlineStr">
         <is>
           <t>hello@deepcell.net</t>
         </is>
       </c>
-      <c r="N9" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O9" s="33" t="inlineStr">
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O13" s="42" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P9" s="34" t="inlineStr">
+      <c r="P13" s="43" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="Q9" s="27" t="inlineStr">
+      <c r="Q13" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="31" t="inlineStr">
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="44" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="44" t="n"/>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>Jack</t>
         </is>
       </c>
-      <c r="I10" s="27" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>产品联合创始人</t>
         </is>
       </c>
-      <c r="J10" s="27" t="inlineStr">
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>中欧 MBA 2024</t>
         </is>
       </c>
-      <c r="K10" s="27" t="inlineStr">
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t>前 PwC 约四年，估值建模与投资备忘录</t>
         </is>
       </c>
-      <c r="L10" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M10" s="27" t="inlineStr">
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="inlineStr">
         <is>
           <t>hello@deepcell.net</t>
         </is>
       </c>
-      <c r="N10" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O10" s="36" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P10" s="27" t="inlineStr">
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O14" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P14" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q10" s="27" t="inlineStr">
+      <c r="Q14" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="13" t="n"/>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="31" t="inlineStr">
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>Amy Wang</t>
         </is>
       </c>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>联合创始人</t>
         </is>
       </c>
-      <c r="J11" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>软件工程师背景；DeepCell 联合创始人</t>
         </is>
       </c>
-      <c r="L11" s="27" t="inlineStr">
+      <c r="L15" s="18" t="inlineStr">
         <is>
           <t>上海 / 胡志明市（LinkedIn 任职地不一）</t>
         </is>
       </c>
-      <c r="M11" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N11" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O11" s="33" t="inlineStr">
+      <c r="M15" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N15" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O15" s="42" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P11" s="27" t="inlineStr">
+      <c r="P15" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q11" s="27" t="inlineStr">
+      <c r="Q15" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>UseIt Studio</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1640,299 +1951,299 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D16" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="37" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="38" t="n">
+      <c r="F16" s="37" t="n">
         <v>264</v>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>10-21 #1</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H16" s="31" t="inlineStr">
         <is>
           <t>郜迪飞（Difei Gao / Daniel Gao）</t>
         </is>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>创始人兼 CEO</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="J16" s="27" t="inlineStr">
         <is>
           <t>中科院计算所博士；NUS 博士后</t>
         </is>
       </c>
-      <c r="K12" s="18" t="inlineStr">
+      <c r="K16" s="27" t="inlineStr">
         <is>
           <t>NUS Show Lab 高级研究员；AssistGUI、AssistGPT、ShowUI 作者；2025-07 起创办 UseIt AI</t>
         </is>
       </c>
-      <c r="L12" s="18" t="inlineStr">
+      <c r="L16" s="27" t="inlineStr">
         <is>
           <t>新加坡</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N12" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O12" s="39" t="inlineStr">
+      <c r="M16" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N16" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O16" s="38" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P12" s="40" t="inlineStr">
+      <c r="P16" s="34" t="inlineStr">
         <is>
           <t>Google Scholar</t>
         </is>
       </c>
-      <c r="Q12" s="18" t="inlineStr">
+      <c r="Q16" s="27" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="22" t="inlineStr">
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="44" t="n"/>
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+      <c r="F17" s="44" t="n"/>
+      <c r="G17" s="44" t="n"/>
+      <c r="H17" s="31" t="inlineStr">
         <is>
           <t>陈芷恒（Lindia Chen）</t>
         </is>
       </c>
-      <c r="I13" s="18" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>联合创始人兼增长负责人</t>
         </is>
       </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="J17" s="27" t="inlineStr">
         <is>
           <t>新加坡国立大学硕士</t>
         </is>
       </c>
-      <c r="K13" s="18" t="inlineStr">
+      <c r="K17" s="27" t="inlineStr">
         <is>
           <t>曾在学而思做策划；上海中学校友</t>
         </is>
       </c>
-      <c r="L13" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M13" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O13" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P13" s="40" t="inlineStr">
+      <c r="L17" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M17" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N17" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O17" s="33" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P17" s="34" t="inlineStr">
         <is>
           <t>producthunt</t>
         </is>
       </c>
-      <c r="Q13" s="18" t="inlineStr">
+      <c r="Q17" s="27" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="22" t="inlineStr">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="44" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="44" t="n"/>
+      <c r="F18" s="44" t="n"/>
+      <c r="G18" s="44" t="n"/>
+      <c r="H18" s="31" t="inlineStr">
         <is>
           <t>丁云培</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>联合创始人兼产品负责人</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J18" s="27" t="inlineStr">
         <is>
           <t>UCL 计算机视觉硕士</t>
         </is>
       </c>
-      <c r="K14" s="18" t="inlineStr">
+      <c r="K18" s="27" t="inlineStr">
         <is>
           <t>连续创业者</t>
         </is>
       </c>
-      <c r="L14" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M14" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N14" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O14" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="Q14" s="40" t="inlineStr">
+      <c r="L18" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M18" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N18" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O18" s="33" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P18" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q18" s="34" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="22" t="inlineStr">
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="31" t="inlineStr">
         <is>
           <t>刘佳琦</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>联合创始人兼技术负责人</t>
         </is>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J19" s="27" t="inlineStr">
         <is>
           <t>北京工业大学人工智能博士</t>
         </is>
       </c>
-      <c r="K15" s="18" t="inlineStr">
+      <c r="K19" s="27" t="inlineStr">
         <is>
           <t>连续创业者；前 AIGC 创作分享平台技术负责人</t>
         </is>
       </c>
-      <c r="L15" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M15" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N15" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O15" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="Q15" s="40" t="inlineStr">
+      <c r="L19" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M19" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N19" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O19" s="33" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P19" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q19" s="34" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="64" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Wally by Willow</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>语音</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>Mac AI 语音输入工具 Willow 的新功能 Wally，学习用户写作风格；YC 公司，2025 年成立，团队 7 人，总部旧金山
 团队：按姓名与背景判断为华人，本人族裔表述未查到</t>
         </is>
       </c>
-      <c r="D16" s="41" t="n">
+      <c r="D20" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="E16" s="29" t="inlineStr">
+      <c r="E20" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F20" s="41" t="n">
         <v>123</v>
       </c>
-      <c r="G16" s="27" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t>10-19 #7</t>
         </is>
       </c>
-      <c r="H16" s="31" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>Allan Guo</t>
         </is>
       </c>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO</t>
         </is>
       </c>
-      <c r="J16" s="27" t="inlineStr">
+      <c r="J20" s="18" t="inlineStr">
         <is>
           <t>斯坦福计算机系（2023–2024，离校创业）；University of Toronto Schools</t>
         </is>
       </c>
-      <c r="K16" s="27" t="inlineStr">
+      <c r="K20" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1953,61 +2264,61 @@
           </r>
         </is>
       </c>
-      <c r="L16" s="27" t="inlineStr">
+      <c r="L20" s="18" t="inlineStr">
         <is>
           <t>旧金山</t>
         </is>
       </c>
-      <c r="M16" s="27" t="inlineStr">
+      <c r="M20" s="18" t="inlineStr">
         <is>
           <t>allanguo@stanford.edu</t>
         </is>
       </c>
-      <c r="N16" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O16" s="33" t="inlineStr">
+      <c r="N20" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O20" s="42" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P16" s="27" t="inlineStr">
+      <c r="P20" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q16" s="27" t="inlineStr">
+      <c r="Q20" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="13" t="n"/>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="31" t="inlineStr">
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>Lawrence Liu</t>
         </is>
       </c>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>联合创始人兼 CTO</t>
         </is>
       </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="J21" s="18" t="inlineStr">
         <is>
           <t>斯坦福计算机学士；就读过卡内基梅隆；Fox Chapel Area High School</t>
         </is>
       </c>
-      <c r="K17" s="27" t="inlineStr">
+      <c r="K21" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2036,85 +2347,85 @@
           </r>
         </is>
       </c>
-      <c r="L17" s="27" t="inlineStr">
+      <c r="L21" s="18" t="inlineStr">
         <is>
           <t>LinkedIn 写匹兹堡；公司在旧金山</t>
         </is>
       </c>
-      <c r="M17" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N17" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O17" s="33" t="inlineStr">
+      <c r="M21" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N21" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O21" s="42" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P17" s="27" t="inlineStr">
+      <c r="P21" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q17" s="27" t="inlineStr">
+      <c r="Q21" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="22" ht="50" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Mintlify Autopilot</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>Mintlify 常驻文档智能体，自动随代码更新文档；YC 公司</t>
         </is>
       </c>
-      <c r="D18" s="42" t="n">
+      <c r="D22" s="46" t="n">
         <v>6</v>
       </c>
-      <c r="E18" s="37" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="38" t="n">
+      <c r="F22" s="37" t="n">
         <v>122</v>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G22" s="27" t="inlineStr">
         <is>
           <t>10-20 #6</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H22" s="31" t="inlineStr">
         <is>
           <t>Han Wang（王，生于河南新乡）</t>
         </is>
       </c>
-      <c r="I18" s="18" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO</t>
         </is>
       </c>
-      <c r="J18" s="18" t="inlineStr">
+      <c r="J22" s="27" t="inlineStr">
         <is>
           <t>康奈尔大学信息科学学士</t>
         </is>
       </c>
-      <c r="K18" s="18" t="inlineStr">
+      <c r="K22" s="27" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2135,289 +2446,289 @@
           </r>
         </is>
       </c>
-      <c r="L18" s="18" t="inlineStr">
+      <c r="L22" s="27" t="inlineStr">
         <is>
           <t>旧金山</t>
         </is>
       </c>
-      <c r="M18" s="18" t="inlineStr">
+      <c r="M22" s="27" t="inlineStr">
         <is>
           <t>han@mintlify.com</t>
         </is>
       </c>
-      <c r="N18" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O18" s="39" t="inlineStr">
+      <c r="N22" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O22" s="38" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P18" s="18" t="inlineStr">
+      <c r="P22" s="27" t="inlineStr">
         <is>
           <t>个人站
 X</t>
         </is>
       </c>
-      <c r="Q18" s="18" t="inlineStr">
+      <c r="Q22" s="27" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="13" t="n"/>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="22" t="inlineStr">
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="31" t="inlineStr">
         <is>
           <t>Hahnbee Lee</t>
         </is>
       </c>
-      <c r="I19" s="18" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>联合创始人</t>
         </is>
       </c>
-      <c r="J19" s="18" t="inlineStr">
+      <c r="J23" s="27" t="inlineStr">
         <is>
           <t>康奈尔大学计算机本科</t>
         </is>
       </c>
-      <c r="K19" s="18" t="inlineStr">
+      <c r="K23" s="27" t="inlineStr">
         <is>
           <t>与 Han 共同创办 Mintlify；早年参与 People</t>
         </is>
       </c>
-      <c r="L19" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M19" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N19" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O19" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P19" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="Q19" s="40" t="inlineStr">
+      <c r="L23" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M23" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N23" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O23" s="33" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P23" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q23" s="34" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="50" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+    <row r="24" ht="50" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>CutBay</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>聊天式 AI 视频智能体，由 PearlMountain（FlexClip 团队）出品</t>
         </is>
       </c>
-      <c r="D20" s="41" t="n">
+      <c r="D24" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="E20" s="29" t="inlineStr">
+      <c r="E24" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F24" s="41" t="n">
         <v>117</v>
       </c>
-      <c r="G20" s="27" t="inlineStr">
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>10-22 #9</t>
         </is>
       </c>
-      <c r="H20" s="31" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>林霄（David Lin / Lin Xiao）</t>
         </is>
       </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>PearlMountain 创始人兼 CEO</t>
         </is>
       </c>
-      <c r="J20" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K20" s="27" t="inlineStr">
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>PearlMountain Limited 创始人；FlexClip 创始人兼 CEO</t>
         </is>
       </c>
-      <c r="L20" s="27" t="inlineStr">
+      <c r="L24" s="18" t="inlineStr">
         <is>
           <t>香港（公司）</t>
         </is>
       </c>
-      <c r="M20" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N20" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O20" s="36" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P20" s="34" t="inlineStr">
+      <c r="M24" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N24" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O24" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P24" s="43" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="Q20" s="27" t="inlineStr">
+      <c r="Q24" s="18" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="50" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="25" ht="50" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Asimov 1</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>Menlo Research 的可定制人形机器人；新加坡开放 AI/机器人实验室
 团队：新加坡华人背景（籍贯/姓氏）；Daniel 公开写在新加坡长大</t>
         </is>
       </c>
-      <c r="D21" s="42" t="n">
+      <c r="D25" s="46" t="n">
         <v>8</v>
       </c>
-      <c r="E21" s="37" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="38" t="n">
+      <c r="F25" s="37" t="n">
         <v>110</v>
       </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="G25" s="27" t="inlineStr">
         <is>
           <t>10-20 #8</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H25" s="31" t="inlineStr">
         <is>
           <t>Daniel Ong</t>
         </is>
       </c>
-      <c r="I21" s="18" t="inlineStr">
+      <c r="I25" s="27" t="inlineStr">
         <is>
           <t>联合创始人</t>
         </is>
       </c>
-      <c r="J21" s="18" t="inlineStr">
+      <c r="J25" s="27" t="inlineStr">
         <is>
           <t>斯坦福大学（转读计算机）</t>
         </is>
       </c>
-      <c r="K21" s="18" t="inlineStr">
+      <c r="K25" s="27" t="inlineStr">
         <is>
           <t>新加坡警察 5 年；早期以太坊相关创业；与 Nicole 创办 Menlo Research</t>
         </is>
       </c>
-      <c r="L21" s="18" t="inlineStr">
+      <c r="L25" s="27" t="inlineStr">
         <is>
           <t>新加坡</t>
         </is>
       </c>
-      <c r="M21" s="18" t="inlineStr">
+      <c r="M25" s="27" t="inlineStr">
         <is>
           <t>dan@daniel.ai</t>
         </is>
       </c>
-      <c r="N21" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O21" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P21" s="18" t="inlineStr">
+      <c r="N25" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O25" s="33" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P25" s="27" t="inlineStr">
         <is>
           <t>个人站
 GitHub</t>
         </is>
       </c>
-      <c r="Q21" s="18" t="inlineStr">
+      <c r="Q25" s="27" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="22" t="inlineStr">
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="31" t="inlineStr">
         <is>
           <t>Nicole Zhu</t>
         </is>
       </c>
-      <c r="I22" s="18" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>联合创始人</t>
         </is>
       </c>
-      <c r="J22" s="18" t="inlineStr">
+      <c r="J26" s="27" t="inlineStr">
         <is>
           <t>斯坦福机械工程学士、计算机硕士</t>
         </is>
       </c>
-      <c r="K22" s="18" t="inlineStr">
+      <c r="K26" s="27" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2446,50 +2757,212 @@
           </r>
         </is>
       </c>
-      <c r="L22" s="18" t="inlineStr">
+      <c r="L26" s="27" t="inlineStr">
         <is>
           <t>新加坡</t>
         </is>
       </c>
-      <c r="M22" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N22" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O22" s="39" t="inlineStr">
+      <c r="M26" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N26" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O26" s="38" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P22" s="18" t="inlineStr">
+      <c r="P26" s="27" t="inlineStr">
         <is>
           <t>X
 个人站</t>
         </is>
       </c>
-      <c r="Q22" s="18" t="inlineStr">
+      <c r="Q26" s="27" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="64" customHeight="1">
-      <c r="A23" s="43" t="inlineStr">
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Agent Hunt · Monid</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>智能体工具版 OpenRouter</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：一个接入调用 2,700+ API、按次付费；Agent Hunt 为智能体真实调用排行</t>
+          </r>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>Shengkun Ye</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>联合创始人</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>华盛顿大学（University of Washington）</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>前 TabaPay 产品</t>
+        </is>
+      </c>
+      <c r="L27" s="18" t="inlineStr">
+        <is>
+          <t>旧金山</t>
+        </is>
+      </c>
+      <c r="M27" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N27" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O27" s="42" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P27" s="43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q27" s="18" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>Feiyou Guo</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>联合创始人</t>
+        </is>
+      </c>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>华盛顿大学 计算机科学与生物（2018–2023）</t>
+        </is>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>Founders, Inc. 驻场创业者（2026.04 起）</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="inlineStr">
+        <is>
+          <t>旧金山湾区</t>
+        </is>
+      </c>
+      <c r="M28" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N28" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O28" s="42" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P28" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q28" s="18" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="48" t="inlineStr">
         <is>
           <t>orca</t>
         </is>
       </c>
-      <c r="B23" s="44" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>编程智能体</t>
         </is>
       </c>
-      <c r="C23" s="45" t="inlineStr">
+      <c r="C29" s="50" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2510,36 +2983,36 @@
           </r>
         </is>
       </c>
-      <c r="D23" s="46" t="n">
+      <c r="D29" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="47" t="n">
+      <c r="E29" s="52" t="n">
         <v>5842</v>
       </c>
-      <c r="F23" s="48" t="n">
+      <c r="F29" s="53" t="n">
         <v>101219</v>
       </c>
-      <c r="G23" s="45" t="inlineStr">
+      <c r="G29" s="50" t="inlineStr">
         <is>
           <t>10-18/19 #5 +1,146 → 10-20 #2 +1,590 → 10-21 #3 +1,565 → 10-22 #3 +1,541</t>
         </is>
       </c>
-      <c r="H23" s="49" t="inlineStr">
+      <c r="H29" s="54" t="inlineStr">
         <is>
           <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
-      <c r="I23" s="45" t="inlineStr">
+      <c r="I29" s="50" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO，Orca 维护者</t>
         </is>
       </c>
-      <c r="J23" s="45" t="inlineStr">
+      <c r="J29" s="50" t="inlineStr">
         <is>
           <t>康奈尔大学校友（专业与学位未查到）</t>
         </is>
       </c>
-      <c r="K23" s="45" t="inlineStr">
+      <c r="K29" s="50" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2568,62 +3041,62 @@
           </r>
         </is>
       </c>
-      <c r="L23" s="45" t="inlineStr">
+      <c r="L29" s="50" t="inlineStr">
         <is>
           <t>美国旧金山湾区</t>
         </is>
       </c>
-      <c r="M23" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N23" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O23" s="50" t="inlineStr">
+      <c r="M29" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N29" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O29" s="55" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P23" s="45" t="inlineStr">
+      <c r="P29" s="50" t="inlineStr">
         <is>
           <t>X
 GitHub</t>
         </is>
       </c>
-      <c r="Q23" s="45" t="inlineStr">
+      <c r="Q29" s="50" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="50" customHeight="1">
-      <c r="A24" s="13" t="n"/>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="49" t="inlineStr">
+    <row r="30" ht="50" customHeight="1">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="54" t="inlineStr">
         <is>
           <t>Neil Parker</t>
         </is>
       </c>
-      <c r="I24" s="45" t="inlineStr">
+      <c r="I30" s="50" t="inlineStr">
         <is>
           <t>联合创始人兼 CTO（非华人，列作团队参考）</t>
         </is>
       </c>
-      <c r="J24" s="45" t="inlineStr">
+      <c r="J30" s="50" t="inlineStr">
         <is>
           <t>康奈尔大学校友</t>
         </is>
       </c>
-      <c r="K24" s="45" t="inlineStr">
+      <c r="K30" s="50" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2652,50 +3125,50 @@
           </r>
         </is>
       </c>
-      <c r="L24" s="45" t="inlineStr">
+      <c r="L30" s="50" t="inlineStr">
         <is>
           <t>美国旧金山湾区</t>
         </is>
       </c>
-      <c r="M24" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N24" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O24" s="50" t="inlineStr">
+      <c r="M30" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N30" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O30" s="55" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P24" s="45" t="inlineStr">
+      <c r="P30" s="50" t="inlineStr">
         <is>
           <t>X
 GitHub</t>
         </is>
       </c>
-      <c r="Q24" s="45" t="inlineStr">
+      <c r="Q30" s="50" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="64" customHeight="1">
-      <c r="A25" s="43" t="inlineStr">
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="48" t="inlineStr">
         <is>
           <t>CLI-Anything</t>
         </is>
       </c>
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>智能体工具</t>
         </is>
       </c>
-      <c r="C25" s="45" t="inlineStr">
+      <c r="C31" s="50" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2716,36 +3189,36 @@
           </r>
         </is>
       </c>
-      <c r="D25" s="51" t="n">
+      <c r="D31" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="E25" s="52" t="n">
+      <c r="E31" s="57" t="n">
         <v>1195</v>
       </c>
-      <c r="F25" s="53" t="n">
+      <c r="F31" s="58" t="n">
         <v>55221</v>
       </c>
-      <c r="G25" s="45" t="inlineStr">
+      <c r="G31" s="50" t="inlineStr">
         <is>
           <t>10-18/19 #6 +589 → 10-20 #6 +606</t>
         </is>
       </c>
-      <c r="H25" s="49" t="inlineStr">
+      <c r="H31" s="54" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="I25" s="45" t="inlineStr">
+      <c r="I31" s="50" t="inlineStr">
         <is>
           <t>通讯作者、HKUDS / Data Intelligence Lab 负责人</t>
         </is>
       </c>
-      <c r="J25" s="45" t="inlineStr">
+      <c r="J31" s="50" t="inlineStr">
         <is>
           <t>University of Notre Dame 计算机博士；现港大计算机系助理教授</t>
         </is>
       </c>
-      <c r="K25" s="45" t="inlineStr">
+      <c r="K31" s="50" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2766,124 +3239,124 @@
           </r>
         </is>
       </c>
-      <c r="L25" s="45" t="inlineStr">
+      <c r="L31" s="50" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M25" s="45" t="inlineStr">
+      <c r="M31" s="50" t="inlineStr">
         <is>
           <t>chuang@cs.hku.hk
 chaohuang75@gmail.com</t>
         </is>
       </c>
-      <c r="N25" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O25" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P25" s="45" t="inlineStr">
+      <c r="N31" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O31" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P31" s="50" t="inlineStr">
         <is>
           <t>个人站
 GitHub 组织</t>
         </is>
       </c>
-      <c r="Q25" s="45" t="inlineStr">
+      <c r="Q31" s="50" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="64" customHeight="1">
-      <c r="A26" s="35" t="n"/>
-      <c r="B26" s="35" t="n"/>
-      <c r="C26" s="35" t="n"/>
-      <c r="D26" s="35" t="n"/>
-      <c r="E26" s="35" t="n"/>
-      <c r="F26" s="35" t="n"/>
-      <c r="G26" s="35" t="n"/>
-      <c r="H26" s="49" t="inlineStr">
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="44" t="n"/>
+      <c r="B32" s="44" t="n"/>
+      <c r="C32" s="44" t="n"/>
+      <c r="D32" s="44" t="n"/>
+      <c r="E32" s="44" t="n"/>
+      <c r="F32" s="44" t="n"/>
+      <c r="G32" s="44" t="n"/>
+      <c r="H32" s="54" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="I26" s="45" t="inlineStr">
+      <c r="I32" s="50" t="inlineStr">
         <is>
           <t>一作</t>
         </is>
       </c>
-      <c r="J26" s="45" t="inlineStr">
+      <c r="J32" s="50" t="inlineStr">
         <is>
           <t>香港大学博士（论文获 2026 ACM SIGKDD Dissertation Award Runner-Up）</t>
         </is>
       </c>
-      <c r="K26" s="45" t="inlineStr">
+      <c r="K32" s="50" t="inlineStr">
         <is>
           <t>主导 CLI-Anything；此前 UltraCUA、Aria-UI 等 computer-use 工作</t>
         </is>
       </c>
-      <c r="L26" s="45" t="inlineStr">
+      <c r="L32" s="50" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M26" s="45" t="inlineStr">
+      <c r="M32" s="50" t="inlineStr">
         <is>
           <t>itsyuhaoy@gmail.com
 yuhao-yang@outlook.com</t>
         </is>
       </c>
-      <c r="N26" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O26" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P26" s="45" t="inlineStr">
+      <c r="N32" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O32" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P32" s="50" t="inlineStr">
         <is>
           <t>个人站
 GitHub</t>
         </is>
       </c>
-      <c r="Q26" s="45" t="inlineStr">
+      <c r="Q32" s="50" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="64" customHeight="1">
-      <c r="A27" s="13" t="n"/>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="13" t="n"/>
-      <c r="H27" s="49" t="inlineStr">
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="13" t="n"/>
+      <c r="H33" s="54" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="I27" s="45" t="inlineStr">
+      <c r="I33" s="50" t="inlineStr">
         <is>
           <t>共同作者</t>
         </is>
       </c>
-      <c r="J27" s="45" t="inlineStr">
+      <c r="J33" s="50" t="inlineStr">
         <is>
           <t>浙江大学自动化本科（2020–2024）；香港大学计算机博士在读（2024–）</t>
         </is>
       </c>
-      <c r="K27" s="45" t="inlineStr">
+      <c r="K33" s="50" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2912,106 +3385,120 @@
           </r>
         </is>
       </c>
-      <c r="L27" s="45" t="inlineStr">
+      <c r="L33" s="50" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M27" s="45" t="inlineStr">
+      <c r="M33" s="50" t="inlineStr">
         <is>
           <t>tianyufan0504@gmail.com</t>
         </is>
       </c>
-      <c r="N27" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O27" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P27" s="45" t="inlineStr">
+      <c r="N33" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O33" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P33" s="50" t="inlineStr">
         <is>
           <t>个人站
 未在个人站显著标注主账号</t>
         </is>
       </c>
-      <c r="Q27" s="45" t="inlineStr">
+      <c r="Q33" s="50" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q27"/>
-  <mergeCells count="65">
-    <mergeCell ref="G23:G24"/>
+  <autoFilter ref="A3:Q33"/>
+  <mergeCells count="79">
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="D27:D28"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B18:B19"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="F16:F19"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E29:E30"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="G16:G19"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="F6:F7"/>
-    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="A16:A19"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="C25:C26"/>
     <mergeCell ref="E6:E7"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="F27:F28"/>
     <mergeCell ref="G4:G5"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="G12:G15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -3022,29 +3509,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId41"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -3188,10 +3685,10 @@
           </r>
         </is>
       </c>
-      <c r="E4" s="54" t="n">
+      <c r="E4" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="55" t="n">
+      <c r="F4" s="60" t="n">
         <v>5235</v>
       </c>
       <c r="G4" s="8" t="n">
@@ -3242,10 +3739,10 @@
           <t>开源编程智能体</t>
         </is>
       </c>
-      <c r="E5" s="56" t="n">
+      <c r="E5" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="55" t="n">
+      <c r="F5" s="60" t="n">
         <v>3965</v>
       </c>
       <c r="G5" s="8" t="n">
@@ -3296,10 +3793,10 @@
           <t>把代码库、文档、SQL、PDF 变成可查询知识图谱</t>
         </is>
       </c>
-      <c r="E6" s="56" t="n">
+      <c r="E6" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="55" t="n">
+      <c r="F6" s="60" t="n">
         <v>3643</v>
       </c>
       <c r="G6" s="8" t="n">
@@ -3353,7 +3850,7 @@
       <c r="E7" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="55" t="n">
+      <c r="F7" s="60" t="n">
         <v>1464</v>
       </c>
       <c r="G7" s="8" t="n">
@@ -3407,7 +3904,7 @@
       <c r="E8" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F8" s="55" t="n">
+      <c r="F8" s="60" t="n">
         <v>1333</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -3458,16 +3955,16 @@
           <t>Postgres 开发平台</t>
         </is>
       </c>
-      <c r="E9" s="57" t="n">
+      <c r="E9" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="58" t="n">
+      <c r="F9" s="29" t="n">
         <v>1197</v>
       </c>
-      <c r="G9" s="59" t="n">
+      <c r="G9" s="62" t="n">
         <v>693</v>
       </c>
-      <c r="H9" s="60" t="n">
+      <c r="H9" s="30" t="n">
         <v>113473</v>
       </c>
       <c r="I9" s="27" t="inlineStr">
@@ -3485,7 +3982,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="36" t="inlineStr">
+      <c r="L9" s="33" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -3494,7 +3991,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>🚀 jasna</t>
+          <t>🚀 php-src</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -3509,29 +4006,29 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>视频修复工具</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="55" t="n">
-        <v>613</v>
+          <t>总星 41,558，PHP 解释器源码</t>
+        </is>
+      </c>
+      <c r="E10" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="60" t="n">
+        <v>1003</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>498</v>
+        <v>716</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>2879</v>
+        <v>41558</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>10-19 #12 +115 → 10-20 #8 +498🚀</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
+          <t>10-23 #6 +287 → 10-24 #3 +716🚀</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>PHP 官方</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -3566,20 +4063,20 @@
           <t>面向开发者的社交网络，JetBrains 办公室 48 小时直播从零写出来的开源项目</t>
         </is>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="E11" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="29" t="inlineStr">
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="29" t="inlineStr">
+      <c r="G11" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="30" t="n">
+      <c r="H11" s="37" t="n">
         <v>401</v>
       </c>
       <c r="I11" s="27" t="inlineStr">
@@ -3597,7 +4094,7 @@
           <t>JetBrains 直播</t>
         </is>
       </c>
-      <c r="L11" s="36" t="inlineStr">
+      <c r="L11" s="33" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -3606,7 +4103,7 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Beam.win</t>
+          <t>Product Hunt Visual Launch Editor</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
@@ -3621,33 +4118,33 @@
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>在一台 Mac 上跑 AI 智能体，在另一台上直接用它的窗口</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="n">
+          <t>边做边预览你的 PH 发布页</t>
+        </is>
+      </c>
+      <c r="E12" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="37" t="inlineStr">
+      <c r="F12" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="37" t="inlineStr">
+      <c r="G12" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="38" t="n">
-        <v>293</v>
+      <c r="H12" s="41" t="n">
+        <v>350</v>
       </c>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>10-19 #1</t>
+          <t>10-23 #1</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
         <is>
-          <t>maker Hiten Shah、Sam Asante</t>
+          <t>Product Hunt 官方</t>
         </is>
       </c>
       <c r="K12" s="18" t="inlineStr">
@@ -3664,7 +4161,7 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>Inbox Zero</t>
+          <t>Beam.win</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
@@ -3679,41 +4176,41 @@
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>开源 AI 邮件助手兼客户端，对标 Superhuman</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="n">
+          <t>在一台 Mac 上跑 AI 智能体，在另一台上直接用它的窗口</t>
+        </is>
+      </c>
+      <c r="E13" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="29" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="29" t="inlineStr">
+      <c r="G13" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="30" t="n">
-        <v>279</v>
+      <c r="H13" s="37" t="n">
+        <v>293</v>
       </c>
       <c r="I13" s="27" t="inlineStr">
         <is>
-          <t>10-18 #1</t>
+          <t>10-19 #1</t>
         </is>
       </c>
       <c r="J13" s="31" t="inlineStr">
         <is>
-          <t>Elie Steinbock</t>
+          <t>maker Hiten Shah、Sam Asante</t>
         </is>
       </c>
       <c r="K13" s="27" t="inlineStr">
         <is>
-          <t>以色列特拉维夫</t>
-        </is>
-      </c>
-      <c r="L13" s="36" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="33" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -3722,7 +4219,7 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Composio Instant</t>
+          <t>Inbox Zero</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
@@ -3737,188 +4234,188 @@
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>给 AI 智能体接 1000+ 生产级工具，含托管鉴权与沙箱执行</t>
-        </is>
-      </c>
-      <c r="E14" s="61" t="n">
+          <t>开源 AI 邮件助手兼客户端，对标 Superhuman</t>
+        </is>
+      </c>
+      <c r="E14" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="41" t="n">
+        <v>279</v>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>10-18 #1</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Elie Steinbock</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>以色列特拉维夫</t>
+        </is>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t>🚀 ai-job-search</t>
+        </is>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="D15" s="50" t="inlineStr">
+        <is>
+          <t>本机运行的 AI 求职框架，基于 Claude Code 评岗位、改简历、写求职信、备面试</t>
+        </is>
+      </c>
+      <c r="E15" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="64" t="n">
+        <v>9949</v>
+      </c>
+      <c r="G15" s="65" t="n">
+        <v>3861</v>
+      </c>
+      <c r="H15" s="66" t="n">
+        <v>60514</v>
+      </c>
+      <c r="I15" s="50" t="inlineStr">
+        <is>
+          <t>10-18/19 #1 +2,232🚀 → 10-20 #1 +3,856🚀 → 10-21 #1 +3,861</t>
+        </is>
+      </c>
+      <c r="J15" s="54" t="inlineStr">
+        <is>
+          <t>Mads Lorentzen</t>
+        </is>
+      </c>
+      <c r="K15" s="50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="49" t="inlineStr">
+        <is>
+          <t>丹麦</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>VoiceStudio</t>
+        </is>
+      </c>
+      <c r="B16" s="49" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C16" s="49" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D16" s="50" t="inlineStr">
+        <is>
+          <t>完全本地的开源 ElevenLabs 替代品</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="37" t="inlineStr">
+      <c r="F16" s="57" t="n">
+        <v>2082</v>
+      </c>
+      <c r="G16" s="68" t="n">
+        <v>2082</v>
+      </c>
+      <c r="H16" s="58" t="n">
+        <v>75310</v>
+      </c>
+      <c r="I16" s="50" t="inlineStr">
+        <is>
+          <t>10-18/19 #2 +2,082</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K16" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="38" t="n">
-        <v>251</v>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>10-20 #2</t>
-        </is>
-      </c>
-      <c r="J14" s="22" t="inlineStr">
-        <is>
-          <t>Composio</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>常见公开资料</t>
-        </is>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>印度创始团队</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>🚀 ai-job-search</t>
-        </is>
-      </c>
-      <c r="B15" s="44" t="inlineStr">
+      <c r="L16" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t>ruflo</t>
+        </is>
+      </c>
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C15" s="44" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="D15" s="45" t="inlineStr">
-        <is>
-          <t>本机运行的 AI 求职框架，基于 Claude Code 评岗位、改简历、写求职信、备面试</t>
-        </is>
-      </c>
-      <c r="E15" s="62" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="63" t="n">
-        <v>9949</v>
-      </c>
-      <c r="G15" s="64" t="n">
-        <v>3861</v>
-      </c>
-      <c r="H15" s="65" t="n">
-        <v>60514</v>
-      </c>
-      <c r="I15" s="45" t="inlineStr">
-        <is>
-          <t>10-18/19 #1 +2,232🚀 → 10-20 #1 +3,856🚀 → 10-21 #1 +3,861</t>
-        </is>
-      </c>
-      <c r="J15" s="49" t="inlineStr">
-        <is>
-          <t>Mads Lorentzen</t>
-        </is>
-      </c>
-      <c r="K15" s="45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="44" t="inlineStr">
-        <is>
-          <t>丹麦</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
-        <is>
-          <t>VoiceStudio</t>
-        </is>
-      </c>
-      <c r="B16" s="44" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C16" s="44" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D16" s="45" t="inlineStr">
-        <is>
-          <t>完全本地的开源 ElevenLabs 替代品</t>
-        </is>
-      </c>
-      <c r="E16" s="66" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="52" t="n">
-        <v>2082</v>
-      </c>
-      <c r="G16" s="67" t="n">
-        <v>2082</v>
-      </c>
-      <c r="H16" s="53" t="n">
-        <v>75310</v>
-      </c>
-      <c r="I16" s="45" t="inlineStr">
-        <is>
-          <t>10-18/19 #2 +2,082</t>
-        </is>
-      </c>
-      <c r="J16" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K16" s="45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L16" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="43" t="inlineStr">
-        <is>
-          <t>ruflo</t>
-        </is>
-      </c>
-      <c r="B17" s="44" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C17" s="44" t="inlineStr">
+      <c r="C17" s="49" t="inlineStr">
         <is>
           <t>多智能体编排</t>
         </is>
       </c>
-      <c r="D17" s="45" t="inlineStr">
+      <c r="D17" s="50" t="inlineStr">
         <is>
           <t>多智能体蜂群编排框架</t>
         </is>
       </c>
-      <c r="E17" s="68" t="n">
+      <c r="E17" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="52" t="n">
         <v>1761</v>
       </c>
-      <c r="G17" s="69" t="n">
+      <c r="G17" s="70" t="n">
         <v>684</v>
       </c>
-      <c r="H17" s="48" t="n">
+      <c r="H17" s="53" t="n">
         <v>77830</v>
       </c>
-      <c r="I17" s="45" t="inlineStr">
+      <c r="I17" s="50" t="inlineStr">
         <is>
           <t>10-18/19 #7 +513 → 10-20 #7 +564 → 10-21 #9 +684</t>
         </is>
@@ -3928,7 +4425,7 @@
           <t>未查到</t>
         </is>
       </c>
-      <c r="K17" s="45" t="inlineStr">
+      <c r="K17" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3981,92 +4478,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>每周开源 / 产品 Sourcing 周报（2026-10-19 – 10-25）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="71" t="inlineStr">
-        <is>
-          <t>全球项目 14 个 · 华人项目 11 个 · 核心人物 24 位</t>
+      <c r="B2" s="72" t="inlineStr">
+        <is>
+          <t>全球项目 14 个 · 华人项目 15 个 · 核心人物 30 位</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="72" t="inlineStr">
+      <c r="B4" s="73" t="inlineStr">
         <is>
           <t>本周总览</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="73" t="inlineStr">
+      <c r="A5" s="74" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="74" t="inlineStr">
-        <is>
-          <t>本周进行中 · 已更新至 10-23（第 5/7 天），每天日报后自动刷新。</t>
+      <c r="B5" s="75" t="inlineStr">
+        <is>
+          <t>本周进行中 · 已更新至 10-24（第 6/7 天），每天日报后自动刷新。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="73" t="inlineStr">
+      <c r="A6" s="74" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="74" t="inlineStr">
-        <is>
-          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search；已收录全球项目 14 个、华人项目 11 个，今日新增华人项目：DeepCell、Meloong-Git/PCL、CutBay。</t>
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search；已收录全球项目 14 个、华人项目 15 个，今日新增华人项目：Renhuai123/ziwei-doushu、OpenBMB/VoxCPM、MOVO AI、Agent Hunt · Monid。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="73" t="inlineStr">
+      <c r="A7" s="74" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="75" t="inlineStr">
         <is>
           <t>标「✨ 今日新增」的为今天首次上榜；灰色为前 3 周周报已出现过的项目，排在最后。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="75" t="inlineStr">
+      <c r="B9" s="76" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>黄底：日榜第 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="77" t="inlineStr">
+      <c r="B11" s="78" t="inlineStr">
         <is>
           <t>橙色：🚀 单日星增速明显放大（华人项目为 ≥ 前一天 1.5 倍）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="78" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>灰色斜体：未查到</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="79" t="inlineStr">
+      <c r="B14" s="80" t="inlineStr">
         <is>
           <t>网页版：https://psylch.github.io/rising-projects/2026-10-25/</t>
         </is>
@@ -4087,7 +4584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4159,7 +4656,7 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E4" s="40" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/yolandyan</t>
         </is>
@@ -4213,7 +4710,7 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E6" s="40" t="inlineStr">
+      <c r="E6" s="43" t="inlineStr">
         <is>
           <t>https://github.com/yoland68</t>
         </is>
@@ -4267,7 +4764,7 @@
           <t>来源4</t>
         </is>
       </c>
-      <c r="E8" s="40" t="inlineStr">
+      <c r="E8" s="43" t="inlineStr">
         <is>
           <t>https://research.crustdata.com/company/comfyui</t>
         </is>
@@ -4321,7 +4818,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="E10" s="43" t="inlineStr">
         <is>
           <t>https://x.com/robinjhuang</t>
         </is>
@@ -4375,7 +4872,7 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="E12" s="43" t="inlineStr">
         <is>
           <t>https://www.getprog.ai/profile/5674242</t>
         </is>
@@ -4429,7 +4926,7 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E14" s="40" t="inlineStr">
+      <c r="E14" s="43" t="inlineStr">
         <is>
           <t>https://github.com/shiyu-coder</t>
         </is>
@@ -4483,7 +4980,7 @@
           <t>来源1</t>
         </is>
       </c>
-      <c r="E16" s="40" t="inlineStr">
+      <c r="E16" s="43" t="inlineStr">
         <is>
           <t>https://arxiv.org/html/2508.02739</t>
         </is>
@@ -4492,12 +4989,12 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Meloong-Git/PCL</t>
+          <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>龙腾猫跃（LTCatt / LTCat）</t>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
       <c r="C17" s="26" t="inlineStr">
@@ -4507,24 +5004,24 @@
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>bilibili</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E17" s="34" t="inlineStr">
         <is>
-          <t>https://space.bilibili.com/11343203/dynamic</t>
+          <t>https://x.com/wdy188</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>Meloong-Git/PCL</t>
+          <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>龙腾猫跃（LTCatt / LTCat）</t>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -4534,51 +5031,51 @@
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>afdian</t>
-        </is>
-      </c>
-      <c r="E18" s="40" t="inlineStr">
-        <is>
-          <t>https://meloong.com/afd/a/LTCat</t>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E18" s="43" t="inlineStr">
+        <is>
+          <t>https://github.com/Renhuai123</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>Meloong-Git/PCL</t>
+          <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>龙腾猫跃（LTCatt / LTCat）</t>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
         <is>
-          <t>个人站</t>
+          <t>来源2</t>
         </is>
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>https://meloong.com/PCL</t>
+          <t>https://github.com/Renhuai123/ziwei-doushu</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>Meloong-Git/PCL</t>
+          <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>龙腾猫跃（LTCatt / LTCat）</t>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -4588,24 +5085,24 @@
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E20" s="40" t="inlineStr">
-        <is>
-          <t>https://github.com/Meloong-Git/PCL</t>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E20" s="43" t="inlineStr">
+        <is>
+          <t>https://metisziwei.com/privacy</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>Meloong-Git/PCL</t>
+          <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>龙腾猫跃（LTCatt / LTCat）</t>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
@@ -4615,105 +5112,105 @@
       </c>
       <c r="D21" s="27" t="inlineStr">
         <is>
-          <t>来源2</t>
+          <t>来源4</t>
         </is>
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>https://github.com/Meloong-Git</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+          <t>https://zamantika.com/profile/wdy188</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>Meloong-Git/PCL</t>
+          <t>OpenBMB/VoxCPM</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>龙腾猫跃（LTCatt / LTCat）</t>
+          <t>周逸轩（Yixuan Zhou）</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>其他联系</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E22" s="40" t="inlineStr">
-        <is>
-          <t>https://pcl2.aoe.top/</t>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E22" s="43" t="inlineStr">
+        <is>
+          <t>https://github.com/Labmem-Zhouyx</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>DeepCell</t>
+          <t>OpenBMB/VoxCPM</t>
         </is>
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>梦琪（Mengqi）</t>
+          <t>周逸轩（Yixuan Zhou）</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>其他联系</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Google Scholar</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/deepcell-ai</t>
+          <t>https://scholar.google.com/citations?user=ZI_Cm1cAAAAJ</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>DeepCell</t>
+          <t>OpenBMB/VoxCPM</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>梦琪（Mengqi）</t>
+          <t>周逸轩（Yixuan Zhou）</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E24" s="40" t="inlineStr">
-        <is>
-          <t>https://deepcell.net</t>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E24" s="43" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/papers/2606.06928</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t>DeepCell</t>
+          <t>OpenBMB/VoxCPM</t>
         </is>
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>梦琪（Mengqi）</t>
+          <t>周逸轩（Yixuan Zhou）</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
@@ -4723,402 +5220,402 @@
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>https://openbmb.cn/docs/en/assets/files/VFeCbeqLKorYJsxmiW6cuwqynsf-6a3e0cb9a7ff0e27f8605a45a1e118c7.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>OpenBMB/VoxCPM</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>ZGY（GitHub a710128，全名未查到）</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E26" s="43" t="inlineStr">
+        <is>
+          <t>https://github.com/a710128</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>Meloong-Git/PCL</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>bilibili</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t>https://space.bilibili.com/11343203/dynamic</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Meloong-Git/PCL</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>afdian</t>
+        </is>
+      </c>
+      <c r="E28" s="43" t="inlineStr">
+        <is>
+          <t>https://meloong.com/afd/a/LTCat</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>Meloong-Git/PCL</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="inlineStr">
+        <is>
+          <t>https://meloong.com/PCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Meloong-Git/PCL</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E25" s="34" t="inlineStr">
-        <is>
-          <t>https://cn.ceibs.edu.cn/mba/student-life/27019</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>DeepCell</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>梦琪（Mengqi）</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="E30" s="43" t="inlineStr">
+        <is>
+          <t>https://github.com/Meloong-Git/PCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>Meloong-Git/PCL</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E26" s="40" t="inlineStr">
-        <is>
-          <t>https://www.ceibs.edu/mba/student-life/27022</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>DeepCell</t>
-        </is>
-      </c>
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>梦琪（Mengqi）</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="E31" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/Meloong-Git</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Meloong-Git/PCL</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>龙腾猫跃（LTCatt / LTCat）</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E32" s="43" t="inlineStr">
+        <is>
+          <t>https://pcl2.aoe.top/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>MOVO AI</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>陈麒聪（Edward Chen）</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E33" s="34" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/edward-chen-b682b090</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>MOVO AI</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>陈麒聪（Edward Chen）</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E34" s="43" t="inlineStr">
+        <is>
+          <t>https://www.rcrai.com/about-us/news/cover/data_138.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>MOVO AI</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>陈麒聪（Edward Chen）</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>https://recordowl.com/company/speakly-ai-pte-ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>MOVO AI</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>陈麒聪（Edward Chen）</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E27" s="34" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/deepcell</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>DeepCell</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="E36" s="43" t="inlineStr">
+        <is>
+          <t>https://www.crunchbase.com/organization/speakly-ai-cac1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>MOVO AI</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>陈麒聪（Edward Chen）</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E28" s="40" t="inlineStr">
-        <is>
-          <t>https://cn.ceibs.edu.cn/mba/student-life/27019</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
-        <is>
-          <t>DeepCell</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E29" s="34" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/deepcell</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="22" t="inlineStr">
-        <is>
-          <t>DeepCell</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>Amy Wang</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E30" s="40" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/xinyuan4</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="31" t="inlineStr">
-        <is>
-          <t>DeepCell</t>
-        </is>
-      </c>
-      <c r="B31" s="27" t="inlineStr">
-        <is>
-          <t>Amy Wang</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D31" s="27" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E31" s="34" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/deepcell-ai</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>DeepCell</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>Amy Wang</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E32" s="40" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/deepcell</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>UseIt Studio</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="inlineStr">
-        <is>
-          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D33" s="27" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E33" s="34" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/daniel-gao-342504253</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>UseIt Studio</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>Google Scholar</t>
-        </is>
-      </c>
-      <c r="E34" s="40" t="inlineStr">
-        <is>
-          <t>https://scholar.google.com/citations?hl=en&amp;user=No9OsocAAAAJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="31" t="inlineStr">
-        <is>
-          <t>UseIt Studio</t>
-        </is>
-      </c>
-      <c r="B35" s="27" t="inlineStr">
-        <is>
-          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D35" s="27" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E35" s="34" t="inlineStr">
-        <is>
-          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
-        <is>
-          <t>UseIt Studio</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E36" s="40" t="inlineStr">
-        <is>
-          <t>https://www.alphaxiv.org/@difei-gao</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="31" t="inlineStr">
-        <is>
-          <t>UseIt Studio</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="inlineStr">
-        <is>
-          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
       <c r="D37" s="27" t="inlineStr">
         <is>
-          <t>来源4</t>
+          <t>来源5</t>
         </is>
       </c>
       <c r="E37" s="34" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content/CVPR2024/html/Gao_AssistGUI_Task-Oriented_PC_Graphical_User_Interface_Automation_CVPR_2024_paper.html</t>
+          <t>https://www.producthunt.com/products/movo-ai</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>UseIt Studio</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>陈芷恒（Lindia Chen）</t>
+          <t>梦琪（Mengqi）</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D38" s="18" t="inlineStr">
         <is>
-          <t>producthunt</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/@lindiac</t>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E38" s="43" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/deepcell-ai</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="31" t="inlineStr">
         <is>
-          <t>UseIt Studio</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>陈芷恒（Lindia Chen）</t>
+          <t>梦琪（Mengqi）</t>
         </is>
       </c>
       <c r="C39" s="26" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>其他联系</t>
         </is>
       </c>
       <c r="D39" s="27" t="inlineStr">
         <is>
-          <t>来源1</t>
+          <t>个人站</t>
         </is>
       </c>
       <c r="E39" s="34" t="inlineStr">
         <is>
-          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+          <t>https://deepcell.net</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>UseIt Studio</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>陈芷恒（Lindia Chen）</t>
+          <t>梦琪（Mengqi）</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
@@ -5128,24 +5625,24 @@
       </c>
       <c r="D40" s="18" t="inlineStr">
         <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E40" s="40" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/useit-studio-from-idea-to-delivery</t>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E40" s="43" t="inlineStr">
+        <is>
+          <t>https://cn.ceibs.edu.cn/mba/student-life/27019</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="31" t="inlineStr">
         <is>
-          <t>UseIt Studio</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>丁云培</t>
+          <t>梦琪（Mengqi）</t>
         </is>
       </c>
       <c r="C41" s="26" t="inlineStr">
@@ -5155,24 +5652,24 @@
       </c>
       <c r="D41" s="27" t="inlineStr">
         <is>
-          <t>来源1</t>
+          <t>来源2</t>
         </is>
       </c>
       <c r="E41" s="34" t="inlineStr">
         <is>
-          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+          <t>https://www.ceibs.edu/mba/student-life/27022</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>UseIt Studio</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>刘佳琦</t>
+          <t>梦琪（Mengqi）</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
@@ -5182,51 +5679,51 @@
       </c>
       <c r="D42" s="18" t="inlineStr">
         <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E42" s="40" t="inlineStr">
-        <is>
-          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E42" s="43" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/deepcell</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="31" t="inlineStr">
         <is>
-          <t>Wally by Willow</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Allan Guo</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>来源1</t>
         </is>
       </c>
       <c r="E43" s="34" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/allan-guo</t>
+          <t>https://cn.ceibs.edu.cn/mba/student-life/27019</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>Wally by Willow</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Allan Guo</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
@@ -5236,78 +5733,78 @@
       </c>
       <c r="D44" s="18" t="inlineStr">
         <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E44" s="40" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/companies/willow</t>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E44" s="43" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/deepcell</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="31" t="inlineStr">
         <is>
-          <t>Wally by Willow</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>Allan Guo</t>
+          <t>Amy Wang</t>
         </is>
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
         <is>
-          <t>来源2</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E45" s="34" t="inlineStr">
         <is>
-          <t>https://profiles.stanford.edu/allan-guo</t>
+          <t>https://linkedin.com/in/xinyuan4</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>Wally by Willow</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Lawrence Liu</t>
+          <t>Amy Wang</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D46" s="18" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E46" s="40" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/lawrenceliuu</t>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E46" s="43" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/deepcell-ai</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="31" t="inlineStr">
         <is>
-          <t>Wally by Willow</t>
+          <t>DeepCell</t>
         </is>
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Lawrence Liu</t>
+          <t>Amy Wang</t>
         </is>
       </c>
       <c r="C47" s="26" t="inlineStr">
@@ -5317,24 +5814,24 @@
       </c>
       <c r="D47" s="27" t="inlineStr">
         <is>
-          <t>来源2</t>
+          <t>来源3</t>
         </is>
       </c>
       <c r="E47" s="34" t="inlineStr">
         <is>
-          <t>https://www.stackforce.co/talent/lawrence-liu-ceo-69d744662a55b09f46c5deaa</t>
+          <t>https://www.producthunt.com/products/deepcell</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>Mintlify Autopilot</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>Han Wang（王，生于河南新乡）</t>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
@@ -5347,21 +5844,21 @@
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E48" s="40" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/handotdev</t>
+      <c r="E48" s="43" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/daniel-gao-342504253</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="31" t="inlineStr">
         <is>
-          <t>Mintlify Autopilot</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>Han Wang（王，生于河南新乡）</t>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
         </is>
       </c>
       <c r="C49" s="26" t="inlineStr">
@@ -5371,51 +5868,51 @@
       </c>
       <c r="D49" s="27" t="inlineStr">
         <is>
-          <t>个人站</t>
+          <t>Google Scholar</t>
         </is>
       </c>
       <c r="E49" s="34" t="inlineStr">
         <is>
-          <t>https://han.dev/</t>
+          <t>https://scholar.google.com/citations?hl=en&amp;user=No9OsocAAAAJ</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>Mintlify Autopilot</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>Han Wang（王，生于河南新乡）</t>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E50" s="40" t="inlineStr">
-        <is>
-          <t>https://x.com/handotdev</t>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E50" s="43" t="inlineStr">
+        <is>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="31" t="inlineStr">
         <is>
-          <t>Mintlify Autopilot</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>Han Wang（王，生于河南新乡）</t>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
         </is>
       </c>
       <c r="C51" s="26" t="inlineStr">
@@ -5425,24 +5922,24 @@
       </c>
       <c r="D51" s="27" t="inlineStr">
         <is>
-          <t>来源2</t>
+          <t>来源3</t>
         </is>
       </c>
       <c r="E51" s="34" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
+          <t>https://www.alphaxiv.org/@difei-gao</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>Mintlify Autopilot</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>Han Wang（王，生于河南新乡）</t>
+          <t>郜迪飞（Difei Gao / Daniel Gao）</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
@@ -5452,78 +5949,78 @@
       </c>
       <c r="D52" s="18" t="inlineStr">
         <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E52" s="40" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/posts/handotdev_my-grandparents-in-rural-china-use-ai-more-activity-7430270997586489346-XzLv</t>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E52" s="43" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2024/html/Gao_AssistGUI_Task-Oriented_PC_Graphical_User_Interface_Automation_CVPR_2024_paper.html</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="31" t="inlineStr">
         <is>
-          <t>Mintlify Autopilot</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>Hahnbee Lee</t>
+          <t>陈芷恒（Lindia Chen）</t>
         </is>
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D53" s="27" t="inlineStr">
+        <is>
+          <t>producthunt</t>
+        </is>
+      </c>
+      <c r="E53" s="34" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/@lindiac</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>陈芷恒（Lindia Chen）</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D53" s="27" t="inlineStr">
+      <c r="D54" s="18" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E53" s="34" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="22" t="inlineStr">
-        <is>
-          <t>CutBay</t>
-        </is>
-      </c>
-      <c r="B54" s="18" t="inlineStr">
-        <is>
-          <t>林霄（David Lin / Lin Xiao）</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E54" s="40" t="inlineStr">
-        <is>
-          <t>https://www.cutbay.ai</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="36" customHeight="1">
+      <c r="E54" s="43" t="inlineStr">
+        <is>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
       <c r="A55" s="31" t="inlineStr">
         <is>
-          <t>CutBay</t>
+          <t>UseIt Studio</t>
         </is>
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>林霄（David Lin / Lin Xiao）</t>
+          <t>陈芷恒（Lindia Chen）</t>
         </is>
       </c>
       <c r="C55" s="26" t="inlineStr">
@@ -5533,213 +6030,213 @@
       </c>
       <c r="D55" s="27" t="inlineStr">
         <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E55" s="34" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/useit-studio-from-idea-to-delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>丁云培</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E55" s="34" t="inlineStr">
-        <is>
-          <t>https://www.prnewswire.com/news-releases/introducing-cutbay-the-ai-video-agent-transforming-video-creation-with-chat-based-workflows-302908185.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="22" t="inlineStr">
-        <is>
-          <t>CutBay</t>
-        </is>
-      </c>
-      <c r="B56" s="18" t="inlineStr">
-        <is>
-          <t>林霄（David Lin / Lin Xiao）</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
+      <c r="E56" s="43" t="inlineStr">
+        <is>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t>UseIt Studio</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>刘佳琦</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D56" s="18" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E56" s="40" t="inlineStr">
-        <is>
-          <t>https://www.cutbay.ai/about</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="36" customHeight="1">
-      <c r="A57" s="31" t="inlineStr">
-        <is>
-          <t>CutBay</t>
-        </is>
-      </c>
-      <c r="B57" s="27" t="inlineStr">
-        <is>
-          <t>林霄（David Lin / Lin Xiao）</t>
-        </is>
-      </c>
-      <c r="C57" s="26" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
       <c r="D57" s="27" t="inlineStr">
         <is>
-          <t>来源3</t>
+          <t>来源1</t>
         </is>
       </c>
       <c r="E57" s="34" t="inlineStr">
         <is>
-          <t>https://kr-asia.com/developing-easy-to-use-software-for-video-editing-inside-chinas-startups</t>
+          <t>https://mplus-gallery.nimbus-nimo.com/project/2026S-032</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>Asimov 1</t>
+          <t>Wally by Willow</t>
         </is>
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>Daniel Ong</t>
+          <t>Allan Guo</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D58" s="18" t="inlineStr">
         <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E58" s="40" t="inlineStr">
-        <is>
-          <t>https://daniel.ai/</t>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E58" s="43" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/allan-guo</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="31" t="inlineStr">
         <is>
-          <t>Asimov 1</t>
+          <t>Wally by Willow</t>
         </is>
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>Daniel Ong</t>
+          <t>Allan Guo</t>
         </is>
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>来源1</t>
         </is>
       </c>
       <c r="E59" s="34" t="inlineStr">
         <is>
-          <t>https://github.com/dan-menlo</t>
+          <t>https://www.ycombinator.com/companies/willow</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>Asimov 1</t>
+          <t>Wally by Willow</t>
         </is>
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>Nicole Zhu</t>
+          <t>Allan Guo</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E60" s="40" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/nicolezhu</t>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E60" s="43" t="inlineStr">
+        <is>
+          <t>https://profiles.stanford.edu/allan-guo</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="31" t="inlineStr">
         <is>
-          <t>Asimov 1</t>
+          <t>Wally by Willow</t>
         </is>
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>Nicole Zhu</t>
+          <t>Lawrence Liu</t>
         </is>
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E61" s="34" t="inlineStr">
         <is>
-          <t>https://x.com/freelerobot</t>
+          <t>https://linkedin.com/in/lawrenceliuu</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="22" t="inlineStr">
         <is>
-          <t>Asimov 1</t>
+          <t>Wally by Willow</t>
         </is>
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>Nicole Zhu</t>
+          <t>Lawrence Liu</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D62" s="18" t="inlineStr">
         <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E62" s="40" t="inlineStr">
-        <is>
-          <t>https://nicole.ai/</t>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E62" s="43" t="inlineStr">
+        <is>
+          <t>https://www.stackforce.co/talent/lawrence-liu-ceo-69d744662a55b09f46c5deaa</t>
         </is>
       </c>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>Mintlify Autopilot</t>
         </is>
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>Jinjing Liang（中文名未查到）</t>
+          <t>Han Wang（王，生于河南新乡）</t>
         </is>
       </c>
       <c r="C63" s="26" t="inlineStr">
@@ -5754,19 +6251,19 @@
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/jinjingliang</t>
+          <t>https://linkedin.com/in/handotdev</t>
         </is>
       </c>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="22" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>Mintlify Autopilot</t>
         </is>
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>Jinjing Liang（中文名未查到）</t>
+          <t>Han Wang（王，生于河南新乡）</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
@@ -5776,24 +6273,24 @@
       </c>
       <c r="D64" s="18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E64" s="40" t="inlineStr">
-        <is>
-          <t>https://x.com/JinjingLiang</t>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E64" s="43" t="inlineStr">
+        <is>
+          <t>https://han.dev/</t>
         </is>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>Mintlify Autopilot</t>
         </is>
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>Jinjing Liang（中文名未查到）</t>
+          <t>Han Wang（王，生于河南新乡）</t>
         </is>
       </c>
       <c r="C65" s="26" t="inlineStr">
@@ -5803,24 +6300,24 @@
       </c>
       <c r="D65" s="27" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>https://github.com/AmethystLiang</t>
+          <t>https://x.com/handotdev</t>
         </is>
       </c>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>Mintlify Autopilot</t>
         </is>
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>Jinjing Liang（中文名未查到）</t>
+          <t>Han Wang（王，生于河南新乡）</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
@@ -5830,105 +6327,105 @@
       </c>
       <c r="D66" s="18" t="inlineStr">
         <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E66" s="40" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E66" s="43" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1">
       <c r="A67" s="31" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>Mintlify Autopilot</t>
         </is>
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>Neil Parker</t>
+          <t>Han Wang（王，生于河南新乡）</t>
         </is>
       </c>
       <c r="C67" s="26" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>来源3</t>
         </is>
       </c>
       <c r="E67" s="34" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/neilwilliamparker</t>
+          <t>https://www.linkedin.com/posts/handotdev_my-grandparents-in-rural-china-use-ai-more-activity-7430270997586489346-XzLv</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>Mintlify Autopilot</t>
         </is>
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>Neil Parker</t>
+          <t>Hahnbee Lee</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E68" s="43" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2024/09/05/mintlify-is-building-a-next-gen-platform-for-writing-software-docs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>CutBay</t>
+        </is>
+      </c>
+      <c r="B69" s="27" t="inlineStr">
+        <is>
+          <t>林霄（David Lin / Lin Xiao）</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="inlineStr">
+        <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D68" s="18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E68" s="40" t="inlineStr">
-        <is>
-          <t>https://x.com/nwparker_</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
-      <c r="B69" s="27" t="inlineStr">
-        <is>
-          <t>Neil Parker</t>
-        </is>
-      </c>
-      <c r="C69" s="26" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
       <c r="D69" s="27" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>个人站</t>
         </is>
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>https://github.com/nwparker</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1">
+          <t>https://www.cutbay.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="36" customHeight="1">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>CutBay</t>
         </is>
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>Neil Parker</t>
+          <t>林霄（David Lin / Lin Xiao）</t>
         </is>
       </c>
       <c r="C70" s="17" t="inlineStr">
@@ -5941,284 +6438,878 @@
           <t>来源1</t>
         </is>
       </c>
-      <c r="E70" s="40" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="22" customHeight="1">
+      <c r="E70" s="43" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/introducing-cutbay-the-ai-video-agent-transforming-video-creation-with-chat-based-workflows-302908185.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="36" customHeight="1">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HKUDS/CLI-Anything</t>
+          <t>CutBay</t>
         </is>
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>Huang Chao（黄超）</t>
+          <t>林霄（David Lin / Lin Xiao）</t>
         </is>
       </c>
       <c r="C71" s="26" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
         <is>
-          <t>个人站</t>
+          <t>来源2</t>
         </is>
       </c>
       <c r="E71" s="34" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/chaoh</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
+          <t>https://www.cutbay.ai/about</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="36" customHeight="1">
       <c r="A72" s="22" t="inlineStr">
         <is>
-          <t>HKUDS/CLI-Anything</t>
+          <t>CutBay</t>
         </is>
       </c>
       <c r="B72" s="18" t="inlineStr">
         <is>
-          <t>Huang Chao（黄超）</t>
+          <t>林霄（David Lin / Lin Xiao）</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D72" s="18" t="inlineStr">
         <is>
-          <t>GitHub 组织</t>
-        </is>
-      </c>
-      <c r="E72" s="40" t="inlineStr">
-        <is>
-          <t>https://github.com/HKUDS</t>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E72" s="43" t="inlineStr">
+        <is>
+          <t>https://kr-asia.com/developing-easy-to-use-software-for-video-editing-inside-chinas-startups</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HKUDS/CLI-Anything</t>
+          <t>Asimov 1</t>
         </is>
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>Huang Chao（黄超）</t>
+          <t>Daniel Ong</t>
         </is>
       </c>
       <c r="C73" s="26" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>其他联系</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
         <is>
-          <t>来源1</t>
+          <t>个人站</t>
         </is>
       </c>
       <c r="E73" s="34" t="inlineStr">
         <is>
-          <t>https://datascience.hku.hk/people/chao-huang/</t>
+          <t>https://daniel.ai/</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="22" t="inlineStr">
         <is>
-          <t>HKUDS/CLI-Anything</t>
+          <t>Asimov 1</t>
         </is>
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>Huang Chao（黄超）</t>
+          <t>Daniel Ong</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>其他联系</t>
         </is>
       </c>
       <c r="D74" s="18" t="inlineStr">
         <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E74" s="40" t="inlineStr">
-        <is>
-          <t>https://www.ai.hku.hk/people/academic-staff/chuang</t>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E74" s="43" t="inlineStr">
+        <is>
+          <t>https://github.com/dan-menlo</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="31" t="inlineStr">
         <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B75" s="27" t="inlineStr">
+        <is>
+          <t>Nicole Zhu</t>
+        </is>
+      </c>
+      <c r="C75" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D75" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E75" s="34" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/nicolezhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>Nicole Zhu</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E76" s="43" t="inlineStr">
+        <is>
+          <t>https://x.com/freelerobot</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Asimov 1</t>
+        </is>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>Nicole Zhu</t>
+        </is>
+      </c>
+      <c r="C77" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D77" s="27" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E77" s="34" t="inlineStr">
+        <is>
+          <t>https://nicole.ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="22" t="inlineStr">
+        <is>
+          <t>Agent Hunt · Monid</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>Shengkun Ye</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E78" s="43" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/shengkun-ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>Agent Hunt · Monid</t>
+        </is>
+      </c>
+      <c r="B79" s="27" t="inlineStr">
+        <is>
+          <t>Shengkun Ye</t>
+        </is>
+      </c>
+      <c r="C79" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D79" s="27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E79" s="34" t="inlineStr">
+        <is>
+          <t>https://x.com/shengkunye</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="22" t="inlineStr">
+        <is>
+          <t>Agent Hunt · Monid</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>Shengkun Ye</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E80" s="43" t="inlineStr">
+        <is>
+          <t>https://www.crunchbase.com/person/shengkun-ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Agent Hunt · Monid</t>
+        </is>
+      </c>
+      <c r="B81" s="27" t="inlineStr">
+        <is>
+          <t>Shengkun Ye</t>
+        </is>
+      </c>
+      <c r="C81" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D81" s="27" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E81" s="34" t="inlineStr">
+        <is>
+          <t>https://f.inc/portfolio/monid/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t>Agent Hunt · Monid</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>Feiyou Guo</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E82" s="43" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/feiyouguo</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
+          <t>Agent Hunt · Monid</t>
+        </is>
+      </c>
+      <c r="B83" s="27" t="inlineStr">
+        <is>
+          <t>Feiyou Guo</t>
+        </is>
+      </c>
+      <c r="C83" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D83" s="27" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E83" s="34" t="inlineStr">
+        <is>
+          <t>https://www.crunchbase.com/person/feiyou-guo</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>Agent Hunt · Monid</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>Feiyou Guo</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E84" s="43" t="inlineStr">
+        <is>
+          <t>https://f.inc/portfolio/monid/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="31" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B85" s="27" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C85" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D85" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E85" s="34" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/jinjingliang</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E86" s="43" t="inlineStr">
+        <is>
+          <t>https://x.com/JinjingLiang</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="31" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B87" s="27" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C87" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D87" s="27" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E87" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/AmethystLiang</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E88" s="43" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="31" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B89" s="27" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C89" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D89" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E89" s="34" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/neilwilliamparker</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E90" s="43" t="inlineStr">
+        <is>
+          <t>https://x.com/nwparker_</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="31" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C91" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D91" s="27" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E91" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/nwparker</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>stablyai/orca</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>Neil Parker</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D92" s="18" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E92" s="43" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="31" t="inlineStr">
+        <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B75" s="27" t="inlineStr">
+      <c r="B93" s="27" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="C75" s="26" t="inlineStr">
+      <c r="C93" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D93" s="27" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E93" s="34" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/chaoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D94" s="18" t="inlineStr">
+        <is>
+          <t>GitHub 组织</t>
+        </is>
+      </c>
+      <c r="E94" s="43" t="inlineStr">
+        <is>
+          <t>https://github.com/HKUDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="31" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C95" s="26" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D75" s="27" t="inlineStr">
+      <c r="D95" s="27" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E95" s="34" t="inlineStr">
+        <is>
+          <t>https://datascience.hku.hk/people/chao-huang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D96" s="18" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E96" s="43" t="inlineStr">
+        <is>
+          <t>https://www.ai.hku.hk/people/academic-staff/chuang</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="31" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B97" s="27" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C97" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D97" s="27" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E75" s="34" t="inlineStr">
+      <c r="E97" s="34" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="36" customHeight="1">
-      <c r="A76" s="22" t="inlineStr">
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B76" s="18" t="inlineStr">
+      <c r="B98" s="18" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C76" s="17" t="inlineStr">
+      <c r="C98" s="17" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D76" s="18" t="inlineStr">
+      <c r="D98" s="18" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E76" s="40" t="inlineStr">
+      <c r="E98" s="43" t="inlineStr">
         <is>
           <t>https://yuh-yang.github.io</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="36" customHeight="1">
-      <c r="A77" s="31" t="inlineStr">
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="31" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B77" s="27" t="inlineStr">
+      <c r="B99" s="27" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C77" s="26" t="inlineStr">
+      <c r="C99" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D77" s="27" t="inlineStr">
+      <c r="D99" s="27" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E77" s="34" t="inlineStr">
+      <c r="E99" s="34" t="inlineStr">
         <is>
           <t>https://github.com/yuh-yang</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="36" customHeight="1">
-      <c r="A78" s="22" t="inlineStr">
+    <row r="100" ht="36" customHeight="1">
+      <c r="A100" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B78" s="18" t="inlineStr">
+      <c r="B100" s="18" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C78" s="17" t="inlineStr">
+      <c r="C100" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D78" s="18" t="inlineStr">
+      <c r="D100" s="18" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E78" s="40" t="inlineStr">
+      <c r="E100" s="43" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="36" customHeight="1">
-      <c r="A79" s="31" t="inlineStr">
+    <row r="101" ht="36" customHeight="1">
+      <c r="A101" s="31" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B79" s="27" t="inlineStr">
+      <c r="B101" s="27" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="C79" s="26" t="inlineStr">
+      <c r="C101" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D79" s="27" t="inlineStr">
+      <c r="D101" s="27" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E79" s="34" t="inlineStr">
+      <c r="E101" s="34" t="inlineStr">
         <is>
           <t>https://tianyufan0504.github.io/</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="36" customHeight="1">
-      <c r="A80" s="22" t="inlineStr">
+    <row r="102" ht="36" customHeight="1">
+      <c r="A102" s="22" t="inlineStr">
         <is>
           <t>HKUDS/CLI-Anything</t>
         </is>
       </c>
-      <c r="B80" s="18" t="inlineStr">
+      <c r="B102" s="18" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="C80" s="17" t="inlineStr">
+      <c r="C102" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D80" s="18" t="inlineStr">
+      <c r="D102" s="18" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E80" s="40" t="inlineStr">
+      <c r="E102" s="43" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E80"/>
+  <autoFilter ref="A3:E102"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -6301,6 +7392,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId99"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/2026-10-25/weekly-2026-10-25.xlsx
+++ b/2026-10-25/weekly-2026-10-25.xlsx
@@ -13,15 +13,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'华人项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全球项目'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$106</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'链接'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$102</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -364,6 +364,9 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -373,13 +376,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -388,13 +391,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -421,14 +424,8 @@
     <xf numFmtId="166" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -812,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2951,18 +2948,105 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="64" customHeight="1">
-      <c r="A29" s="48" t="inlineStr">
+    <row r="29" ht="78" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>zCAD AI（子虔科技 Zixel）</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>文字/图片生成可编辑参数化 CAD 零件与装配体，浏览器内编辑，导出 STEP；子虔科技 2020 年成立于上海，2026-01 浩辰软件 6000 万元入股 8.45%</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="31" t="inlineStr">
+        <is>
+          <t>龚敏彦（Gong Minyan）</t>
+        </is>
+      </c>
+      <c r="I29" s="27" t="inlineStr">
+        <is>
+          <t>子虔科技创始人兼 CEO、法定代表人</t>
+        </is>
+      </c>
+      <c r="J29" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K29" s="27" t="inlineStr">
+        <is>
+          <t>85 后，多年耕耘工业软件；2020 年创立子虔科技（云原生 3D CAD，客户含中国商飞、上汽、华为等）</t>
+        </is>
+      </c>
+      <c r="L29" s="27" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="M29" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N29" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O29" s="33" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P29" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q29" s="27" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3、来源4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="49" t="inlineStr">
         <is>
           <t>orca</t>
         </is>
       </c>
-      <c r="B29" s="49" t="inlineStr">
+      <c r="B30" s="50" t="inlineStr">
         <is>
           <t>编程智能体</t>
         </is>
       </c>
-      <c r="C29" s="50" t="inlineStr">
+      <c r="C30" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2983,36 +3067,36 @@
           </r>
         </is>
       </c>
-      <c r="D29" s="51" t="n">
+      <c r="D30" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="52" t="n">
+      <c r="E30" s="53" t="n">
         <v>5842</v>
       </c>
-      <c r="F29" s="53" t="n">
+      <c r="F30" s="54" t="n">
         <v>101219</v>
       </c>
-      <c r="G29" s="50" t="inlineStr">
+      <c r="G30" s="51" t="inlineStr">
         <is>
           <t>10-18/19 #5 +1,146 → 10-20 #2 +1,590 → 10-21 #3 +1,565 → 10-22 #3 +1,541</t>
         </is>
       </c>
-      <c r="H29" s="54" t="inlineStr">
+      <c r="H30" s="55" t="inlineStr">
         <is>
           <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
-      <c r="I29" s="50" t="inlineStr">
+      <c r="I30" s="51" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO，Orca 维护者</t>
         </is>
       </c>
-      <c r="J29" s="50" t="inlineStr">
+      <c r="J30" s="51" t="inlineStr">
         <is>
           <t>康奈尔大学校友（专业与学位未查到）</t>
         </is>
       </c>
-      <c r="K29" s="50" t="inlineStr">
+      <c r="K30" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3041,62 +3125,62 @@
           </r>
         </is>
       </c>
-      <c r="L29" s="50" t="inlineStr">
+      <c r="L30" s="51" t="inlineStr">
         <is>
           <t>美国旧金山湾区</t>
         </is>
       </c>
-      <c r="M29" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N29" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O29" s="55" t="inlineStr">
+      <c r="M30" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N30" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O30" s="56" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P29" s="50" t="inlineStr">
+      <c r="P30" s="51" t="inlineStr">
         <is>
           <t>X
 GitHub</t>
         </is>
       </c>
-      <c r="Q29" s="50" t="inlineStr">
+      <c r="Q30" s="51" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="50" customHeight="1">
-      <c r="A30" s="13" t="n"/>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="54" t="inlineStr">
+    <row r="31" ht="50" customHeight="1">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="55" t="inlineStr">
         <is>
           <t>Neil Parker</t>
         </is>
       </c>
-      <c r="I30" s="50" t="inlineStr">
+      <c r="I31" s="51" t="inlineStr">
         <is>
           <t>联合创始人兼 CTO（非华人，列作团队参考）</t>
         </is>
       </c>
-      <c r="J30" s="50" t="inlineStr">
+      <c r="J31" s="51" t="inlineStr">
         <is>
           <t>康奈尔大学校友</t>
         </is>
       </c>
-      <c r="K30" s="50" t="inlineStr">
+      <c r="K31" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3125,50 +3209,50 @@
           </r>
         </is>
       </c>
-      <c r="L30" s="50" t="inlineStr">
+      <c r="L31" s="51" t="inlineStr">
         <is>
           <t>美国旧金山湾区</t>
         </is>
       </c>
-      <c r="M30" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N30" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O30" s="55" t="inlineStr">
+      <c r="M31" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N31" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O31" s="56" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P30" s="50" t="inlineStr">
+      <c r="P31" s="51" t="inlineStr">
         <is>
           <t>X
 GitHub</t>
         </is>
       </c>
-      <c r="Q30" s="50" t="inlineStr">
+      <c r="Q31" s="51" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="64" customHeight="1">
-      <c r="A31" s="48" t="inlineStr">
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="49" t="inlineStr">
         <is>
           <t>CLI-Anything</t>
         </is>
       </c>
-      <c r="B31" s="49" t="inlineStr">
+      <c r="B32" s="50" t="inlineStr">
         <is>
           <t>智能体工具</t>
         </is>
       </c>
-      <c r="C31" s="50" t="inlineStr">
+      <c r="C32" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3189,36 +3273,36 @@
           </r>
         </is>
       </c>
-      <c r="D31" s="56" t="n">
+      <c r="D32" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="E31" s="57" t="n">
+      <c r="E32" s="58" t="n">
         <v>1195</v>
       </c>
-      <c r="F31" s="58" t="n">
+      <c r="F32" s="59" t="n">
         <v>55221</v>
       </c>
-      <c r="G31" s="50" t="inlineStr">
+      <c r="G32" s="51" t="inlineStr">
         <is>
           <t>10-18/19 #6 +589 → 10-20 #6 +606</t>
         </is>
       </c>
-      <c r="H31" s="54" t="inlineStr">
+      <c r="H32" s="55" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="I31" s="50" t="inlineStr">
+      <c r="I32" s="51" t="inlineStr">
         <is>
           <t>通讯作者、HKUDS / Data Intelligence Lab 负责人</t>
         </is>
       </c>
-      <c r="J31" s="50" t="inlineStr">
+      <c r="J32" s="51" t="inlineStr">
         <is>
           <t>University of Notre Dame 计算机博士；现港大计算机系助理教授</t>
         </is>
       </c>
-      <c r="K31" s="50" t="inlineStr">
+      <c r="K32" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3239,124 +3323,124 @@
           </r>
         </is>
       </c>
-      <c r="L31" s="50" t="inlineStr">
+      <c r="L32" s="51" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M31" s="50" t="inlineStr">
+      <c r="M32" s="51" t="inlineStr">
         <is>
           <t>chuang@cs.hku.hk
 chaohuang75@gmail.com</t>
         </is>
       </c>
-      <c r="N31" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O31" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P31" s="50" t="inlineStr">
+      <c r="N32" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O32" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P32" s="51" t="inlineStr">
         <is>
           <t>个人站
 GitHub 组织</t>
         </is>
       </c>
-      <c r="Q31" s="50" t="inlineStr">
+      <c r="Q32" s="51" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="64" customHeight="1">
-      <c r="A32" s="44" t="n"/>
-      <c r="B32" s="44" t="n"/>
-      <c r="C32" s="44" t="n"/>
-      <c r="D32" s="44" t="n"/>
-      <c r="E32" s="44" t="n"/>
-      <c r="F32" s="44" t="n"/>
-      <c r="G32" s="44" t="n"/>
-      <c r="H32" s="54" t="inlineStr">
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="44" t="n"/>
+      <c r="B33" s="44" t="n"/>
+      <c r="C33" s="44" t="n"/>
+      <c r="D33" s="44" t="n"/>
+      <c r="E33" s="44" t="n"/>
+      <c r="F33" s="44" t="n"/>
+      <c r="G33" s="44" t="n"/>
+      <c r="H33" s="55" t="inlineStr">
         <is>
           <t>Yuhao Yang（中文名未查到）</t>
         </is>
       </c>
-      <c r="I32" s="50" t="inlineStr">
+      <c r="I33" s="51" t="inlineStr">
         <is>
           <t>一作</t>
         </is>
       </c>
-      <c r="J32" s="50" t="inlineStr">
+      <c r="J33" s="51" t="inlineStr">
         <is>
           <t>香港大学博士（论文获 2026 ACM SIGKDD Dissertation Award Runner-Up）</t>
         </is>
       </c>
-      <c r="K32" s="50" t="inlineStr">
+      <c r="K33" s="51" t="inlineStr">
         <is>
           <t>主导 CLI-Anything；此前 UltraCUA、Aria-UI 等 computer-use 工作</t>
         </is>
       </c>
-      <c r="L32" s="50" t="inlineStr">
+      <c r="L33" s="51" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M32" s="50" t="inlineStr">
+      <c r="M33" s="51" t="inlineStr">
         <is>
           <t>itsyuhaoy@gmail.com
 yuhao-yang@outlook.com</t>
         </is>
       </c>
-      <c r="N32" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O32" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P32" s="50" t="inlineStr">
+      <c r="N33" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O33" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P33" s="51" t="inlineStr">
         <is>
           <t>个人站
 GitHub</t>
         </is>
       </c>
-      <c r="Q32" s="50" t="inlineStr">
+      <c r="Q33" s="51" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="64" customHeight="1">
-      <c r="A33" s="13" t="n"/>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="54" t="inlineStr">
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="13" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="13" t="n"/>
+      <c r="H34" s="55" t="inlineStr">
         <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="I33" s="50" t="inlineStr">
+      <c r="I34" s="51" t="inlineStr">
         <is>
           <t>共同作者</t>
         </is>
       </c>
-      <c r="J33" s="50" t="inlineStr">
+      <c r="J34" s="51" t="inlineStr">
         <is>
           <t>浙江大学自动化本科（2020–2024）；香港大学计算机博士在读（2024–）</t>
         </is>
       </c>
-      <c r="K33" s="50" t="inlineStr">
+      <c r="K34" s="51" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3385,50 +3469,51 @@
           </r>
         </is>
       </c>
-      <c r="L33" s="50" t="inlineStr">
+      <c r="L34" s="51" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
-      <c r="M33" s="50" t="inlineStr">
+      <c r="M34" s="51" t="inlineStr">
         <is>
           <t>tianyufan0504@gmail.com</t>
         </is>
       </c>
-      <c r="N33" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O33" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P33" s="50" t="inlineStr">
+      <c r="N34" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O34" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P34" s="51" t="inlineStr">
         <is>
           <t>个人站
 未在个人站显著标注主账号</t>
         </is>
       </c>
-      <c r="Q33" s="50" t="inlineStr">
+      <c r="Q34" s="51" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q33"/>
+  <autoFilter ref="A3:Q34"/>
   <mergeCells count="79">
-    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="E32:E34"/>
     <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="F30:F31"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="D31:D33"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="A20:A21"/>
@@ -3444,35 +3529,36 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F16:F19"/>
+    <mergeCell ref="A32:A34"/>
     <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G31:G33"/>
     <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A31:A33"/>
     <mergeCell ref="E27:E28"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="G25:G26"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="G27:G28"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="F32:F34"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E29:E30"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="D16:D19"/>
+    <mergeCell ref="E30:E31"/>
     <mergeCell ref="B9:B10"/>
+    <mergeCell ref="G30:G31"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D29:D30"/>
     <mergeCell ref="E13:E15"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C31:C33"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="B13:B15"/>
@@ -3480,7 +3566,6 @@
     <mergeCell ref="G16:G19"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F31:F33"/>
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A1:Q1"/>
@@ -3490,14 +3575,13 @@
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="E6:E7"/>
+    <mergeCell ref="B32:B34"/>
     <mergeCell ref="G20:G21"/>
-    <mergeCell ref="G29:G30"/>
     <mergeCell ref="F27:F28"/>
     <mergeCell ref="G4:G5"/>
-    <mergeCell ref="A29:A30"/>
     <mergeCell ref="G13:G15"/>
     <mergeCell ref="E22:E23"/>
-    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="D22:D23"/>
   </mergeCells>
   <hyperlinks>
@@ -3539,9 +3623,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId42"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -3685,10 +3770,10 @@
           </r>
         </is>
       </c>
-      <c r="E4" s="59" t="n">
+      <c r="E4" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="60" t="n">
+      <c r="F4" s="61" t="n">
         <v>5235</v>
       </c>
       <c r="G4" s="8" t="n">
@@ -3739,10 +3824,10 @@
           <t>开源编程智能体</t>
         </is>
       </c>
-      <c r="E5" s="61" t="n">
+      <c r="E5" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="60" t="n">
+      <c r="F5" s="61" t="n">
         <v>3965</v>
       </c>
       <c r="G5" s="8" t="n">
@@ -3793,10 +3878,10 @@
           <t>把代码库、文档、SQL、PDF 变成可查询知识图谱</t>
         </is>
       </c>
-      <c r="E6" s="61" t="n">
+      <c r="E6" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="60" t="n">
+      <c r="F6" s="61" t="n">
         <v>3643</v>
       </c>
       <c r="G6" s="8" t="n">
@@ -3850,7 +3935,7 @@
       <c r="E7" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="60" t="n">
+      <c r="F7" s="61" t="n">
         <v>1464</v>
       </c>
       <c r="G7" s="8" t="n">
@@ -3904,7 +3989,7 @@
       <c r="E8" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F8" s="60" t="n">
+      <c r="F8" s="61" t="n">
         <v>1333</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -3961,7 +4046,7 @@
       <c r="F9" s="29" t="n">
         <v>1197</v>
       </c>
-      <c r="G9" s="62" t="n">
+      <c r="G9" s="63" t="n">
         <v>693</v>
       </c>
       <c r="H9" s="30" t="n">
@@ -4009,10 +4094,10 @@
           <t>总星 41,558，PHP 解释器源码</t>
         </is>
       </c>
-      <c r="E10" s="61" t="n">
+      <c r="E10" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="60" t="n">
+      <c r="F10" s="61" t="n">
         <v>1003</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -4275,93 +4360,93 @@
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>🚀 ai-job-search</t>
         </is>
       </c>
-      <c r="B15" s="49" t="inlineStr">
+      <c r="B15" s="50" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C15" s="49" t="inlineStr">
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>应用</t>
         </is>
       </c>
-      <c r="D15" s="50" t="inlineStr">
+      <c r="D15" s="51" t="inlineStr">
         <is>
           <t>本机运行的 AI 求职框架，基于 Claude Code 评岗位、改简历、写求职信、备面试</t>
         </is>
       </c>
-      <c r="E15" s="63" t="n">
+      <c r="E15" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="64" t="n">
+      <c r="F15" s="65" t="n">
         <v>9949</v>
       </c>
-      <c r="G15" s="65" t="n">
+      <c r="G15" s="66" t="n">
         <v>3861</v>
       </c>
-      <c r="H15" s="66" t="n">
+      <c r="H15" s="67" t="n">
         <v>60514</v>
       </c>
-      <c r="I15" s="50" t="inlineStr">
+      <c r="I15" s="51" t="inlineStr">
         <is>
           <t>10-18/19 #1 +2,232🚀 → 10-20 #1 +3,856🚀 → 10-21 #1 +3,861</t>
         </is>
       </c>
-      <c r="J15" s="54" t="inlineStr">
+      <c r="J15" s="55" t="inlineStr">
         <is>
           <t>Mads Lorentzen</t>
         </is>
       </c>
-      <c r="K15" s="50" t="inlineStr">
+      <c r="K15" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="49" t="inlineStr">
+      <c r="L15" s="50" t="inlineStr">
         <is>
           <t>丹麦</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="49" t="inlineStr">
         <is>
           <t>VoiceStudio</t>
         </is>
       </c>
-      <c r="B16" s="49" t="inlineStr">
+      <c r="B16" s="50" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C16" s="49" t="inlineStr">
+      <c r="C16" s="50" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D16" s="50" t="inlineStr">
+      <c r="D16" s="51" t="inlineStr">
         <is>
           <t>完全本地的开源 ElevenLabs 替代品</t>
         </is>
       </c>
-      <c r="E16" s="67" t="n">
+      <c r="E16" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="57" t="n">
+      <c r="F16" s="53" t="n">
         <v>2082</v>
       </c>
       <c r="G16" s="68" t="n">
         <v>2082</v>
       </c>
-      <c r="H16" s="58" t="n">
+      <c r="H16" s="54" t="n">
         <v>75310</v>
       </c>
-      <c r="I16" s="50" t="inlineStr">
+      <c r="I16" s="51" t="inlineStr">
         <is>
           <t>10-18/19 #2 +2,082</t>
         </is>
@@ -4371,7 +4456,7 @@
           <t>未查到</t>
         </is>
       </c>
-      <c r="K16" s="50" t="inlineStr">
+      <c r="K16" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4383,39 +4468,39 @@
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>ruflo</t>
         </is>
       </c>
-      <c r="B17" s="49" t="inlineStr">
+      <c r="B17" s="50" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t>多智能体编排</t>
         </is>
       </c>
-      <c r="D17" s="50" t="inlineStr">
+      <c r="D17" s="51" t="inlineStr">
         <is>
           <t>多智能体蜂群编排框架</t>
         </is>
       </c>
-      <c r="E17" s="69" t="n">
+      <c r="E17" s="57" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="52" t="n">
+      <c r="F17" s="58" t="n">
         <v>1761</v>
       </c>
-      <c r="G17" s="70" t="n">
+      <c r="G17" s="69" t="n">
         <v>684</v>
       </c>
-      <c r="H17" s="53" t="n">
+      <c r="H17" s="59" t="n">
         <v>77830</v>
       </c>
-      <c r="I17" s="50" t="inlineStr">
+      <c r="I17" s="51" t="inlineStr">
         <is>
           <t>10-18/19 #7 +513 → 10-20 #7 +564 → 10-21 #9 +684</t>
         </is>
@@ -4425,7 +4510,7 @@
           <t>未查到</t>
         </is>
       </c>
-      <c r="K17" s="50" t="inlineStr">
+      <c r="K17" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4478,92 +4563,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="B1" s="71" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>每周开源 / 产品 Sourcing 周报（2026-10-19 – 10-25）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="72" t="inlineStr">
-        <is>
-          <t>全球项目 14 个 · 华人项目 15 个 · 核心人物 30 位</t>
+      <c r="B2" s="71" t="inlineStr">
+        <is>
+          <t>全球项目 14 个 · 华人项目 16 个 · 核心人物 31 位</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="73" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t>本周总览</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="74" t="inlineStr">
+      <c r="A5" s="73" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="75" t="inlineStr">
-        <is>
-          <t>本周进行中 · 已更新至 10-24（第 6/7 天），每天日报后自动刷新。</t>
+      <c r="B5" s="74" t="inlineStr">
+        <is>
+          <t>本周终版 · 覆盖 10-19 – 10-25（7/7 天）。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="74" t="inlineStr">
+      <c r="A6" s="73" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="75" t="inlineStr">
-        <is>
-          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search；已收录全球项目 14 个、华人项目 15 个，今日新增华人项目：Renhuai123/ziwei-doushu、OpenBMB/VoxCPM、MOVO AI、Agent Hunt · Monid。</t>
+      <c r="B6" s="74" t="inlineStr">
+        <is>
+          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search；已收录全球项目 14 个、华人项目 16 个，今日新增华人项目：zCAD AI（子虔科技 Zixel）。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="74" t="inlineStr">
+      <c r="A7" s="73" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="75" t="inlineStr">
+      <c r="B7" s="74" t="inlineStr">
         <is>
           <t>标「✨ 今日新增」的为今天首次上榜；灰色为前 3 周周报已出现过的项目，排在最后。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="75" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="77" t="inlineStr">
+      <c r="B10" s="76" t="inlineStr">
         <is>
           <t>黄底：日榜第 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="78" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>橙色：🚀 单日星增速明显放大（华人项目为 ≥ 前一天 1.5 倍）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="79" t="inlineStr">
+      <c r="B12" s="78" t="inlineStr">
         <is>
           <t>灰色斜体：未查到</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="80" t="inlineStr">
+      <c r="B14" s="79" t="inlineStr">
         <is>
           <t>网页版：https://psylch.github.io/rising-projects/2026-10-25/</t>
         </is>
@@ -4584,7 +4669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6825,201 +6910,201 @@
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="31" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>zCAD AI（子虔科技 Zixel）</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>Jinjing Liang（中文名未查到）</t>
+          <t>龚敏彦（Gong Minyan）</t>
         </is>
       </c>
       <c r="C85" s="26" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>来源1</t>
         </is>
       </c>
       <c r="E85" s="34" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/jinjingliang</t>
+          <t>https://zcad.ai/about</t>
         </is>
       </c>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="22" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>zCAD AI（子虔科技 Zixel）</t>
         </is>
       </c>
       <c r="B86" s="18" t="inlineStr">
         <is>
-          <t>Jinjing Liang（中文名未查到）</t>
+          <t>龚敏彦（Gong Minyan）</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D86" s="18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>来源2</t>
         </is>
       </c>
       <c r="E86" s="43" t="inlineStr">
         <is>
-          <t>https://x.com/JinjingLiang</t>
+          <t>https://paper.cnstock.com/html/2024-12/28/content_2011697.htm</t>
         </is>
       </c>
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="31" t="inlineStr">
         <is>
-          <t>stablyai/orca</t>
+          <t>zCAD AI（子虔科技 Zixel）</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>Jinjing Liang（中文名未查到）</t>
+          <t>龚敏彦（Gong Minyan）</t>
         </is>
       </c>
       <c r="C87" s="26" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D87" s="27" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>来源3</t>
         </is>
       </c>
       <c r="E87" s="34" t="inlineStr">
         <is>
-          <t>https://github.com/AmethystLiang</t>
+          <t>https://m.qcc.com/firm/58cc815b3bafe3d74cab2e4eb76fe021.html</t>
         </is>
       </c>
     </row>
     <row r="88" ht="36" customHeight="1">
       <c r="A88" s="22" t="inlineStr">
         <is>
+          <t>zCAD AI（子虔科技 Zixel）</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>龚敏彦（Gong Minyan）</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E88" s="43" t="inlineStr">
+        <is>
+          <t>https://www.zixel3d.com/news/zixel-gstarsoft-3D-CAD-new-launch-at-gstarsoft-3D-foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="31" t="inlineStr">
+        <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B88" s="18" t="inlineStr">
+      <c r="B89" s="27" t="inlineStr">
         <is>
           <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
-      <c r="C88" s="17" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D88" s="18" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E88" s="43" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="31" t="inlineStr">
+      <c r="C89" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D89" s="27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E89" s="34" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/jinjingliang</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="22" t="inlineStr">
         <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B89" s="27" t="inlineStr">
-        <is>
-          <t>Neil Parker</t>
-        </is>
-      </c>
-      <c r="C89" s="26" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D89" s="27" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E89" s="34" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/neilwilliamparker</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="22" t="inlineStr">
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E90" s="43" t="inlineStr">
+        <is>
+          <t>https://x.com/JinjingLiang</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="A91" s="31" t="inlineStr">
         <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B90" s="18" t="inlineStr">
-        <is>
-          <t>Neil Parker</t>
-        </is>
-      </c>
-      <c r="C90" s="17" t="inlineStr">
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>Jinjing Liang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C91" s="26" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D90" s="18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E90" s="43" t="inlineStr">
-        <is>
-          <t>https://x.com/nwparker_</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="31" t="inlineStr">
+      <c r="D91" s="27" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E91" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/AmethystLiang</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="36" customHeight="1">
+      <c r="A92" s="22" t="inlineStr">
         <is>
           <t>stablyai/orca</t>
         </is>
       </c>
-      <c r="B91" s="27" t="inlineStr">
-        <is>
-          <t>Neil Parker</t>
-        </is>
-      </c>
-      <c r="C91" s="26" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D91" s="27" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E91" s="34" t="inlineStr">
-        <is>
-          <t>https://github.com/nwparker</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="22" t="inlineStr">
-        <is>
-          <t>stablyai/orca</t>
-        </is>
-      </c>
       <c r="B92" s="18" t="inlineStr">
         <is>
-          <t>Neil Parker</t>
+          <t>Jinjing Liang（中文名未查到）</t>
         </is>
       </c>
       <c r="C92" s="17" t="inlineStr">
@@ -7041,39 +7126,39 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="31" t="inlineStr">
         <is>
-          <t>HKUDS/CLI-Anything</t>
+          <t>stablyai/orca</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>Huang Chao（黄超）</t>
+          <t>Neil Parker</t>
         </is>
       </c>
       <c r="C93" s="26" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D93" s="27" t="inlineStr">
         <is>
-          <t>个人站</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E93" s="34" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/chaoh</t>
+          <t>https://linkedin.com/in/neilwilliamparker</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="22" t="inlineStr">
         <is>
-          <t>HKUDS/CLI-Anything</t>
+          <t>stablyai/orca</t>
         </is>
       </c>
       <c r="B94" s="18" t="inlineStr">
         <is>
-          <t>Huang Chao（黄超）</t>
+          <t>Neil Parker</t>
         </is>
       </c>
       <c r="C94" s="17" t="inlineStr">
@@ -7083,51 +7168,51 @@
       </c>
       <c r="D94" s="18" t="inlineStr">
         <is>
-          <t>GitHub 组织</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E94" s="43" t="inlineStr">
         <is>
-          <t>https://github.com/HKUDS</t>
+          <t>https://x.com/nwparker_</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="31" t="inlineStr">
         <is>
-          <t>HKUDS/CLI-Anything</t>
+          <t>stablyai/orca</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>Huang Chao（黄超）</t>
+          <t>Neil Parker</t>
         </is>
       </c>
       <c r="C95" s="26" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>其他联系</t>
         </is>
       </c>
       <c r="D95" s="27" t="inlineStr">
         <is>
-          <t>来源1</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="E95" s="34" t="inlineStr">
         <is>
-          <t>https://datascience.hku.hk/people/chao-huang/</t>
+          <t>https://github.com/nwparker</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="22" t="inlineStr">
         <is>
-          <t>HKUDS/CLI-Anything</t>
+          <t>stablyai/orca</t>
         </is>
       </c>
       <c r="B96" s="18" t="inlineStr">
         <is>
-          <t>Huang Chao（黄超）</t>
+          <t>Neil Parker</t>
         </is>
       </c>
       <c r="C96" s="17" t="inlineStr">
@@ -7137,12 +7222,12 @@
       </c>
       <c r="D96" s="18" t="inlineStr">
         <is>
-          <t>来源2</t>
+          <t>来源1</t>
         </is>
       </c>
       <c r="E96" s="43" t="inlineStr">
         <is>
-          <t>https://www.ai.hku.hk/people/academic-staff/chuang</t>
+          <t>https://www.ycombinator.com/companies/stably-ai-orca</t>
         </is>
       </c>
     </row>
@@ -7159,125 +7244,125 @@
       </c>
       <c r="C97" s="26" t="inlineStr">
         <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D97" s="27" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E97" s="34" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/chaoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B98" s="18" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D98" s="18" t="inlineStr">
+        <is>
+          <t>GitHub 组织</t>
+        </is>
+      </c>
+      <c r="E98" s="43" t="inlineStr">
+        <is>
+          <t>https://github.com/HKUDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="31" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B99" s="27" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C99" s="26" t="inlineStr">
+        <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D97" s="27" t="inlineStr">
+      <c r="D99" s="27" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E99" s="34" t="inlineStr">
+        <is>
+          <t>https://datascience.hku.hk/people/chao-huang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D100" s="18" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E100" s="43" t="inlineStr">
+        <is>
+          <t>https://www.ai.hku.hk/people/academic-staff/chuang</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="31" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B101" s="27" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C101" s="26" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D101" s="27" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E97" s="34" t="inlineStr">
+      <c r="E101" s="34" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="36" customHeight="1">
-      <c r="A98" s="22" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B98" s="18" t="inlineStr">
-        <is>
-          <t>Yuhao Yang（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C98" s="17" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D98" s="18" t="inlineStr">
-        <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E98" s="43" t="inlineStr">
-        <is>
-          <t>https://yuh-yang.github.io</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="36" customHeight="1">
-      <c r="A99" s="31" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B99" s="27" t="inlineStr">
-        <is>
-          <t>Yuhao Yang（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C99" s="26" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D99" s="27" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E99" s="34" t="inlineStr">
-        <is>
-          <t>https://github.com/yuh-yang</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="36" customHeight="1">
-      <c r="A100" s="22" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B100" s="18" t="inlineStr">
-        <is>
-          <t>Yuhao Yang（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C100" s="17" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D100" s="18" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E100" s="43" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2606.03854</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="36" customHeight="1">
-      <c r="A101" s="31" t="inlineStr">
-        <is>
-          <t>HKUDS/CLI-Anything</t>
-        </is>
-      </c>
-      <c r="B101" s="27" t="inlineStr">
-        <is>
-          <t>Tianyu Fan（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C101" s="26" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D101" s="27" t="inlineStr">
-        <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E101" s="34" t="inlineStr">
-        <is>
-          <t>https://tianyufan0504.github.io/</t>
         </is>
       </c>
     </row>
@@ -7289,27 +7374,135 @@
       </c>
       <c r="B102" s="18" t="inlineStr">
         <is>
+          <t>Yuhao Yang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D102" s="18" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E102" s="43" t="inlineStr">
+        <is>
+          <t>https://yuh-yang.github.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
+      <c r="A103" s="31" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>Yuhao Yang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C103" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D103" s="27" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E103" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/yuh-yang</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="A104" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B104" s="18" t="inlineStr">
+        <is>
+          <t>Yuhao Yang（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D104" s="18" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E104" s="43" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.03854</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="36" customHeight="1">
+      <c r="A105" s="31" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
           <t>Tianyu Fan（中文名未查到）</t>
         </is>
       </c>
-      <c r="C102" s="17" t="inlineStr">
+      <c r="C105" s="26" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D105" s="27" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E105" s="34" t="inlineStr">
+        <is>
+          <t>https://tianyufan0504.github.io/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="36" customHeight="1">
+      <c r="A106" s="22" t="inlineStr">
+        <is>
+          <t>HKUDS/CLI-Anything</t>
+        </is>
+      </c>
+      <c r="B106" s="18" t="inlineStr">
+        <is>
+          <t>Tianyu Fan（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D102" s="18" t="inlineStr">
+      <c r="D106" s="18" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E102" s="43" t="inlineStr">
+      <c r="E106" s="43" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.03854</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E102"/>
+  <autoFilter ref="A3:E106"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -7414,6 +7607,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId103"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/2026-10-25/weekly-2026-10-25.xlsx
+++ b/2026-10-25/weekly-2026-10-25.xlsx
@@ -16,9 +16,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'华人项目'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全球项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$106</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'链接'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$106</definedName>
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -409,9 +409,6 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -424,10 +421,16 @@
     <xf numFmtId="166" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -841,7 +844,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>按本周 GitHub 新增星排序（PH 项目排后），🚀 表示本周出现单日星增速 ≥ 前一天 1.5 倍，✨ 今日新增 为今天首次出现。  本周新增星 = 本周日榜各天新增合计；黄底 = 日榜第 1；橙色 = 单日增速翻倍信号；灰色 = 未查到。</t>
+          <t>按本周 GitHub 新增星排序（PH 项目排后），🚀 表示本周出现单日星增速 ≥ 前一天 1.5 倍。  本周新增星 = 本周日榜各天新增合计；黄底 = 日榜第 1；橙色 = 单日增速翻倍信号；灰色 = 未查到。</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3929,7 +3932,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>总星 12,315，给编程 CLI 智能体的长期记忆，方便在不同厂商的智能体之间交接</t>
+          <t>给编程 CLI 智能体的长期记忆，方便在不同厂商的智能体之间交接</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
@@ -4019,15 +4022,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="64" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>supabase</t>
+          <t>/dev/null</t>
         </is>
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
@@ -4037,115 +4040,123 @@
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
-          <t>Postgres 开发平台</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>1197</v>
-      </c>
-      <c r="G9" s="63" t="n">
-        <v>693</v>
-      </c>
-      <c r="H9" s="30" t="n">
-        <v>113473</v>
+          <t>面向开发者的社交网络，JetBrains 办公室 48 小时直播从零写出来的开源项目</t>
+        </is>
+      </c>
+      <c r="E9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="37" t="n">
+        <v>401</v>
       </c>
       <c r="I9" s="27" t="inlineStr">
         <is>
-          <t>10-22 #7 +504 → 10-23 #4 +693</t>
+          <t>10-20 #1</t>
         </is>
       </c>
       <c r="J9" s="31" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Nuno Maduro、Brent Roose、Matthieu Napoli、Pauline Vos 等</t>
         </is>
       </c>
       <c r="K9" s="27" t="inlineStr">
         <is>
+          <t>JetBrains 直播</t>
+        </is>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Beam.win</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>在一台 Mac 上跑 AI 智能体，在另一台上直接用它的窗口</t>
+        </is>
+      </c>
+      <c r="E10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="33" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>🚀 php-src</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="41" t="n">
+        <v>293</v>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>10-19 #1</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>maker Hiten Shah、Sam Asante</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Inbox Zero</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>总星 41,558，PHP 解释器源码</t>
-        </is>
-      </c>
-      <c r="E10" s="62" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="61" t="n">
-        <v>1003</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>716</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>41558</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>10-23 #6 +287 → 10-24 #3 +716🚀</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>PHP 官方</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>/dev/null</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>面向开发者的社交网络，JetBrains 办公室 48 小时直播从零写出来的开源项目</t>
+          <t>开源 AI 邮件助手兼客户端，对标 Superhuman</t>
         </is>
       </c>
       <c r="E11" s="39" t="n">
@@ -4162,21 +4173,21 @@
         </is>
       </c>
       <c r="H11" s="37" t="n">
-        <v>401</v>
+        <v>279</v>
       </c>
       <c r="I11" s="27" t="inlineStr">
         <is>
-          <t>10-20 #1</t>
+          <t>10-18 #1</t>
         </is>
       </c>
       <c r="J11" s="31" t="inlineStr">
         <is>
-          <t>Nuno Maduro、Brent Roose、Matthieu Napoli、Pauline Vos 等</t>
+          <t>Elie Steinbock</t>
         </is>
       </c>
       <c r="K11" s="27" t="inlineStr">
         <is>
-          <t>JetBrains 直播</t>
+          <t>以色列特拉维夫</t>
         </is>
       </c>
       <c r="L11" s="33" t="inlineStr">
@@ -4186,343 +4197,169 @@
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Product Hunt Visual Launch Editor</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="A12" s="49" t="inlineStr">
+        <is>
+          <t>🚀 ai-job-search</t>
+        </is>
+      </c>
+      <c r="B12" s="50" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C12" s="50" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>本机运行的 AI 求职框架，基于 Claude Code 评岗位、改简历、写求职信、备面试</t>
+        </is>
+      </c>
+      <c r="E12" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="64" t="n">
+        <v>9949</v>
+      </c>
+      <c r="G12" s="65" t="n">
+        <v>3861</v>
+      </c>
+      <c r="H12" s="66" t="n">
+        <v>60514</v>
+      </c>
+      <c r="I12" s="51" t="inlineStr">
+        <is>
+          <t>10-18/19 #1 +2,232🚀 → 10-20 #1 +3,856🚀 → 10-21 #1 +3,861</t>
+        </is>
+      </c>
+      <c r="J12" s="55" t="inlineStr">
+        <is>
+          <t>Mads Lorentzen</t>
+        </is>
+      </c>
+      <c r="K12" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="50" t="inlineStr">
+        <is>
+          <t>丹麦</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>VoiceStudio</t>
+        </is>
+      </c>
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>边做边预览你的 PH 发布页</t>
-        </is>
-      </c>
-      <c r="E12" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>完全本地的开源 ElevenLabs 替代品</t>
+        </is>
+      </c>
+      <c r="E13" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="58" t="n">
+        <v>2082</v>
+      </c>
+      <c r="G13" s="68" t="n">
+        <v>2082</v>
+      </c>
+      <c r="H13" s="59" t="n">
+        <v>75310</v>
+      </c>
+      <c r="I13" s="51" t="inlineStr">
+        <is>
+          <t>10-18/19 #2 +2,082</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K13" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="40" t="inlineStr">
+      <c r="L13" s="24" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="49" t="inlineStr">
+        <is>
+          <t>ruflo</t>
+        </is>
+      </c>
+      <c r="B14" s="50" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C14" s="50" t="inlineStr">
+        <is>
+          <t>多智能体编排</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>多智能体蜂群编排框架</t>
+        </is>
+      </c>
+      <c r="E14" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="53" t="n">
+        <v>1761</v>
+      </c>
+      <c r="G14" s="70" t="n">
+        <v>684</v>
+      </c>
+      <c r="H14" s="54" t="n">
+        <v>77830</v>
+      </c>
+      <c r="I14" s="51" t="inlineStr">
+        <is>
+          <t>10-18/19 #7 +513 → 10-20 #7 +564 → 10-21 #9 +684</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K14" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="41" t="n">
-        <v>350</v>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>10-23 #1</t>
-        </is>
-      </c>
-      <c r="J12" s="22" t="inlineStr">
-        <is>
-          <t>Product Hunt 官方</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>Beam.win</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>在一台 Mac 上跑 AI 智能体，在另一台上直接用它的窗口</t>
-        </is>
-      </c>
-      <c r="E13" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="37" t="n">
-        <v>293</v>
-      </c>
-      <c r="I13" s="27" t="inlineStr">
-        <is>
-          <t>10-19 #1</t>
-        </is>
-      </c>
-      <c r="J13" s="31" t="inlineStr">
-        <is>
-          <t>maker Hiten Shah、Sam Asante</t>
-        </is>
-      </c>
-      <c r="K13" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="33" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Inbox Zero</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>开源 AI 邮件助手兼客户端，对标 Superhuman</t>
-        </is>
-      </c>
-      <c r="E14" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="41" t="n">
-        <v>279</v>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>10-18 #1</t>
-        </is>
-      </c>
-      <c r="J14" s="22" t="inlineStr">
-        <is>
-          <t>Elie Steinbock</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>以色列特拉维夫</t>
-        </is>
-      </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="49" t="inlineStr">
-        <is>
-          <t>🚀 ai-job-search</t>
-        </is>
-      </c>
-      <c r="B15" s="50" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C15" s="50" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="D15" s="51" t="inlineStr">
-        <is>
-          <t>本机运行的 AI 求职框架，基于 Claude Code 评岗位、改简历、写求职信、备面试</t>
-        </is>
-      </c>
-      <c r="E15" s="64" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="65" t="n">
-        <v>9949</v>
-      </c>
-      <c r="G15" s="66" t="n">
-        <v>3861</v>
-      </c>
-      <c r="H15" s="67" t="n">
-        <v>60514</v>
-      </c>
-      <c r="I15" s="51" t="inlineStr">
-        <is>
-          <t>10-18/19 #1 +2,232🚀 → 10-20 #1 +3,856🚀 → 10-21 #1 +3,861</t>
-        </is>
-      </c>
-      <c r="J15" s="55" t="inlineStr">
-        <is>
-          <t>Mads Lorentzen</t>
-        </is>
-      </c>
-      <c r="K15" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="50" t="inlineStr">
-        <is>
-          <t>丹麦</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="49" t="inlineStr">
-        <is>
-          <t>VoiceStudio</t>
-        </is>
-      </c>
-      <c r="B16" s="50" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C16" s="50" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D16" s="51" t="inlineStr">
-        <is>
-          <t>完全本地的开源 ElevenLabs 替代品</t>
-        </is>
-      </c>
-      <c r="E16" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="53" t="n">
-        <v>2082</v>
-      </c>
-      <c r="G16" s="68" t="n">
-        <v>2082</v>
-      </c>
-      <c r="H16" s="54" t="n">
-        <v>75310</v>
-      </c>
-      <c r="I16" s="51" t="inlineStr">
-        <is>
-          <t>10-18/19 #2 +2,082</t>
-        </is>
-      </c>
-      <c r="J16" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K16" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L16" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
-        <is>
-          <t>ruflo</t>
-        </is>
-      </c>
-      <c r="B17" s="50" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C17" s="50" t="inlineStr">
-        <is>
-          <t>多智能体编排</t>
-        </is>
-      </c>
-      <c r="D17" s="51" t="inlineStr">
-        <is>
-          <t>多智能体蜂群编排框架</t>
-        </is>
-      </c>
-      <c r="E17" s="57" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="58" t="n">
-        <v>1761</v>
-      </c>
-      <c r="G17" s="69" t="n">
-        <v>684</v>
-      </c>
-      <c r="H17" s="59" t="n">
-        <v>77830</v>
-      </c>
-      <c r="I17" s="51" t="inlineStr">
-        <is>
-          <t>10-18/19 #7 +513 → 10-20 #7 +564 → 10-21 #9 +684</t>
-        </is>
-      </c>
-      <c r="J17" s="23" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K17" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L17" s="24" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:L17"/>
+  <autoFilter ref="A3:L14"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
@@ -4539,9 +4376,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -4563,92 +4397,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>每周开源 / 产品 Sourcing 周报（2026-10-19 – 10-25）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="71" t="inlineStr">
-        <is>
-          <t>全球项目 14 个 · 华人项目 16 个 · 核心人物 31 位</t>
+      <c r="B2" s="72" t="inlineStr">
+        <is>
+          <t>全球项目 11 个 · 华人项目 16 个 · 核心人物 31 位</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="72" t="inlineStr">
+      <c r="B4" s="73" t="inlineStr">
         <is>
           <t>本周总览</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="73" t="inlineStr">
+      <c r="A5" s="74" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="74" t="inlineStr">
-        <is>
-          <t>本周终版 · 覆盖 10-19 – 10-25（7/7 天）。</t>
+      <c r="B5" s="75" t="inlineStr">
+        <is>
+          <t>本周定稿 · 覆盖 10-19 – 10-25（7/7 天）。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="73" t="inlineStr">
+      <c r="A6" s="74" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="74" t="inlineStr">
-        <is>
-          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search；已收录全球项目 14 个、华人项目 16 个，今日新增华人项目：zCAD AI（子虔科技 Zixel）。</t>
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>本周 GitHub 累计星增第一是 MadsLorentzen/ai-job-search（上周已收录）；本周新上榜里最猛的是 DietrichGebert/ponytail（3 天 +5,235 星）。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="73" t="inlineStr">
+      <c r="A7" s="74" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="74" t="inlineStr">
-        <is>
-          <t>标「✨ 今日新增」的为今天首次上榜；灰色为前 3 周周报已出现过的项目，排在最后。</t>
+      <c r="B7" s="75" t="inlineStr">
+        <is>
+          <t>收录全球项目 11 个、华人项目 16 个；灰色为前 3 周周报已出现过的项目，排在最后。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="75" t="inlineStr">
+      <c r="B9" s="76" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>黄底：日榜第 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="77" t="inlineStr">
+      <c r="B11" s="78" t="inlineStr">
         <is>
           <t>橙色：🚀 单日星增速明显放大（华人项目为 ≥ 前一天 1.5 倍）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="78" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>灰色斜体：未查到</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="79" t="inlineStr">
+      <c r="B14" s="80" t="inlineStr">
         <is>
           <t>网页版：https://psylch.github.io/rising-projects/2026-10-25/</t>
         </is>
